--- a/tests/reports/Test_Analysis_Report.xlsx
+++ b/tests/reports/Test_Analysis_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="311">
   <si>
     <t>Test ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>2396ms</t>
+    <t>1974ms</t>
   </si>
   <si>
     <t>Assertion passed successfully</t>
@@ -68,7 +68,7 @@
     <t>Verify brand name PayBuddy header exists</t>
   </si>
   <si>
-    <t>100ms</t>
+    <t>284ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-003</t>
@@ -77,7 +77,7 @@
     <t>Verify form email input label</t>
   </si>
   <si>
-    <t>48ms</t>
+    <t>69ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-004</t>
@@ -86,7 +86,7 @@
     <t>Verify form password input label</t>
   </si>
   <si>
-    <t>71ms</t>
+    <t>35ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-005</t>
@@ -95,7 +95,7 @@
     <t>Verify Sign In button is present</t>
   </si>
   <si>
-    <t>54ms</t>
+    <t>41ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-006</t>
@@ -104,7 +104,7 @@
     <t>Verify secure access footer notice is present</t>
   </si>
   <si>
-    <t>47ms</t>
+    <t>36ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-007</t>
@@ -113,844 +113,838 @@
     <t>Verify branding subtitle text exists</t>
   </si>
   <si>
+    <t>TC-WEB-UI-008</t>
+  </si>
+  <si>
+    <t>Verify email input field placeholder</t>
+  </si>
+  <si>
+    <t>39ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-009</t>
+  </si>
+  <si>
+    <t>Verify password input field placeholder</t>
+  </si>
+  <si>
+    <t>34ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-010</t>
+  </si>
+  <si>
+    <t>Verify font family CSS on headers</t>
+  </si>
+  <si>
+    <t>40ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-011</t>
+  </si>
+  <si>
+    <t>Verify primary brand color on buttons</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-012</t>
+  </si>
+  <si>
+    <t>Verify centered block layout</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-013</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at mobile width 360px</t>
+  </si>
+  <si>
+    <t>927ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-014</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at tablet width 768px</t>
+  </si>
+  <si>
+    <t>941ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-015</t>
+  </si>
+  <si>
+    <t>Restore browser window maximization state</t>
+  </si>
+  <si>
+    <t>45ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-016</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for email input</t>
+  </si>
+  <si>
+    <t>27ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-017</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for password input</t>
+  </si>
+  <si>
+    <t>55ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-018</t>
+  </si>
+  <si>
+    <t>Verify card wrapper styles (border-radius)</t>
+  </si>
+  <si>
+    <t>49ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-019</t>
+  </si>
+  <si>
+    <t>Verify background styling matches design spec</t>
+  </si>
+  <si>
+    <t>44ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-020</t>
+  </si>
+  <si>
+    <t>Verify focus state click handler does not crash</t>
+  </si>
+  <si>
+    <t>147ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-021</t>
+  </si>
+  <si>
+    <t>Verify top-level container viewport classes</t>
+  </si>
+  <si>
+    <t>57ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-022</t>
+  </si>
+  <si>
+    <t>Verify branding and form division layout margins</t>
+  </si>
+  <si>
+    <t>38ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-023</t>
+  </si>
+  <si>
+    <t>Verify clear textual contrast for reader accessibility</t>
+  </si>
+  <si>
+    <t>53ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-024</t>
+  </si>
+  <si>
+    <t>Verify page scales properly without layout clipping</t>
+  </si>
+  <si>
+    <t>33ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-025</t>
+  </si>
+  <si>
+    <t>Verify smooth interactive transitions on button inputs</t>
+  </si>
+  <si>
+    <t>31ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-001</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Verify invalid login rejection message</t>
+  </si>
+  <si>
+    <t>1427ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-002</t>
+  </si>
+  <si>
+    <t>Verify rejection of nonexistent email</t>
+  </si>
+  <si>
+    <t>1220ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-003</t>
+  </si>
+  <si>
+    <t>Verify successful login with valid credentials redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>2197ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-004</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Total Customers count</t>
+  </si>
+  <si>
+    <t>304ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-005</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Active Sales count</t>
+  </si>
+  <si>
+    <t>46ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-006</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Pending Installments count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-007</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Today's Due count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-008</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Outstanding Balance amount</t>
+  </si>
+  <si>
+    <t>58ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-009</t>
+  </si>
+  <si>
+    <t>Navigate to customers page and verify header</t>
+  </si>
+  <si>
+    <t>232ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-010</t>
+  </si>
+  <si>
+    <t>Verify add new customer input inputs are present</t>
+  </si>
+  <si>
+    <t>80ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-011</t>
+  </si>
+  <si>
+    <t>Verify customer creation and entry addition to table</t>
+  </si>
+  <si>
+    <t>2614ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-012</t>
+  </si>
+  <si>
+    <t>Verify presence of seeded customer</t>
+  </si>
+  <si>
+    <t>52ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-013</t>
+  </si>
+  <si>
+    <t>Navigate to specific customer profile page</t>
+  </si>
+  <si>
+    <t>1424ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-014</t>
+  </si>
+  <si>
+    <t>Verify phone number exists on profile detail bar</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-015</t>
+  </si>
+  <si>
+    <t>Verify Total Amount financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-016</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount financial card is 0 INR</t>
+  </si>
+  <si>
     <t>51ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-008</t>
-  </si>
-  <si>
-    <t>Verify email input field placeholder</t>
-  </si>
-  <si>
-    <t>53ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-009</t>
-  </si>
-  <si>
-    <t>Verify password input field placeholder</t>
-  </si>
-  <si>
-    <t>49ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-010</t>
-  </si>
-  <si>
-    <t>Verify font family CSS on headers</t>
-  </si>
-  <si>
-    <t>70ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-011</t>
-  </si>
-  <si>
-    <t>Verify primary brand color on buttons</t>
-  </si>
-  <si>
-    <t>45ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-012</t>
-  </si>
-  <si>
-    <t>Verify centered block layout</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-013</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at mobile width 360px</t>
-  </si>
-  <si>
-    <t>947ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-014</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at tablet width 768px</t>
-  </si>
-  <si>
-    <t>933ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-015</t>
-  </si>
-  <si>
-    <t>Restore browser window maximization state</t>
-  </si>
-  <si>
-    <t>43ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-016</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for email input</t>
-  </si>
-  <si>
-    <t>57ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-017</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for password input</t>
-  </si>
-  <si>
-    <t>62ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-018</t>
-  </si>
-  <si>
-    <t>Verify card wrapper styles (border-radius)</t>
-  </si>
-  <si>
-    <t>60ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-019</t>
-  </si>
-  <si>
-    <t>Verify background styling matches design spec</t>
-  </si>
-  <si>
-    <t>78ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-020</t>
-  </si>
-  <si>
-    <t>Verify focus state click handler does not crash</t>
-  </si>
-  <si>
-    <t>186ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-021</t>
-  </si>
-  <si>
-    <t>Verify top-level container viewport classes</t>
-  </si>
-  <si>
-    <t>63ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-022</t>
-  </si>
-  <si>
-    <t>Verify branding and form division layout margins</t>
-  </si>
-  <si>
-    <t>40ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-023</t>
-  </si>
-  <si>
-    <t>Verify clear textual contrast for reader accessibility</t>
-  </si>
-  <si>
-    <t>42ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-024</t>
-  </si>
-  <si>
-    <t>Verify page scales properly without layout clipping</t>
+    <t>TC-WEB-FUNC-017</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-018</t>
+  </si>
+  <si>
+    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-019</t>
+  </si>
+  <si>
+    <t>Verify redirect to record payment page</t>
+  </si>
+  <si>
+    <t>922ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-020</t>
+  </si>
+  <si>
+    <t>Verify remaining balance display match before payment</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-021</t>
+  </si>
+  <si>
+    <t>Record payment E2E execution and redirection validation</t>
+  </si>
+  <si>
+    <t>3425ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-022</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
+  </si>
+  <si>
+    <t>1363ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-023</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount updates to 200 INR in customer card</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-024</t>
+  </si>
+  <si>
+    <t>Verify recorded payment entry list matches mode UPI</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-025</t>
+  </si>
+  <si>
+    <t>Verify sales management index loads properly</t>
+  </si>
+  <si>
+    <t>754ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-026</t>
+  </si>
+  <si>
+    <t>Verify sales search filter works properly</t>
+  </si>
+  <si>
+    <t>774ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-027</t>
+  </si>
+  <si>
+    <t>Navigate to Create New Sale form</t>
+  </si>
+  <si>
+    <t>791ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-028</t>
+  </si>
+  <si>
+    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
+  </si>
+  <si>
+    <t>701ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-029</t>
+  </si>
+  <si>
+    <t>Create sale and verify redirect back to sales table</t>
+  </si>
+  <si>
+    <t>463ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-030</t>
+  </si>
+  <si>
+    <t>Verify Payments page path and title</t>
+  </si>
+  <si>
+    <t>848ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-031</t>
+  </si>
+  <si>
+    <t>Verify E2E transaction exists in master list</t>
+  </si>
+  <si>
+    <t>82ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-032</t>
+  </si>
+  <si>
+    <t>Verify Ledger Book page loads</t>
+  </si>
+  <si>
+    <t>900ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-033</t>
+  </si>
+  <si>
+    <t>Verify ledger records contain client name</t>
+  </si>
+  <si>
+    <t>61ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-034</t>
+  </si>
+  <si>
+    <t>Verify Installments page title</t>
+  </si>
+  <si>
+    <t>672ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-035</t>
+  </si>
+  <si>
+    <t>Verify customer details exist on installment board</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-036</t>
+  </si>
+  <si>
+    <t>Verify direct Dashboard URL redirect</t>
+  </si>
+  <si>
+    <t>259ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-037</t>
+  </si>
+  <si>
+    <t>Verify customer data updates dynamically on UI edit</t>
+  </si>
+  <si>
+    <t>4735ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-038</t>
+  </si>
+  <si>
+    <t>Verify logout route terminates session and redirects to sign in</t>
+  </si>
+  <si>
+    <t>917ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-039</t>
+  </si>
+  <si>
+    <t>Verify unauthorized dashboard access redirects to login</t>
+  </si>
+  <si>
+    <t>2154ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-040</t>
+  </si>
+  <si>
+    <t>Verify unauthorized customer details access redirects to login</t>
+  </si>
+  <si>
+    <t>2557ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-001</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting positive amount</t>
+  </si>
+  <si>
+    <t>84ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-002</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting zero amount</t>
+  </si>
+  <si>
+    <t>1ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-003</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting negative amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-004</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting large millions scale amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-005</t>
+  </si>
+  <si>
+    <t>Test formatCurrency decimal rounding functionality</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-006</t>
+  </si>
+  <si>
+    <t>Test formatDate string matching date details</t>
+  </si>
+  <si>
+    <t>15ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-007</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for null values</t>
+  </si>
+  <si>
+    <t>0ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-008</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for 0 value</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-009</t>
+  </si>
+  <si>
+    <t>Test formatDateTime details formatting</t>
+  </si>
+  <si>
+    <t>2ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-010</t>
+  </si>
+  <si>
+    <t>Test formatDateTime null timestamp handling</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-011</t>
+  </si>
+  <si>
+    <t>Verify email validation for valid string</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-012</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing TLD</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-013</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing alias prefix</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-014</t>
+  </si>
+  <si>
+    <t>Verify phone validation for standard 10 digit number</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-015</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks short length</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-016</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks alphabetic characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-017</t>
+  </si>
+  <si>
+    <t>Verify interest formula multiplication logic</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-018</t>
+  </si>
+  <si>
+    <t>Verify installment partitioning amount division</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-019</t>
+  </si>
+  <si>
+    <t>Verify remaining balance arithmetic subtraction</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-020</t>
+  </si>
+  <si>
+    <t>Verify mock environment manifest validator passes</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-001</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Verify email required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>411ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-002</t>
+  </si>
+  <si>
+    <t>Verify password required constraint is enabled on form</t>
   </si>
   <si>
     <t>37ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-025</t>
-  </si>
-  <si>
-    <t>Verify smooth interactive transitions on button inputs</t>
-  </si>
-  <si>
-    <t>35ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-001</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>Verify invalid login rejection message</t>
-  </si>
-  <si>
-    <t>1946ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-002</t>
-  </si>
-  <si>
-    <t>Verify rejection of nonexistent email</t>
-  </si>
-  <si>
-    <t>1564ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-003</t>
-  </si>
-  <si>
-    <t>Verify successful login with valid credentials redirects to Dashboard</t>
-  </si>
-  <si>
-    <t>2296ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-004</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Total Customers count</t>
-  </si>
-  <si>
-    <t>299ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-005</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Active Sales count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-006</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Pending Installments count</t>
-  </si>
-  <si>
-    <t>34ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-007</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Today's Due count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-008</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Outstanding Balance amount</t>
-  </si>
-  <si>
-    <t>33ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-009</t>
-  </si>
-  <si>
-    <t>Navigate to customers page and verify header</t>
-  </si>
-  <si>
-    <t>276ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-010</t>
-  </si>
-  <si>
-    <t>Verify add new customer input inputs are present</t>
-  </si>
-  <si>
-    <t>83ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-011</t>
-  </si>
-  <si>
-    <t>Verify customer creation and entry addition to table</t>
-  </si>
-  <si>
-    <t>2658ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-012</t>
-  </si>
-  <si>
-    <t>Verify presence of seeded customer</t>
-  </si>
-  <si>
-    <t>36ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-013</t>
-  </si>
-  <si>
-    <t>Navigate to specific customer profile page</t>
-  </si>
-  <si>
-    <t>1209ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-014</t>
-  </si>
-  <si>
-    <t>Verify phone number exists on profile detail bar</t>
-  </si>
-  <si>
-    <t>50ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-015</t>
-  </si>
-  <si>
-    <t>Verify Total Amount financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>55ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-016</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount financial card is 0 INR</t>
-  </si>
-  <si>
-    <t>56ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-017</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance financial card is 1000 INR</t>
+    <t>TC-WEB-VAL-003</t>
+  </si>
+  <si>
+    <t>Verify browser client blocks submissions for invalid email inputs</t>
+  </si>
+  <si>
+    <t>257ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-004</t>
+  </si>
+  <si>
+    <t>Verify character bounds for data buffers limit to 255 characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-005</t>
+  </si>
+  <si>
+    <t>Verify customer creation form prevents empty submit</t>
+  </si>
+  <si>
+    <t>3671ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-006</t>
+  </si>
+  <si>
+    <t>Verify phone input uses tel semantic element type</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-007</t>
+  </si>
+  <si>
+    <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
+  </si>
+  <si>
+    <t>1154ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-008</t>
+  </si>
+  <si>
+    <t>Verify unit price input restricts negative numbers</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-009</t>
+  </si>
+  <si>
+    <t>Verify script tag input text does not trigger native alerts</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>2270ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-010</t>
+  </si>
+  <si>
+    <t>Verify database adapter parameters parameterized input query parsing</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-011</t>
+  </si>
+  <si>
+    <t>Verify error prevents overpayment collections</t>
+  </si>
+  <si>
+    <t>2883ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-012</t>
+  </si>
+  <si>
+    <t>Verify collection input restricts 0 value submissions</t>
+  </si>
+  <si>
+    <t>1453ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-013</t>
+  </si>
+  <si>
+    <t>Verify Firestore writes match schema constraints</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-014</t>
+  </si>
+  <si>
+    <t>Verify wildcard URLs redirect to main route base</t>
+  </si>
+  <si>
+    <t>2165ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-015</t>
+  </si>
+  <si>
+    <t>Verify HTML password hidden mask attribute config</t>
+  </si>
+  <si>
+    <t>1008ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-001</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Verify load paint FCP under 2.5s threshold</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>497ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-002</t>
+  </si>
+  <si>
+    <t>Verify full render transition load time under limit</t>
+  </si>
+  <si>
+    <t>1660ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-003</t>
+  </si>
+  <si>
+    <t>Verify DNS host domain matches Vercel production edge</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-004</t>
+  </si>
+  <si>
+    <t>Verify favicon.ico endpoint yields clean HTTP status</t>
+  </si>
+  <si>
+    <t>439ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-005</t>
+  </si>
+  <si>
+    <t>Verify production connection protocol HTTPS encryption is active</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-006</t>
+  </si>
+  <si>
+    <t>Verify head links contain manifest registration details</t>
+  </si>
+  <si>
+    <t>167ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-007</t>
+  </si>
+  <si>
+    <t>Verify console logs have no severe exceptions during login page session</t>
+  </si>
+  <si>
+    <t>6ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-008</t>
+  </si>
+  <si>
+    <t>Verify standard responsive layouts align horizontally</t>
   </si>
   <si>
     <t>65ms</t>
   </si>
   <si>
-    <t>TC-WEB-FUNC-018</t>
-  </si>
-  <si>
-    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-019</t>
-  </si>
-  <si>
-    <t>Verify redirect to record payment page</t>
-  </si>
-  <si>
-    <t>939ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-020</t>
-  </si>
-  <si>
-    <t>Verify remaining balance display match before payment</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-021</t>
-  </si>
-  <si>
-    <t>Record payment E2E execution and redirection validation</t>
-  </si>
-  <si>
-    <t>3680ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-022</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
-  </si>
-  <si>
-    <t>1797ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-023</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount updates to 200 INR in customer card</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-024</t>
-  </si>
-  <si>
-    <t>Verify recorded payment entry list matches mode UPI</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-025</t>
-  </si>
-  <si>
-    <t>Verify sales management index loads properly</t>
-  </si>
-  <si>
-    <t>975ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-026</t>
-  </si>
-  <si>
-    <t>Verify sales search filter works properly</t>
-  </si>
-  <si>
-    <t>861ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-027</t>
-  </si>
-  <si>
-    <t>Navigate to Create New Sale form</t>
-  </si>
-  <si>
-    <t>1477ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-028</t>
-  </si>
-  <si>
-    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
-  </si>
-  <si>
-    <t>700ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-029</t>
-  </si>
-  <si>
-    <t>Create sale and verify redirect back to sales table</t>
-  </si>
-  <si>
-    <t>547ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-030</t>
-  </si>
-  <si>
-    <t>Verify Payments page path and title</t>
-  </si>
-  <si>
-    <t>1150ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-031</t>
-  </si>
-  <si>
-    <t>Verify E2E transaction exists in master list</t>
-  </si>
-  <si>
-    <t>117ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-032</t>
-  </si>
-  <si>
-    <t>Verify Ledger Book page loads</t>
-  </si>
-  <si>
-    <t>748ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-033</t>
-  </si>
-  <si>
-    <t>Verify ledger records contain client name</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-034</t>
-  </si>
-  <si>
-    <t>Verify Installments page title</t>
-  </si>
-  <si>
-    <t>1003ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-035</t>
-  </si>
-  <si>
-    <t>Verify customer details exist on installment board</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-036</t>
-  </si>
-  <si>
-    <t>Verify direct Dashboard URL redirect</t>
-  </si>
-  <si>
-    <t>570ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-037</t>
-  </si>
-  <si>
-    <t>Verify customer data updates dynamically on UI edit</t>
-  </si>
-  <si>
-    <t>5246ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-038</t>
-  </si>
-  <si>
-    <t>Verify logout route terminates session and redirects to sign in</t>
-  </si>
-  <si>
-    <t>1955ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-039</t>
-  </si>
-  <si>
-    <t>Verify unauthorized dashboard access redirects to login</t>
-  </si>
-  <si>
-    <t>3166ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-040</t>
-  </si>
-  <si>
-    <t>Verify unauthorized customer details access redirects to login</t>
-  </si>
-  <si>
-    <t>2256ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-001</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting positive amount</t>
-  </si>
-  <si>
-    <t>73ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-002</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting zero amount</t>
-  </si>
-  <si>
-    <t>0ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-003</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting negative amount</t>
-  </si>
-  <si>
-    <t>1ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-004</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting large millions scale amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-005</t>
-  </si>
-  <si>
-    <t>Test formatCurrency decimal rounding functionality</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-006</t>
-  </si>
-  <si>
-    <t>Test formatDate string matching date details</t>
-  </si>
-  <si>
-    <t>20ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-007</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for null values</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-008</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for 0 value</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-009</t>
-  </si>
-  <si>
-    <t>Test formatDateTime details formatting</t>
-  </si>
-  <si>
-    <t>17ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-010</t>
-  </si>
-  <si>
-    <t>Test formatDateTime null timestamp handling</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-011</t>
-  </si>
-  <si>
-    <t>Verify email validation for valid string</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-012</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing TLD</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-013</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing alias prefix</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-014</t>
-  </si>
-  <si>
-    <t>Verify phone validation for standard 10 digit number</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-015</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks short length</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-016</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks alphabetic characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-017</t>
-  </si>
-  <si>
-    <t>Verify interest formula multiplication logic</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-018</t>
-  </si>
-  <si>
-    <t>Verify installment partitioning amount division</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-019</t>
-  </si>
-  <si>
-    <t>Verify remaining balance arithmetic subtraction</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-020</t>
-  </si>
-  <si>
-    <t>Verify mock environment manifest validator passes</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-001</t>
-  </si>
-  <si>
-    <t>Validation</t>
-  </si>
-  <si>
-    <t>Verify email required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>623ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-002</t>
-  </si>
-  <si>
-    <t>Verify password required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>31ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-003</t>
-  </si>
-  <si>
-    <t>Verify browser client blocks submissions for invalid email inputs</t>
-  </si>
-  <si>
-    <t>239ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-004</t>
-  </si>
-  <si>
-    <t>Verify character bounds for data buffers limit to 255 characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-005</t>
-  </si>
-  <si>
-    <t>Verify customer creation form prevents empty submit</t>
-  </si>
-  <si>
-    <t>7364ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-006</t>
-  </si>
-  <si>
-    <t>Verify phone input uses tel semantic element type</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-007</t>
-  </si>
-  <si>
-    <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
-  </si>
-  <si>
-    <t>2585ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-008</t>
-  </si>
-  <si>
-    <t>Verify unit price input restricts negative numbers</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-009</t>
-  </si>
-  <si>
-    <t>Verify script tag input text does not trigger native alerts</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>3341ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-010</t>
-  </si>
-  <si>
-    <t>Verify database adapter parameters parameterized input query parsing</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-011</t>
-  </si>
-  <si>
-    <t>Verify error prevents overpayment collections</t>
-  </si>
-  <si>
-    <t>2484ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-012</t>
-  </si>
-  <si>
-    <t>Verify collection input restricts 0 value submissions</t>
-  </si>
-  <si>
-    <t>1416ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-013</t>
-  </si>
-  <si>
-    <t>Verify Firestore writes match schema constraints</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-014</t>
-  </si>
-  <si>
-    <t>Verify wildcard URLs redirect to main route base</t>
-  </si>
-  <si>
-    <t>4026ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-015</t>
-  </si>
-  <si>
-    <t>Verify HTML password hidden mask attribute config</t>
-  </si>
-  <si>
-    <t>1271ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-001</t>
-  </si>
-  <si>
-    <t>Deployment</t>
-  </si>
-  <si>
-    <t>Verify load paint FCP under 2.5s threshold</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>819ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-002</t>
-  </si>
-  <si>
-    <t>Verify full render transition load time under limit</t>
-  </si>
-  <si>
-    <t>1705ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-003</t>
-  </si>
-  <si>
-    <t>Verify DNS host domain matches Vercel production edge</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-004</t>
-  </si>
-  <si>
-    <t>Verify favicon.ico endpoint yields clean HTTP status</t>
-  </si>
-  <si>
-    <t>250ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-005</t>
-  </si>
-  <si>
-    <t>Verify production connection protocol HTTPS encryption is active</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-006</t>
-  </si>
-  <si>
-    <t>Verify head links contain manifest registration details</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-007</t>
-  </si>
-  <si>
-    <t>Verify console logs have no severe exceptions during login page session</t>
-  </si>
-  <si>
-    <t>11ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-008</t>
-  </si>
-  <si>
-    <t>Verify standard responsive layouts align horizontally</t>
-  </si>
-  <si>
     <t>TC-WEB-DEP-009</t>
   </si>
   <si>
     <t>Verify DOM count index scales cleanly</t>
   </si>
   <si>
-    <t>14ms</t>
+    <t>16ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-010</t>
@@ -1570,7 +1564,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1578,13 +1572,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1593,7 +1587,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1601,13 +1595,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1616,7 +1610,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1624,13 +1618,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1639,7 +1633,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -1647,13 +1641,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1662,7 +1656,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1670,13 +1664,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1685,7 +1679,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -1693,13 +1687,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1708,7 +1702,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1716,13 +1710,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1731,7 +1725,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1739,13 +1733,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1754,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1762,13 +1756,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1777,7 +1771,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -1785,13 +1779,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1800,7 +1794,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -1808,13 +1802,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1823,7 +1817,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -1831,13 +1825,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1846,7 +1840,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -1854,13 +1848,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1869,7 +1863,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -1877,13 +1871,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1892,7 +1886,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -1900,13 +1894,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1915,7 +1909,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -1923,13 +1917,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1938,7 +1932,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1946,13 +1940,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1961,7 +1955,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1969,13 +1963,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1984,7 +1978,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2035,22 +2029,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2058,22 +2052,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -2081,22 +2075,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -2104,22 +2098,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -2127,22 +2121,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -2150,22 +2144,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -2173,22 +2167,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2196,22 +2190,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2219,22 +2213,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -2242,22 +2236,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -2265,22 +2259,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -2288,22 +2282,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -2311,22 +2305,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -2334,22 +2328,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -2357,22 +2351,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -2380,22 +2374,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2403,22 +2397,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2426,22 +2420,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2449,22 +2443,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2472,22 +2466,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2495,22 +2489,22 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2518,22 +2512,22 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2541,22 +2535,22 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2564,22 +2558,22 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2587,22 +2581,22 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2610,22 +2604,22 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2633,22 +2627,22 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -2656,22 +2650,22 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -2679,22 +2673,22 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2702,22 +2696,22 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2725,22 +2719,22 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2748,22 +2742,22 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2771,22 +2765,22 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2794,22 +2788,22 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2817,22 +2811,22 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2840,22 +2834,22 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2863,22 +2857,22 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2886,22 +2880,22 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2909,22 +2903,22 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -2932,22 +2926,22 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -2998,22 +2992,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3021,22 +3015,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3044,22 +3038,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3067,22 +3061,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3090,22 +3084,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3113,22 +3107,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3136,22 +3130,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3159,22 +3153,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3182,22 +3176,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3205,22 +3199,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3228,22 +3222,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3251,22 +3245,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3274,22 +3268,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3297,22 +3291,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3320,22 +3314,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3343,22 +3337,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -3366,22 +3360,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -3389,22 +3383,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -3412,22 +3406,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -3435,22 +3429,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -3501,22 +3495,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3524,22 +3518,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3547,22 +3541,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3570,22 +3564,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3593,22 +3587,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3616,22 +3610,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3639,22 +3633,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3662,22 +3656,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3685,22 +3679,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3708,22 +3702,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3731,22 +3725,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3754,22 +3748,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3777,22 +3771,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3800,22 +3794,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3823,22 +3817,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3889,22 +3883,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3912,22 +3906,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3935,22 +3929,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3958,22 +3952,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3981,22 +3975,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -4004,22 +3998,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>110</v>
+        <v>299</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -4027,22 +4021,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -4050,22 +4044,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>28</v>
+        <v>305</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -4073,22 +4067,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -4096,22 +4090,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>

--- a/tests/reports/Test_Analysis_Report.xlsx
+++ b/tests/reports/Test_Analysis_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="310">
   <si>
     <t>Test ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>1974ms</t>
+    <t>10049ms</t>
   </si>
   <si>
     <t>Assertion passed successfully</t>
@@ -68,7 +68,7 @@
     <t>Verify brand name PayBuddy header exists</t>
   </si>
   <si>
-    <t>284ms</t>
+    <t>89ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-003</t>
@@ -77,7 +77,7 @@
     <t>Verify form email input label</t>
   </si>
   <si>
-    <t>69ms</t>
+    <t>56ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-004</t>
@@ -86,718 +86,715 @@
     <t>Verify form password input label</t>
   </si>
   <si>
+    <t>42ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-005</t>
+  </si>
+  <si>
+    <t>Verify Sign In button is present</t>
+  </si>
+  <si>
+    <t>41ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-006</t>
+  </si>
+  <si>
+    <t>Verify secure access footer notice is present</t>
+  </si>
+  <si>
+    <t>32ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-007</t>
+  </si>
+  <si>
+    <t>Verify branding subtitle text exists</t>
+  </si>
+  <si>
     <t>35ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-005</t>
-  </si>
-  <si>
-    <t>Verify Sign In button is present</t>
-  </si>
-  <si>
-    <t>41ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-006</t>
-  </si>
-  <si>
-    <t>Verify secure access footer notice is present</t>
+    <t>TC-WEB-UI-008</t>
+  </si>
+  <si>
+    <t>Verify email input field placeholder</t>
+  </si>
+  <si>
+    <t>34ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-009</t>
+  </si>
+  <si>
+    <t>Verify password input field placeholder</t>
+  </si>
+  <si>
+    <t>31ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-010</t>
+  </si>
+  <si>
+    <t>Verify font family CSS on headers</t>
+  </si>
+  <si>
+    <t>39ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-011</t>
+  </si>
+  <si>
+    <t>Verify primary brand color on buttons</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-012</t>
+  </si>
+  <si>
+    <t>Verify centered block layout</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-013</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at mobile width 360px</t>
+  </si>
+  <si>
+    <t>922ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-014</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at tablet width 768px</t>
+  </si>
+  <si>
+    <t>921ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-015</t>
+  </si>
+  <si>
+    <t>Restore browser window maximization state</t>
+  </si>
+  <si>
+    <t>49ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-016</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for email input</t>
+  </si>
+  <si>
+    <t>61ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-017</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for password input</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-018</t>
+  </si>
+  <si>
+    <t>Verify card wrapper styles (border-radius)</t>
+  </si>
+  <si>
+    <t>47ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-019</t>
+  </si>
+  <si>
+    <t>Verify background styling matches design spec</t>
+  </si>
+  <si>
+    <t>43ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-020</t>
+  </si>
+  <si>
+    <t>Verify focus state click handler does not crash</t>
+  </si>
+  <si>
+    <t>196ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-021</t>
+  </si>
+  <si>
+    <t>Verify top-level container viewport classes</t>
+  </si>
+  <si>
+    <t>51ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-022</t>
+  </si>
+  <si>
+    <t>Verify branding and form division layout margins</t>
   </si>
   <si>
     <t>36ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-007</t>
-  </si>
-  <si>
-    <t>Verify branding subtitle text exists</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-008</t>
-  </si>
-  <si>
-    <t>Verify email input field placeholder</t>
-  </si>
-  <si>
-    <t>39ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-009</t>
-  </si>
-  <si>
-    <t>Verify password input field placeholder</t>
-  </si>
-  <si>
-    <t>34ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-010</t>
-  </si>
-  <si>
-    <t>Verify font family CSS on headers</t>
-  </si>
-  <si>
-    <t>40ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-011</t>
-  </si>
-  <si>
-    <t>Verify primary brand color on buttons</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-012</t>
-  </si>
-  <si>
-    <t>Verify centered block layout</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-013</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at mobile width 360px</t>
-  </si>
-  <si>
-    <t>927ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-014</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at tablet width 768px</t>
-  </si>
-  <si>
-    <t>941ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-015</t>
-  </si>
-  <si>
-    <t>Restore browser window maximization state</t>
-  </si>
-  <si>
-    <t>45ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-016</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for email input</t>
+    <t>TC-WEB-UI-023</t>
+  </si>
+  <si>
+    <t>Verify clear textual contrast for reader accessibility</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-024</t>
+  </si>
+  <si>
+    <t>Verify page scales properly without layout clipping</t>
+  </si>
+  <si>
+    <t>54ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-025</t>
+  </si>
+  <si>
+    <t>Verify smooth interactive transitions on button inputs</t>
+  </si>
+  <si>
+    <t>30ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-001</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Verify invalid login rejection message</t>
+  </si>
+  <si>
+    <t>3917ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-002</t>
+  </si>
+  <si>
+    <t>Verify rejection of nonexistent email</t>
+  </si>
+  <si>
+    <t>3709ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-003</t>
+  </si>
+  <si>
+    <t>Verify successful login with valid credentials redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>3328ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-004</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Total Customers count</t>
+  </si>
+  <si>
+    <t>944ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-005</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Active Sales count</t>
+  </si>
+  <si>
+    <t>76ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-006</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Pending Installments count</t>
+  </si>
+  <si>
+    <t>48ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-007</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Today's Due count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-008</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Outstanding Balance amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-009</t>
+  </si>
+  <si>
+    <t>Navigate to customers page and verify header</t>
+  </si>
+  <si>
+    <t>205ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-010</t>
+  </si>
+  <si>
+    <t>Verify add new customer input inputs are present</t>
+  </si>
+  <si>
+    <t>50ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-011</t>
+  </si>
+  <si>
+    <t>Verify customer creation and entry addition to table</t>
+  </si>
+  <si>
+    <t>2597ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-012</t>
+  </si>
+  <si>
+    <t>Verify presence of seeded customer</t>
+  </si>
+  <si>
+    <t>55ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-013</t>
+  </si>
+  <si>
+    <t>Navigate to specific customer profile page</t>
+  </si>
+  <si>
+    <t>1731ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-014</t>
+  </si>
+  <si>
+    <t>Verify phone number exists on profile detail bar</t>
+  </si>
+  <si>
+    <t>38ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-015</t>
+  </si>
+  <si>
+    <t>Verify Total Amount financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-016</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount financial card is 0 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-017</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-018</t>
+  </si>
+  <si>
+    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-019</t>
+  </si>
+  <si>
+    <t>Verify redirect to record payment page</t>
+  </si>
+  <si>
+    <t>1312ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-020</t>
+  </si>
+  <si>
+    <t>Verify remaining balance display match before payment</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-021</t>
+  </si>
+  <si>
+    <t>Record payment E2E execution and redirection validation</t>
+  </si>
+  <si>
+    <t>3421ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-022</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
+  </si>
+  <si>
+    <t>1998ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-023</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount updates to 200 INR in customer card</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-024</t>
+  </si>
+  <si>
+    <t>Verify recorded payment entry list matches mode UPI</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-025</t>
+  </si>
+  <si>
+    <t>Verify sales management index loads properly</t>
+  </si>
+  <si>
+    <t>1151ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-026</t>
+  </si>
+  <si>
+    <t>Verify sales search filter works properly</t>
+  </si>
+  <si>
+    <t>784ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-027</t>
+  </si>
+  <si>
+    <t>Navigate to Create New Sale form</t>
+  </si>
+  <si>
+    <t>1201ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-028</t>
+  </si>
+  <si>
+    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
+  </si>
+  <si>
+    <t>675ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-029</t>
+  </si>
+  <si>
+    <t>Create sale and verify redirect back to sales table</t>
+  </si>
+  <si>
+    <t>447ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-030</t>
+  </si>
+  <si>
+    <t>Verify Payments page path and title</t>
+  </si>
+  <si>
+    <t>2540ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-031</t>
+  </si>
+  <si>
+    <t>Verify E2E transaction exists in master list</t>
+  </si>
+  <si>
+    <t>52ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-032</t>
+  </si>
+  <si>
+    <t>Verify Ledger Book page loads</t>
+  </si>
+  <si>
+    <t>1580ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-033</t>
+  </si>
+  <si>
+    <t>Verify ledger records contain client name</t>
+  </si>
+  <si>
+    <t>73ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-034</t>
+  </si>
+  <si>
+    <t>Verify Installments page title</t>
+  </si>
+  <si>
+    <t>1056ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-035</t>
+  </si>
+  <si>
+    <t>Verify customer details exist on installment board</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-036</t>
+  </si>
+  <si>
+    <t>Verify direct Dashboard URL redirect</t>
+  </si>
+  <si>
+    <t>775ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-037</t>
+  </si>
+  <si>
+    <t>Verify customer data updates dynamically on UI edit</t>
+  </si>
+  <si>
+    <t>4643ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-038</t>
+  </si>
+  <si>
+    <t>Verify logout route terminates session and redirects to sign in</t>
+  </si>
+  <si>
+    <t>1664ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-039</t>
+  </si>
+  <si>
+    <t>Verify unauthorized dashboard access redirects to login</t>
+  </si>
+  <si>
+    <t>2406ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-040</t>
+  </si>
+  <si>
+    <t>Verify unauthorized customer details access redirects to login</t>
+  </si>
+  <si>
+    <t>2228ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-001</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting positive amount</t>
+  </si>
+  <si>
+    <t>78ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-002</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting zero amount</t>
+  </si>
+  <si>
+    <t>1ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-003</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting negative amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-004</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting large millions scale amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-005</t>
+  </si>
+  <si>
+    <t>Test formatCurrency decimal rounding functionality</t>
+  </si>
+  <si>
+    <t>0ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-006</t>
+  </si>
+  <si>
+    <t>Test formatDate string matching date details</t>
+  </si>
+  <si>
+    <t>17ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-007</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for null values</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-008</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for 0 value</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-009</t>
+  </si>
+  <si>
+    <t>Test formatDateTime details formatting</t>
+  </si>
+  <si>
+    <t>2ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-010</t>
+  </si>
+  <si>
+    <t>Test formatDateTime null timestamp handling</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-011</t>
+  </si>
+  <si>
+    <t>Verify email validation for valid string</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-012</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing TLD</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-013</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing alias prefix</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-014</t>
+  </si>
+  <si>
+    <t>Verify phone validation for standard 10 digit number</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-015</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks short length</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-016</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks alphabetic characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-017</t>
+  </si>
+  <si>
+    <t>Verify interest formula multiplication logic</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-018</t>
+  </si>
+  <si>
+    <t>Verify installment partitioning amount division</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-019</t>
+  </si>
+  <si>
+    <t>Verify remaining balance arithmetic subtraction</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-020</t>
+  </si>
+  <si>
+    <t>Verify mock environment manifest validator passes</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-001</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Verify email required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>330ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-002</t>
+  </si>
+  <si>
+    <t>Verify password required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-003</t>
+  </si>
+  <si>
+    <t>Verify browser client blocks submissions for invalid email inputs</t>
+  </si>
+  <si>
+    <t>245ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-004</t>
+  </si>
+  <si>
+    <t>Verify character bounds for data buffers limit to 255 characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-005</t>
+  </si>
+  <si>
+    <t>Verify customer creation form prevents empty submit</t>
+  </si>
+  <si>
+    <t>4492ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-006</t>
+  </si>
+  <si>
+    <t>Verify phone input uses tel semantic element type</t>
   </si>
   <si>
     <t>27ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-017</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for password input</t>
-  </si>
-  <si>
-    <t>55ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-018</t>
-  </si>
-  <si>
-    <t>Verify card wrapper styles (border-radius)</t>
-  </si>
-  <si>
-    <t>49ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-019</t>
-  </si>
-  <si>
-    <t>Verify background styling matches design spec</t>
-  </si>
-  <si>
-    <t>44ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-020</t>
-  </si>
-  <si>
-    <t>Verify focus state click handler does not crash</t>
-  </si>
-  <si>
-    <t>147ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-021</t>
-  </si>
-  <si>
-    <t>Verify top-level container viewport classes</t>
-  </si>
-  <si>
-    <t>57ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-022</t>
-  </si>
-  <si>
-    <t>Verify branding and form division layout margins</t>
-  </si>
-  <si>
-    <t>38ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-023</t>
-  </si>
-  <si>
-    <t>Verify clear textual contrast for reader accessibility</t>
-  </si>
-  <si>
-    <t>53ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-024</t>
-  </si>
-  <si>
-    <t>Verify page scales properly without layout clipping</t>
-  </si>
-  <si>
-    <t>33ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-025</t>
-  </si>
-  <si>
-    <t>Verify smooth interactive transitions on button inputs</t>
-  </si>
-  <si>
-    <t>31ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-001</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>Verify invalid login rejection message</t>
-  </si>
-  <si>
-    <t>1427ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-002</t>
-  </si>
-  <si>
-    <t>Verify rejection of nonexistent email</t>
-  </si>
-  <si>
-    <t>1220ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-003</t>
-  </si>
-  <si>
-    <t>Verify successful login with valid credentials redirects to Dashboard</t>
-  </si>
-  <si>
-    <t>2197ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-004</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Total Customers count</t>
-  </si>
-  <si>
-    <t>304ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-005</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Active Sales count</t>
-  </si>
-  <si>
-    <t>46ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-006</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Pending Installments count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-007</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Today's Due count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-008</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Outstanding Balance amount</t>
-  </si>
-  <si>
-    <t>58ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-009</t>
-  </si>
-  <si>
-    <t>Navigate to customers page and verify header</t>
-  </si>
-  <si>
-    <t>232ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-010</t>
-  </si>
-  <si>
-    <t>Verify add new customer input inputs are present</t>
-  </si>
-  <si>
-    <t>80ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-011</t>
-  </si>
-  <si>
-    <t>Verify customer creation and entry addition to table</t>
-  </si>
-  <si>
-    <t>2614ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-012</t>
-  </si>
-  <si>
-    <t>Verify presence of seeded customer</t>
-  </si>
-  <si>
-    <t>52ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-013</t>
-  </si>
-  <si>
-    <t>Navigate to specific customer profile page</t>
-  </si>
-  <si>
-    <t>1424ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-014</t>
-  </si>
-  <si>
-    <t>Verify phone number exists on profile detail bar</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-015</t>
-  </si>
-  <si>
-    <t>Verify Total Amount financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-016</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount financial card is 0 INR</t>
-  </si>
-  <si>
-    <t>51ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-017</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-018</t>
-  </si>
-  <si>
-    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-019</t>
-  </si>
-  <si>
-    <t>Verify redirect to record payment page</t>
-  </si>
-  <si>
-    <t>922ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-020</t>
-  </si>
-  <si>
-    <t>Verify remaining balance display match before payment</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-021</t>
-  </si>
-  <si>
-    <t>Record payment E2E execution and redirection validation</t>
-  </si>
-  <si>
-    <t>3425ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-022</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
-  </si>
-  <si>
-    <t>1363ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-023</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount updates to 200 INR in customer card</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-024</t>
-  </si>
-  <si>
-    <t>Verify recorded payment entry list matches mode UPI</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-025</t>
-  </si>
-  <si>
-    <t>Verify sales management index loads properly</t>
-  </si>
-  <si>
-    <t>754ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-026</t>
-  </si>
-  <si>
-    <t>Verify sales search filter works properly</t>
-  </si>
-  <si>
-    <t>774ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-027</t>
-  </si>
-  <si>
-    <t>Navigate to Create New Sale form</t>
-  </si>
-  <si>
-    <t>791ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-028</t>
-  </si>
-  <si>
-    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
-  </si>
-  <si>
-    <t>701ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-029</t>
-  </si>
-  <si>
-    <t>Create sale and verify redirect back to sales table</t>
-  </si>
-  <si>
-    <t>463ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-030</t>
-  </si>
-  <si>
-    <t>Verify Payments page path and title</t>
-  </si>
-  <si>
-    <t>848ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-031</t>
-  </si>
-  <si>
-    <t>Verify E2E transaction exists in master list</t>
-  </si>
-  <si>
-    <t>82ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-032</t>
-  </si>
-  <si>
-    <t>Verify Ledger Book page loads</t>
-  </si>
-  <si>
-    <t>900ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-033</t>
-  </si>
-  <si>
-    <t>Verify ledger records contain client name</t>
-  </si>
-  <si>
-    <t>61ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-034</t>
-  </si>
-  <si>
-    <t>Verify Installments page title</t>
-  </si>
-  <si>
-    <t>672ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-035</t>
-  </si>
-  <si>
-    <t>Verify customer details exist on installment board</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-036</t>
-  </si>
-  <si>
-    <t>Verify direct Dashboard URL redirect</t>
-  </si>
-  <si>
-    <t>259ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-037</t>
-  </si>
-  <si>
-    <t>Verify customer data updates dynamically on UI edit</t>
-  </si>
-  <si>
-    <t>4735ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-038</t>
-  </si>
-  <si>
-    <t>Verify logout route terminates session and redirects to sign in</t>
-  </si>
-  <si>
-    <t>917ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-039</t>
-  </si>
-  <si>
-    <t>Verify unauthorized dashboard access redirects to login</t>
-  </si>
-  <si>
-    <t>2154ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-040</t>
-  </si>
-  <si>
-    <t>Verify unauthorized customer details access redirects to login</t>
-  </si>
-  <si>
-    <t>2557ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-001</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting positive amount</t>
-  </si>
-  <si>
-    <t>84ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-002</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting zero amount</t>
-  </si>
-  <si>
-    <t>1ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-003</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting negative amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-004</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting large millions scale amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-005</t>
-  </si>
-  <si>
-    <t>Test formatCurrency decimal rounding functionality</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-006</t>
-  </si>
-  <si>
-    <t>Test formatDate string matching date details</t>
-  </si>
-  <si>
-    <t>15ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-007</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for null values</t>
-  </si>
-  <si>
-    <t>0ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-008</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for 0 value</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-009</t>
-  </si>
-  <si>
-    <t>Test formatDateTime details formatting</t>
-  </si>
-  <si>
-    <t>2ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-010</t>
-  </si>
-  <si>
-    <t>Test formatDateTime null timestamp handling</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-011</t>
-  </si>
-  <si>
-    <t>Verify email validation for valid string</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-012</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing TLD</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-013</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing alias prefix</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-014</t>
-  </si>
-  <si>
-    <t>Verify phone validation for standard 10 digit number</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-015</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks short length</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-016</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks alphabetic characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-017</t>
-  </si>
-  <si>
-    <t>Verify interest formula multiplication logic</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-018</t>
-  </si>
-  <si>
-    <t>Verify installment partitioning amount division</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-019</t>
-  </si>
-  <si>
-    <t>Verify remaining balance arithmetic subtraction</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-020</t>
-  </si>
-  <si>
-    <t>Verify mock environment manifest validator passes</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-001</t>
-  </si>
-  <si>
-    <t>Validation</t>
-  </si>
-  <si>
-    <t>Verify email required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>411ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-002</t>
-  </si>
-  <si>
-    <t>Verify password required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>37ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-003</t>
-  </si>
-  <si>
-    <t>Verify browser client blocks submissions for invalid email inputs</t>
-  </si>
-  <si>
-    <t>257ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-004</t>
-  </si>
-  <si>
-    <t>Verify character bounds for data buffers limit to 255 characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-005</t>
-  </si>
-  <si>
-    <t>Verify customer creation form prevents empty submit</t>
-  </si>
-  <si>
-    <t>3671ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-006</t>
-  </si>
-  <si>
-    <t>Verify phone input uses tel semantic element type</t>
-  </si>
-  <si>
     <t>TC-WEB-VAL-007</t>
   </si>
   <si>
     <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
   </si>
   <si>
-    <t>1154ms</t>
+    <t>1009ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-008</t>
@@ -806,6 +803,9 @@
     <t>Verify unit price input restricts negative numbers</t>
   </si>
   <si>
+    <t>24ms</t>
+  </si>
+  <si>
     <t>TC-WEB-VAL-009</t>
   </si>
   <si>
@@ -815,7 +815,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2270ms</t>
+    <t>2423ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-010</t>
@@ -830,7 +830,7 @@
     <t>Verify error prevents overpayment collections</t>
   </si>
   <si>
-    <t>2883ms</t>
+    <t>3061ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-012</t>
@@ -839,7 +839,7 @@
     <t>Verify collection input restricts 0 value submissions</t>
   </si>
   <si>
-    <t>1453ms</t>
+    <t>1384ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-013</t>
@@ -854,7 +854,7 @@
     <t>Verify wildcard URLs redirect to main route base</t>
   </si>
   <si>
-    <t>2165ms</t>
+    <t>4117ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-015</t>
@@ -863,7 +863,7 @@
     <t>Verify HTML password hidden mask attribute config</t>
   </si>
   <si>
-    <t>1008ms</t>
+    <t>2036ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-001</t>
@@ -878,7 +878,7 @@
     <t>Performance</t>
   </si>
   <si>
-    <t>497ms</t>
+    <t>527ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-002</t>
@@ -887,7 +887,7 @@
     <t>Verify full render transition load time under limit</t>
   </si>
   <si>
-    <t>1660ms</t>
+    <t>2200ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-003</t>
@@ -902,7 +902,7 @@
     <t>Verify favicon.ico endpoint yields clean HTTP status</t>
   </si>
   <si>
-    <t>439ms</t>
+    <t>358ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-005</t>
@@ -917,7 +917,7 @@
     <t>Verify head links contain manifest registration details</t>
   </si>
   <si>
-    <t>167ms</t>
+    <t>798ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-007</t>
@@ -942,9 +942,6 @@
   </si>
   <si>
     <t>Verify DOM count index scales cleanly</t>
-  </si>
-  <si>
-    <t>16ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-010</t>
@@ -1564,7 +1561,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1572,13 +1569,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1587,7 +1584,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1595,13 +1592,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1610,7 +1607,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1618,13 +1615,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1633,7 +1630,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -1641,13 +1638,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1656,7 +1653,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1664,13 +1661,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1679,7 +1676,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -1687,13 +1684,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1702,7 +1699,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1710,13 +1707,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1725,7 +1722,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1733,13 +1730,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1748,7 +1745,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1756,13 +1753,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1771,7 +1768,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -1779,13 +1776,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1794,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -1932,7 +1929,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1940,13 +1937,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1955,7 +1952,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1963,13 +1960,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1978,7 +1975,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2029,22 +2026,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2052,22 +2049,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -2075,22 +2072,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -2098,22 +2095,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -2121,22 +2118,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -2144,22 +2141,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -2170,19 +2167,19 @@
         <v>101</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2193,19 +2190,19 @@
         <v>103</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2213,22 +2210,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -2236,22 +2233,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -2259,22 +2256,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -2282,22 +2279,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -2305,22 +2302,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -2328,22 +2325,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -2354,19 +2351,19 @@
         <v>123</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -2377,19 +2374,19 @@
         <v>125</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2397,22 +2394,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2420,22 +2417,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2443,22 +2440,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2466,22 +2463,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2489,22 +2486,22 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2512,22 +2509,22 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2535,22 +2532,22 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2558,22 +2555,22 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2581,22 +2578,22 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2604,22 +2601,22 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2627,22 +2624,22 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -2650,22 +2647,22 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -2673,22 +2670,22 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2696,22 +2693,22 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2719,22 +2716,22 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2742,22 +2739,22 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2765,22 +2762,22 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2788,22 +2785,22 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2811,22 +2808,22 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2834,22 +2831,22 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2857,22 +2854,22 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2880,22 +2877,22 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2903,22 +2900,22 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -2926,22 +2923,22 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -2992,22 +2989,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3015,22 +3012,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3038,22 +3035,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3061,22 +3058,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3084,22 +3081,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3110,13 +3107,13 @@
         <v>207</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>208</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
@@ -3133,19 +3130,19 @@
         <v>210</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>211</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3153,22 +3150,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3176,22 +3173,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3199,22 +3196,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3222,22 +3219,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3245,22 +3242,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3268,22 +3265,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3291,22 +3288,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3314,22 +3311,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3337,22 +3334,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -3360,22 +3357,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -3383,22 +3380,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -3406,22 +3403,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -3429,22 +3426,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -3495,22 +3492,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3518,22 +3515,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3541,22 +3538,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3564,22 +3561,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3587,22 +3584,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3610,22 +3607,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3633,22 +3630,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3656,22 +3653,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3682,7 +3679,7 @@
         <v>262</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>263</v>
@@ -3705,7 +3702,7 @@
         <v>266</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>267</v>
@@ -3717,7 +3714,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3728,13 +3725,13 @@
         <v>268</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>269</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
@@ -3751,13 +3748,13 @@
         <v>271</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>272</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
@@ -3774,19 +3771,19 @@
         <v>274</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>275</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3797,13 +3794,13 @@
         <v>276</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>277</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
@@ -3820,7 +3817,7 @@
         <v>279</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>280</v>
@@ -3944,7 +3941,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3990,7 +3987,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -4082,7 +4079,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -4090,13 +4087,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>283</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>283</v>
@@ -4105,7 +4102,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>

--- a/tests/reports/Test_Analysis_Report.xlsx
+++ b/tests/reports/Test_Analysis_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="304">
   <si>
     <t>Test ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>10049ms</t>
+    <t>2898ms</t>
   </si>
   <si>
     <t>Assertion passed successfully</t>
@@ -68,7 +68,7 @@
     <t>Verify brand name PayBuddy header exists</t>
   </si>
   <si>
-    <t>89ms</t>
+    <t>241ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-003</t>
@@ -77,693 +77,672 @@
     <t>Verify form email input label</t>
   </si>
   <si>
+    <t>15ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-004</t>
+  </si>
+  <si>
+    <t>Verify form password input label</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-005</t>
+  </si>
+  <si>
+    <t>Verify Sign In button is present</t>
+  </si>
+  <si>
+    <t>12ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-006</t>
+  </si>
+  <si>
+    <t>Verify secure access footer notice is present</t>
+  </si>
+  <si>
+    <t>13ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-007</t>
+  </si>
+  <si>
+    <t>Verify branding subtitle text exists</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-008</t>
+  </si>
+  <si>
+    <t>Verify email input field placeholder</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-009</t>
+  </si>
+  <si>
+    <t>Verify password input field placeholder</t>
+  </si>
+  <si>
+    <t>14ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-010</t>
+  </si>
+  <si>
+    <t>Verify font family CSS on headers</t>
+  </si>
+  <si>
+    <t>17ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-011</t>
+  </si>
+  <si>
+    <t>Verify primary brand color on buttons</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-012</t>
+  </si>
+  <si>
+    <t>Verify centered block layout</t>
+  </si>
+  <si>
+    <t>16ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-013</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at mobile width 360px</t>
+  </si>
+  <si>
+    <t>908ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-014</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at tablet width 768px</t>
+  </si>
+  <si>
+    <t>904ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-015</t>
+  </si>
+  <si>
+    <t>Restore browser window maximization state</t>
+  </si>
+  <si>
+    <t>34ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-016</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for email input</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-017</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for password input</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-018</t>
+  </si>
+  <si>
+    <t>Verify card wrapper styles (border-radius)</t>
+  </si>
+  <si>
+    <t>20ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-019</t>
+  </si>
+  <si>
+    <t>Verify background styling matches design spec</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-020</t>
+  </si>
+  <si>
+    <t>Verify focus state click handler does not crash</t>
+  </si>
+  <si>
+    <t>90ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-021</t>
+  </si>
+  <si>
+    <t>Verify top-level container viewport classes</t>
+  </si>
+  <si>
+    <t>24ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-022</t>
+  </si>
+  <si>
+    <t>Verify branding and form division layout margins</t>
+  </si>
+  <si>
+    <t>42ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-023</t>
+  </si>
+  <si>
+    <t>Verify clear textual contrast for reader accessibility</t>
+  </si>
+  <si>
+    <t>25ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-024</t>
+  </si>
+  <si>
+    <t>Verify page scales properly without layout clipping</t>
+  </si>
+  <si>
+    <t>23ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-025</t>
+  </si>
+  <si>
+    <t>Verify smooth interactive transitions on button inputs</t>
+  </si>
+  <si>
+    <t>19ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-001</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Verify invalid login rejection message</t>
+  </si>
+  <si>
+    <t>2371ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-002</t>
+  </si>
+  <si>
+    <t>Verify rejection of nonexistent email</t>
+  </si>
+  <si>
+    <t>784ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-003</t>
+  </si>
+  <si>
+    <t>Verify successful login with valid credentials redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>1610ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-004</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Total Customers count</t>
+  </si>
+  <si>
+    <t>247ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-005</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Active Sales count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-006</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Pending Installments count</t>
+  </si>
+  <si>
+    <t>18ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-007</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Today's Due count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-008</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Outstanding Balance amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-009</t>
+  </si>
+  <si>
+    <t>Navigate to customers page and verify header</t>
+  </si>
+  <si>
+    <t>129ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-010</t>
+  </si>
+  <si>
+    <t>Verify add new customer input inputs are present</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-011</t>
+  </si>
+  <si>
+    <t>Verify customer creation and entry addition to table</t>
+  </si>
+  <si>
+    <t>2346ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-012</t>
+  </si>
+  <si>
+    <t>Verify presence of seeded customer</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-013</t>
+  </si>
+  <si>
+    <t>Navigate to specific customer profile page</t>
+  </si>
+  <si>
+    <t>989ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-014</t>
+  </si>
+  <si>
+    <t>Verify phone number exists on profile detail bar</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-015</t>
+  </si>
+  <si>
+    <t>Verify Total Amount financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-016</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount financial card is 0 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-017</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-018</t>
+  </si>
+  <si>
+    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-019</t>
+  </si>
+  <si>
+    <t>Verify redirect to record payment page</t>
+  </si>
+  <si>
+    <t>790ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-020</t>
+  </si>
+  <si>
+    <t>Verify remaining balance display match before payment</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-021</t>
+  </si>
+  <si>
+    <t>Record payment E2E execution and redirection validation</t>
+  </si>
+  <si>
+    <t>2821ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-022</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
+  </si>
+  <si>
+    <t>1140ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-023</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount updates to 200 INR in customer card</t>
+  </si>
+  <si>
+    <t>11ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-024</t>
+  </si>
+  <si>
+    <t>Verify recorded payment entry list matches mode UPI</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-025</t>
+  </si>
+  <si>
+    <t>Verify sales management index loads properly</t>
+  </si>
+  <si>
+    <t>552ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-026</t>
+  </si>
+  <si>
+    <t>Verify sales search filter works properly</t>
+  </si>
+  <si>
+    <t>626ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-027</t>
+  </si>
+  <si>
+    <t>Navigate to Create New Sale form</t>
+  </si>
+  <si>
+    <t>840ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-028</t>
+  </si>
+  <si>
+    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
+  </si>
+  <si>
+    <t>231ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-029</t>
+  </si>
+  <si>
+    <t>Create sale and verify redirect back to sales table</t>
+  </si>
+  <si>
+    <t>204ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-030</t>
+  </si>
+  <si>
+    <t>Verify Payments page path and title</t>
+  </si>
+  <si>
+    <t>574ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-031</t>
+  </si>
+  <si>
+    <t>Verify E2E transaction exists in master list</t>
+  </si>
+  <si>
+    <t>33ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-032</t>
+  </si>
+  <si>
+    <t>Verify Ledger Book page loads</t>
+  </si>
+  <si>
+    <t>827ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-033</t>
+  </si>
+  <si>
+    <t>Verify ledger records contain client name</t>
+  </si>
+  <si>
+    <t>31ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-034</t>
+  </si>
+  <si>
+    <t>Verify Installments page title</t>
+  </si>
+  <si>
+    <t>562ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-035</t>
+  </si>
+  <si>
+    <t>Verify customer details exist on installment board</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-036</t>
+  </si>
+  <si>
+    <t>Verify direct Dashboard URL redirect</t>
+  </si>
+  <si>
+    <t>99ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-037</t>
+  </si>
+  <si>
+    <t>Verify customer data updates dynamically on UI edit</t>
+  </si>
+  <si>
+    <t>4236ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-038</t>
+  </si>
+  <si>
+    <t>Verify logout route terminates session and redirects to sign in</t>
+  </si>
+  <si>
+    <t>608ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-039</t>
+  </si>
+  <si>
+    <t>Verify unauthorized dashboard access redirects to login</t>
+  </si>
+  <si>
+    <t>2158ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-040</t>
+  </si>
+  <si>
+    <t>Verify unauthorized customer details access redirects to login</t>
+  </si>
+  <si>
+    <t>2808ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-001</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting positive amount</t>
+  </si>
+  <si>
     <t>56ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-004</t>
-  </si>
-  <si>
-    <t>Verify form password input label</t>
-  </si>
-  <si>
-    <t>42ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-005</t>
-  </si>
-  <si>
-    <t>Verify Sign In button is present</t>
-  </si>
-  <si>
-    <t>41ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-006</t>
-  </si>
-  <si>
-    <t>Verify secure access footer notice is present</t>
-  </si>
-  <si>
-    <t>32ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-007</t>
-  </si>
-  <si>
-    <t>Verify branding subtitle text exists</t>
-  </si>
-  <si>
-    <t>35ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-008</t>
-  </si>
-  <si>
-    <t>Verify email input field placeholder</t>
-  </si>
-  <si>
-    <t>34ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-009</t>
-  </si>
-  <si>
-    <t>Verify password input field placeholder</t>
-  </si>
-  <si>
-    <t>31ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-010</t>
-  </si>
-  <si>
-    <t>Verify font family CSS on headers</t>
-  </si>
-  <si>
-    <t>39ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-011</t>
-  </si>
-  <si>
-    <t>Verify primary brand color on buttons</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-012</t>
-  </si>
-  <si>
-    <t>Verify centered block layout</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-013</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at mobile width 360px</t>
-  </si>
-  <si>
-    <t>922ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-014</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at tablet width 768px</t>
-  </si>
-  <si>
-    <t>921ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-015</t>
-  </si>
-  <si>
-    <t>Restore browser window maximization state</t>
-  </si>
-  <si>
-    <t>49ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-016</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for email input</t>
-  </si>
-  <si>
-    <t>61ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-017</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for password input</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-018</t>
-  </si>
-  <si>
-    <t>Verify card wrapper styles (border-radius)</t>
-  </si>
-  <si>
-    <t>47ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-019</t>
-  </si>
-  <si>
-    <t>Verify background styling matches design spec</t>
-  </si>
-  <si>
-    <t>43ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-020</t>
-  </si>
-  <si>
-    <t>Verify focus state click handler does not crash</t>
-  </si>
-  <si>
-    <t>196ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-021</t>
-  </si>
-  <si>
-    <t>Verify top-level container viewport classes</t>
-  </si>
-  <si>
-    <t>51ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-022</t>
-  </si>
-  <si>
-    <t>Verify branding and form division layout margins</t>
-  </si>
-  <si>
-    <t>36ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-023</t>
-  </si>
-  <si>
-    <t>Verify clear textual contrast for reader accessibility</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-024</t>
-  </si>
-  <si>
-    <t>Verify page scales properly without layout clipping</t>
-  </si>
-  <si>
-    <t>54ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-025</t>
-  </si>
-  <si>
-    <t>Verify smooth interactive transitions on button inputs</t>
-  </si>
-  <si>
-    <t>30ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-001</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>Verify invalid login rejection message</t>
-  </si>
-  <si>
-    <t>3917ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-002</t>
-  </si>
-  <si>
-    <t>Verify rejection of nonexistent email</t>
-  </si>
-  <si>
-    <t>3709ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-003</t>
-  </si>
-  <si>
-    <t>Verify successful login with valid credentials redirects to Dashboard</t>
-  </si>
-  <si>
-    <t>3328ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-004</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Total Customers count</t>
-  </si>
-  <si>
-    <t>944ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-005</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Active Sales count</t>
+    <t>TC-WEB-UNIT-002</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting zero amount</t>
+  </si>
+  <si>
+    <t>0ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-003</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting negative amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-004</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting large millions scale amount</t>
+  </si>
+  <si>
+    <t>1ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-005</t>
+  </si>
+  <si>
+    <t>Test formatCurrency decimal rounding functionality</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-006</t>
+  </si>
+  <si>
+    <t>Test formatDate string matching date details</t>
+  </si>
+  <si>
+    <t>9ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-007</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for null values</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-008</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for 0 value</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-009</t>
+  </si>
+  <si>
+    <t>Test formatDateTime details formatting</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-010</t>
+  </si>
+  <si>
+    <t>Test formatDateTime null timestamp handling</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-011</t>
+  </si>
+  <si>
+    <t>Verify email validation for valid string</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-012</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing TLD</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-013</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing alias prefix</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-014</t>
+  </si>
+  <si>
+    <t>Verify phone validation for standard 10 digit number</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-015</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks short length</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-016</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks alphabetic characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-017</t>
+  </si>
+  <si>
+    <t>Verify interest formula multiplication logic</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-018</t>
+  </si>
+  <si>
+    <t>Verify installment partitioning amount division</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-019</t>
+  </si>
+  <si>
+    <t>Verify remaining balance arithmetic subtraction</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-020</t>
+  </si>
+  <si>
+    <t>Verify mock environment manifest validator passes</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-001</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Verify email required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>330ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-002</t>
+  </si>
+  <si>
+    <t>Verify password required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-003</t>
+  </si>
+  <si>
+    <t>Verify browser client blocks submissions for invalid email inputs</t>
   </si>
   <si>
     <t>76ms</t>
   </si>
   <si>
-    <t>TC-WEB-FUNC-006</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Pending Installments count</t>
-  </si>
-  <si>
-    <t>48ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-007</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Today's Due count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-008</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Outstanding Balance amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-009</t>
-  </si>
-  <si>
-    <t>Navigate to customers page and verify header</t>
-  </si>
-  <si>
-    <t>205ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-010</t>
-  </si>
-  <si>
-    <t>Verify add new customer input inputs are present</t>
-  </si>
-  <si>
-    <t>50ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-011</t>
-  </si>
-  <si>
-    <t>Verify customer creation and entry addition to table</t>
-  </si>
-  <si>
-    <t>2597ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-012</t>
-  </si>
-  <si>
-    <t>Verify presence of seeded customer</t>
-  </si>
-  <si>
-    <t>55ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-013</t>
-  </si>
-  <si>
-    <t>Navigate to specific customer profile page</t>
-  </si>
-  <si>
-    <t>1731ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-014</t>
-  </si>
-  <si>
-    <t>Verify phone number exists on profile detail bar</t>
-  </si>
-  <si>
-    <t>38ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-015</t>
-  </si>
-  <si>
-    <t>Verify Total Amount financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-016</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount financial card is 0 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-017</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-018</t>
-  </si>
-  <si>
-    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-019</t>
-  </si>
-  <si>
-    <t>Verify redirect to record payment page</t>
-  </si>
-  <si>
-    <t>1312ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-020</t>
-  </si>
-  <si>
-    <t>Verify remaining balance display match before payment</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-021</t>
-  </si>
-  <si>
-    <t>Record payment E2E execution and redirection validation</t>
-  </si>
-  <si>
-    <t>3421ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-022</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
-  </si>
-  <si>
-    <t>1998ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-023</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount updates to 200 INR in customer card</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-024</t>
-  </si>
-  <si>
-    <t>Verify recorded payment entry list matches mode UPI</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-025</t>
-  </si>
-  <si>
-    <t>Verify sales management index loads properly</t>
-  </si>
-  <si>
-    <t>1151ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-026</t>
-  </si>
-  <si>
-    <t>Verify sales search filter works properly</t>
-  </si>
-  <si>
-    <t>784ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-027</t>
-  </si>
-  <si>
-    <t>Navigate to Create New Sale form</t>
-  </si>
-  <si>
-    <t>1201ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-028</t>
-  </si>
-  <si>
-    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
-  </si>
-  <si>
-    <t>675ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-029</t>
-  </si>
-  <si>
-    <t>Create sale and verify redirect back to sales table</t>
-  </si>
-  <si>
-    <t>447ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-030</t>
-  </si>
-  <si>
-    <t>Verify Payments page path and title</t>
-  </si>
-  <si>
-    <t>2540ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-031</t>
-  </si>
-  <si>
-    <t>Verify E2E transaction exists in master list</t>
-  </si>
-  <si>
-    <t>52ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-032</t>
-  </si>
-  <si>
-    <t>Verify Ledger Book page loads</t>
-  </si>
-  <si>
-    <t>1580ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-033</t>
-  </si>
-  <si>
-    <t>Verify ledger records contain client name</t>
-  </si>
-  <si>
-    <t>73ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-034</t>
-  </si>
-  <si>
-    <t>Verify Installments page title</t>
-  </si>
-  <si>
-    <t>1056ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-035</t>
-  </si>
-  <si>
-    <t>Verify customer details exist on installment board</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-036</t>
-  </si>
-  <si>
-    <t>Verify direct Dashboard URL redirect</t>
-  </si>
-  <si>
-    <t>775ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-037</t>
-  </si>
-  <si>
-    <t>Verify customer data updates dynamically on UI edit</t>
-  </si>
-  <si>
-    <t>4643ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-038</t>
-  </si>
-  <si>
-    <t>Verify logout route terminates session and redirects to sign in</t>
-  </si>
-  <si>
-    <t>1664ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-039</t>
-  </si>
-  <si>
-    <t>Verify unauthorized dashboard access redirects to login</t>
-  </si>
-  <si>
-    <t>2406ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-040</t>
-  </si>
-  <si>
-    <t>Verify unauthorized customer details access redirects to login</t>
-  </si>
-  <si>
-    <t>2228ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-001</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting positive amount</t>
-  </si>
-  <si>
-    <t>78ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-002</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting zero amount</t>
-  </si>
-  <si>
-    <t>1ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-003</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting negative amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-004</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting large millions scale amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-005</t>
-  </si>
-  <si>
-    <t>Test formatCurrency decimal rounding functionality</t>
-  </si>
-  <si>
-    <t>0ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-006</t>
-  </si>
-  <si>
-    <t>Test formatDate string matching date details</t>
-  </si>
-  <si>
-    <t>17ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-007</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for null values</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-008</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for 0 value</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-009</t>
-  </si>
-  <si>
-    <t>Test formatDateTime details formatting</t>
-  </si>
-  <si>
-    <t>2ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-010</t>
-  </si>
-  <si>
-    <t>Test formatDateTime null timestamp handling</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-011</t>
-  </si>
-  <si>
-    <t>Verify email validation for valid string</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-012</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing TLD</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-013</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing alias prefix</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-014</t>
-  </si>
-  <si>
-    <t>Verify phone validation for standard 10 digit number</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-015</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks short length</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-016</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks alphabetic characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-017</t>
-  </si>
-  <si>
-    <t>Verify interest formula multiplication logic</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-018</t>
-  </si>
-  <si>
-    <t>Verify installment partitioning amount division</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-019</t>
-  </si>
-  <si>
-    <t>Verify remaining balance arithmetic subtraction</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-020</t>
-  </si>
-  <si>
-    <t>Verify mock environment manifest validator passes</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-001</t>
-  </si>
-  <si>
-    <t>Validation</t>
-  </si>
-  <si>
-    <t>Verify email required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>330ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-002</t>
-  </si>
-  <si>
-    <t>Verify password required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-003</t>
-  </si>
-  <si>
-    <t>Verify browser client blocks submissions for invalid email inputs</t>
-  </si>
-  <si>
-    <t>245ms</t>
-  </si>
-  <si>
     <t>TC-WEB-VAL-004</t>
   </si>
   <si>
@@ -776,7 +755,7 @@
     <t>Verify customer creation form prevents empty submit</t>
   </si>
   <si>
-    <t>4492ms</t>
+    <t>3054ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-006</t>
@@ -785,7 +764,7 @@
     <t>Verify phone input uses tel semantic element type</t>
   </si>
   <si>
-    <t>27ms</t>
+    <t>22ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-007</t>
@@ -794,7 +773,7 @@
     <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
   </si>
   <si>
-    <t>1009ms</t>
+    <t>600ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-008</t>
@@ -803,7 +782,7 @@
     <t>Verify unit price input restricts negative numbers</t>
   </si>
   <si>
-    <t>24ms</t>
+    <t>10ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-009</t>
@@ -815,7 +794,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2423ms</t>
+    <t>1904ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-010</t>
@@ -830,7 +809,7 @@
     <t>Verify error prevents overpayment collections</t>
   </si>
   <si>
-    <t>3061ms</t>
+    <t>1909ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-012</t>
@@ -839,7 +818,7 @@
     <t>Verify collection input restricts 0 value submissions</t>
   </si>
   <si>
-    <t>1384ms</t>
+    <t>1123ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-013</t>
@@ -854,7 +833,7 @@
     <t>Verify wildcard URLs redirect to main route base</t>
   </si>
   <si>
-    <t>4117ms</t>
+    <t>2113ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-015</t>
@@ -863,7 +842,7 @@
     <t>Verify HTML password hidden mask attribute config</t>
   </si>
   <si>
-    <t>2036ms</t>
+    <t>602ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-001</t>
@@ -878,7 +857,7 @@
     <t>Performance</t>
   </si>
   <si>
-    <t>527ms</t>
+    <t>107ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-002</t>
@@ -887,7 +866,7 @@
     <t>Verify full render transition load time under limit</t>
   </si>
   <si>
-    <t>2200ms</t>
+    <t>1149ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-003</t>
@@ -902,7 +881,7 @@
     <t>Verify favicon.ico endpoint yields clean HTTP status</t>
   </si>
   <si>
-    <t>358ms</t>
+    <t>94ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-005</t>
@@ -917,7 +896,7 @@
     <t>Verify head links contain manifest registration details</t>
   </si>
   <si>
-    <t>798ms</t>
+    <t>130ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-007</t>
@@ -926,7 +905,7 @@
     <t>Verify console logs have no severe exceptions during login page session</t>
   </si>
   <si>
-    <t>6ms</t>
+    <t>4ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-008</t>
@@ -935,13 +914,16 @@
     <t>Verify standard responsive layouts align horizontally</t>
   </si>
   <si>
-    <t>65ms</t>
+    <t>45ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-009</t>
   </si>
   <si>
     <t>Verify DOM count index scales cleanly</t>
+  </si>
+  <si>
+    <t>5ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-010</t>
@@ -1492,7 +1474,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -1500,13 +1482,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -1515,7 +1497,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -1523,13 +1505,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
@@ -1538,7 +1520,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -1546,13 +1528,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1561,7 +1543,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1569,13 +1551,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1584,7 +1566,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1592,13 +1574,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1607,7 +1589,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1615,13 +1597,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1630,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -1638,13 +1620,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1653,7 +1635,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1661,13 +1643,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1676,7 +1658,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -1684,13 +1666,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1699,7 +1681,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1707,13 +1689,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1722,7 +1704,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1730,13 +1712,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1745,7 +1727,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1753,13 +1735,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1768,7 +1750,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -1776,13 +1758,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1791,7 +1773,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -1799,13 +1781,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1814,7 +1796,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -1822,13 +1804,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1837,7 +1819,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -1845,13 +1827,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1860,7 +1842,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -1868,13 +1850,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1883,7 +1865,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -1891,13 +1873,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1906,7 +1888,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -1914,13 +1896,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1929,7 +1911,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1937,13 +1919,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1952,7 +1934,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1960,13 +1942,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1975,7 +1957,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2026,22 +2008,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2049,22 +2031,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -2072,22 +2054,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -2095,22 +2077,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -2118,22 +2100,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -2141,22 +2123,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -2164,22 +2146,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2187,22 +2169,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2210,22 +2192,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -2233,22 +2215,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -2256,22 +2238,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -2279,22 +2261,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -2302,22 +2284,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -2325,22 +2307,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -2348,22 +2330,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -2371,22 +2353,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2394,22 +2376,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2417,22 +2399,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2440,22 +2422,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2463,22 +2445,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2486,22 +2468,22 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2509,22 +2491,22 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2532,22 +2514,22 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2555,22 +2537,22 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2578,22 +2560,22 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2601,22 +2583,22 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2624,22 +2606,22 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -2647,22 +2629,22 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -2670,22 +2652,22 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2693,22 +2675,22 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2716,22 +2698,22 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2739,22 +2721,22 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2762,22 +2744,22 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2785,22 +2767,22 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2808,22 +2790,22 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2831,22 +2813,22 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2854,22 +2836,22 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2877,22 +2859,22 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2900,22 +2882,22 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -2923,22 +2905,22 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -2989,22 +2971,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3012,22 +2994,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3035,22 +3017,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3058,22 +3040,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3081,22 +3063,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3104,22 +3086,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3127,22 +3109,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3150,22 +3132,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3173,22 +3155,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3196,22 +3178,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3219,22 +3201,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3242,22 +3224,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3265,22 +3247,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3288,22 +3270,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3311,22 +3293,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3334,22 +3316,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -3357,22 +3339,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -3380,22 +3362,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -3403,22 +3385,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -3426,22 +3408,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -3492,22 +3474,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3515,22 +3497,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3538,22 +3520,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3561,22 +3543,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3584,22 +3566,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3607,22 +3589,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3630,22 +3612,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3653,22 +3635,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3676,22 +3658,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3699,22 +3681,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3722,22 +3704,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3745,22 +3727,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3768,22 +3750,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3791,22 +3773,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3814,22 +3796,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3880,22 +3862,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3903,22 +3885,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3926,22 +3908,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3949,22 +3931,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3972,22 +3954,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3995,22 +3977,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -4018,22 +4000,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -4041,22 +4023,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -4064,22 +4046,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -4087,22 +4069,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>

--- a/tests/reports/Test_Analysis_Report.xlsx
+++ b/tests/reports/Test_Analysis_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="306">
   <si>
     <t>Test ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>2898ms</t>
+    <t>304ms</t>
   </si>
   <si>
     <t>Assertion passed successfully</t>
@@ -68,7 +68,7 @@
     <t>Verify brand name PayBuddy header exists</t>
   </si>
   <si>
-    <t>241ms</t>
+    <t>247ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-003</t>
@@ -92,124 +92,127 @@
     <t>Verify Sign In button is present</t>
   </si>
   <si>
+    <t>14ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-006</t>
+  </si>
+  <si>
+    <t>Verify secure access footer notice is present</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-007</t>
+  </si>
+  <si>
+    <t>Verify branding subtitle text exists</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-008</t>
+  </si>
+  <si>
+    <t>Verify email input field placeholder</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-009</t>
+  </si>
+  <si>
+    <t>Verify password input field placeholder</t>
+  </si>
+  <si>
+    <t>13ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-010</t>
+  </si>
+  <si>
+    <t>Verify font family CSS on headers</t>
+  </si>
+  <si>
+    <t>16ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-011</t>
+  </si>
+  <si>
+    <t>Verify primary brand color on buttons</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-012</t>
+  </si>
+  <si>
+    <t>Verify centered block layout</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-013</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at mobile width 360px</t>
+  </si>
+  <si>
+    <t>890ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-014</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at tablet width 768px</t>
+  </si>
+  <si>
+    <t>884ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-015</t>
+  </si>
+  <si>
+    <t>Restore browser window maximization state</t>
+  </si>
+  <si>
+    <t>23ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-016</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for email input</t>
+  </si>
+  <si>
+    <t>25ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-017</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for password input</t>
+  </si>
+  <si>
     <t>12ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-006</t>
-  </si>
-  <si>
-    <t>Verify secure access footer notice is present</t>
-  </si>
-  <si>
-    <t>13ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-007</t>
-  </si>
-  <si>
-    <t>Verify branding subtitle text exists</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-008</t>
-  </si>
-  <si>
-    <t>Verify email input field placeholder</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-009</t>
-  </si>
-  <si>
-    <t>Verify password input field placeholder</t>
-  </si>
-  <si>
-    <t>14ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-010</t>
-  </si>
-  <si>
-    <t>Verify font family CSS on headers</t>
+    <t>TC-WEB-UI-018</t>
+  </si>
+  <si>
+    <t>Verify card wrapper styles (border-radius)</t>
+  </si>
+  <si>
+    <t>37ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-019</t>
+  </si>
+  <si>
+    <t>Verify background styling matches design spec</t>
   </si>
   <si>
     <t>17ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-011</t>
-  </si>
-  <si>
-    <t>Verify primary brand color on buttons</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-012</t>
-  </si>
-  <si>
-    <t>Verify centered block layout</t>
-  </si>
-  <si>
-    <t>16ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-013</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at mobile width 360px</t>
-  </si>
-  <si>
-    <t>908ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-014</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at tablet width 768px</t>
-  </si>
-  <si>
-    <t>904ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-015</t>
-  </si>
-  <si>
-    <t>Restore browser window maximization state</t>
-  </si>
-  <si>
-    <t>34ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-016</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for email input</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-017</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for password input</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-018</t>
-  </si>
-  <si>
-    <t>Verify card wrapper styles (border-radius)</t>
-  </si>
-  <si>
-    <t>20ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-019</t>
-  </si>
-  <si>
-    <t>Verify background styling matches design spec</t>
-  </si>
-  <si>
     <t>TC-WEB-UI-020</t>
   </si>
   <si>
     <t>Verify focus state click handler does not crash</t>
   </si>
   <si>
-    <t>90ms</t>
+    <t>131ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-021</t>
@@ -218,25 +221,25 @@
     <t>Verify top-level container viewport classes</t>
   </si>
   <si>
+    <t>29ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-022</t>
+  </si>
+  <si>
+    <t>Verify branding and form division layout margins</t>
+  </si>
+  <si>
     <t>24ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-022</t>
-  </si>
-  <si>
-    <t>Verify branding and form division layout margins</t>
-  </si>
-  <si>
-    <t>42ms</t>
-  </si>
-  <si>
     <t>TC-WEB-UI-023</t>
   </si>
   <si>
     <t>Verify clear textual contrast for reader accessibility</t>
   </si>
   <si>
-    <t>25ms</t>
+    <t>35ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-024</t>
@@ -245,175 +248,190 @@
     <t>Verify page scales properly without layout clipping</t>
   </si>
   <si>
-    <t>23ms</t>
-  </si>
-  <si>
     <t>TC-WEB-UI-025</t>
   </si>
   <si>
     <t>Verify smooth interactive transitions on button inputs</t>
   </si>
   <si>
+    <t>TC-WEB-FUNC-001</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Verify invalid login rejection message</t>
+  </si>
+  <si>
+    <t>1153ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-002</t>
+  </si>
+  <si>
+    <t>Verify rejection of nonexistent email</t>
+  </si>
+  <si>
+    <t>839ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-003</t>
+  </si>
+  <si>
+    <t>Verify successful login with valid credentials redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>1702ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-004</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Total Customers count</t>
+  </si>
+  <si>
+    <t>496ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-005</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Active Sales count</t>
+  </si>
+  <si>
+    <t>43ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-006</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Pending Installments count</t>
+  </si>
+  <si>
+    <t>45ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-007</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Today's Due count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-008</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Outstanding Balance amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-009</t>
+  </si>
+  <si>
+    <t>Navigate to customers page and verify header</t>
+  </si>
+  <si>
+    <t>163ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-010</t>
+  </si>
+  <si>
+    <t>Verify add new customer input inputs are present</t>
+  </si>
+  <si>
+    <t>33ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-011</t>
+  </si>
+  <si>
+    <t>Verify customer creation and entry addition to table</t>
+  </si>
+  <si>
+    <t>2539ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-012</t>
+  </si>
+  <si>
+    <t>Verify presence of seeded customer</t>
+  </si>
+  <si>
+    <t>21ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-013</t>
+  </si>
+  <si>
+    <t>Navigate to specific customer profile page</t>
+  </si>
+  <si>
+    <t>1131ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-014</t>
+  </si>
+  <si>
+    <t>Verify phone number exists on profile detail bar</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-015</t>
+  </si>
+  <si>
+    <t>Verify Total Amount financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-016</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount financial card is 0 INR</t>
+  </si>
+  <si>
+    <t>86ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-017</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>28ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-018</t>
+  </si>
+  <si>
+    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
+  </si>
+  <si>
+    <t>18ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-019</t>
+  </si>
+  <si>
+    <t>Verify redirect to record payment page</t>
+  </si>
+  <si>
+    <t>761ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-020</t>
+  </si>
+  <si>
+    <t>Verify remaining balance display match before payment</t>
+  </si>
+  <si>
     <t>19ms</t>
   </si>
   <si>
-    <t>TC-WEB-FUNC-001</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>Verify invalid login rejection message</t>
-  </si>
-  <si>
-    <t>2371ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-002</t>
-  </si>
-  <si>
-    <t>Verify rejection of nonexistent email</t>
-  </si>
-  <si>
-    <t>784ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-003</t>
-  </si>
-  <si>
-    <t>Verify successful login with valid credentials redirects to Dashboard</t>
-  </si>
-  <si>
-    <t>1610ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-004</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Total Customers count</t>
-  </si>
-  <si>
-    <t>247ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-005</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Active Sales count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-006</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Pending Installments count</t>
-  </si>
-  <si>
-    <t>18ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-007</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Today's Due count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-008</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Outstanding Balance amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-009</t>
-  </si>
-  <si>
-    <t>Navigate to customers page and verify header</t>
-  </si>
-  <si>
-    <t>129ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-010</t>
-  </si>
-  <si>
-    <t>Verify add new customer input inputs are present</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-011</t>
-  </si>
-  <si>
-    <t>Verify customer creation and entry addition to table</t>
-  </si>
-  <si>
-    <t>2346ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-012</t>
-  </si>
-  <si>
-    <t>Verify presence of seeded customer</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-013</t>
-  </si>
-  <si>
-    <t>Navigate to specific customer profile page</t>
-  </si>
-  <si>
-    <t>989ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-014</t>
-  </si>
-  <si>
-    <t>Verify phone number exists on profile detail bar</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-015</t>
-  </si>
-  <si>
-    <t>Verify Total Amount financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-016</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount financial card is 0 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-017</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-018</t>
-  </si>
-  <si>
-    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-019</t>
-  </si>
-  <si>
-    <t>Verify redirect to record payment page</t>
-  </si>
-  <si>
-    <t>790ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-020</t>
-  </si>
-  <si>
-    <t>Verify remaining balance display match before payment</t>
-  </si>
-  <si>
     <t>TC-WEB-FUNC-021</t>
   </si>
   <si>
     <t>Record payment E2E execution and redirection validation</t>
   </si>
   <si>
-    <t>2821ms</t>
+    <t>3226ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-022</t>
@@ -422,7 +440,7 @@
     <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
   </si>
   <si>
-    <t>1140ms</t>
+    <t>1192ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-023</t>
@@ -431,9 +449,6 @@
     <t>Verify Paid Amount updates to 200 INR in customer card</t>
   </si>
   <si>
-    <t>11ms</t>
-  </si>
-  <si>
     <t>TC-WEB-FUNC-024</t>
   </si>
   <si>
@@ -446,7 +461,7 @@
     <t>Verify sales management index loads properly</t>
   </si>
   <si>
-    <t>552ms</t>
+    <t>866ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-026</t>
@@ -455,7 +470,7 @@
     <t>Verify sales search filter works properly</t>
   </si>
   <si>
-    <t>626ms</t>
+    <t>728ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-027</t>
@@ -464,7 +479,7 @@
     <t>Navigate to Create New Sale form</t>
   </si>
   <si>
-    <t>840ms</t>
+    <t>801ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-028</t>
@@ -473,7 +488,7 @@
     <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
   </si>
   <si>
-    <t>231ms</t>
+    <t>307ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-029</t>
@@ -482,7 +497,7 @@
     <t>Create sale and verify redirect back to sales table</t>
   </si>
   <si>
-    <t>204ms</t>
+    <t>207ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-030</t>
@@ -491,7 +506,7 @@
     <t>Verify Payments page path and title</t>
   </si>
   <si>
-    <t>574ms</t>
+    <t>591ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-031</t>
@@ -500,7 +515,7 @@
     <t>Verify E2E transaction exists in master list</t>
   </si>
   <si>
-    <t>33ms</t>
+    <t>85ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-032</t>
@@ -509,7 +524,7 @@
     <t>Verify Ledger Book page loads</t>
   </si>
   <si>
-    <t>827ms</t>
+    <t>799ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-033</t>
@@ -518,7 +533,7 @@
     <t>Verify ledger records contain client name</t>
   </si>
   <si>
-    <t>31ms</t>
+    <t>121ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-034</t>
@@ -527,7 +542,7 @@
     <t>Verify Installments page title</t>
   </si>
   <si>
-    <t>562ms</t>
+    <t>568ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-035</t>
@@ -536,13 +551,16 @@
     <t>Verify customer details exist on installment board</t>
   </si>
   <si>
+    <t>53ms</t>
+  </si>
+  <si>
     <t>TC-WEB-FUNC-036</t>
   </si>
   <si>
     <t>Verify direct Dashboard URL redirect</t>
   </si>
   <si>
-    <t>99ms</t>
+    <t>106ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-037</t>
@@ -551,7 +569,7 @@
     <t>Verify customer data updates dynamically on UI edit</t>
   </si>
   <si>
-    <t>4236ms</t>
+    <t>4447ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-038</t>
@@ -560,7 +578,7 @@
     <t>Verify logout route terminates session and redirects to sign in</t>
   </si>
   <si>
-    <t>608ms</t>
+    <t>1050ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-039</t>
@@ -569,7 +587,7 @@
     <t>Verify unauthorized dashboard access redirects to login</t>
   </si>
   <si>
-    <t>2158ms</t>
+    <t>2104ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-040</t>
@@ -578,7 +596,7 @@
     <t>Verify unauthorized customer details access redirects to login</t>
   </si>
   <si>
-    <t>2808ms</t>
+    <t>2103ms</t>
   </si>
   <si>
     <t>TC-WEB-UNIT-001</t>
@@ -590,340 +608,328 @@
     <t>Test formatCurrency formatting positive amount</t>
   </si>
   <si>
+    <t>TC-WEB-UNIT-002</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting zero amount</t>
+  </si>
+  <si>
+    <t>0ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-003</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting negative amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-004</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting large millions scale amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-005</t>
+  </si>
+  <si>
+    <t>Test formatCurrency decimal rounding functionality</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-006</t>
+  </si>
+  <si>
+    <t>Test formatDate string matching date details</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-007</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for null values</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-008</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for 0 value</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-009</t>
+  </si>
+  <si>
+    <t>Test formatDateTime details formatting</t>
+  </si>
+  <si>
+    <t>1ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-010</t>
+  </si>
+  <si>
+    <t>Test formatDateTime null timestamp handling</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-011</t>
+  </si>
+  <si>
+    <t>Verify email validation for valid string</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-012</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing TLD</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-013</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing alias prefix</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-014</t>
+  </si>
+  <si>
+    <t>Verify phone validation for standard 10 digit number</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-015</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks short length</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-016</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks alphabetic characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-017</t>
+  </si>
+  <si>
+    <t>Verify interest formula multiplication logic</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-018</t>
+  </si>
+  <si>
+    <t>Verify installment partitioning amount division</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-019</t>
+  </si>
+  <si>
+    <t>Verify remaining balance arithmetic subtraction</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-020</t>
+  </si>
+  <si>
+    <t>Verify mock environment manifest validator passes</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-001</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Verify email required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>329ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-002</t>
+  </si>
+  <si>
+    <t>Verify password required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-003</t>
+  </si>
+  <si>
+    <t>Verify browser client blocks submissions for invalid email inputs</t>
+  </si>
+  <si>
+    <t>107ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-004</t>
+  </si>
+  <si>
+    <t>Verify character bounds for data buffers limit to 255 characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-005</t>
+  </si>
+  <si>
+    <t>Verify customer creation form prevents empty submit</t>
+  </si>
+  <si>
+    <t>3059ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-006</t>
+  </si>
+  <si>
+    <t>Verify phone input uses tel semantic element type</t>
+  </si>
+  <si>
+    <t>26ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-007</t>
+  </si>
+  <si>
+    <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
+  </si>
+  <si>
+    <t>563ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-008</t>
+  </si>
+  <si>
+    <t>Verify unit price input restricts negative numbers</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-009</t>
+  </si>
+  <si>
+    <t>Verify script tag input text does not trigger native alerts</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>2311ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-010</t>
+  </si>
+  <si>
+    <t>Verify database adapter parameters parameterized input query parsing</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-011</t>
+  </si>
+  <si>
+    <t>Verify error prevents overpayment collections</t>
+  </si>
+  <si>
+    <t>2120ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-012</t>
+  </si>
+  <si>
+    <t>Verify collection input restricts 0 value submissions</t>
+  </si>
+  <si>
+    <t>1143ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-013</t>
+  </si>
+  <si>
+    <t>Verify Firestore writes match schema constraints</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-014</t>
+  </si>
+  <si>
+    <t>Verify wildcard URLs redirect to main route base</t>
+  </si>
+  <si>
+    <t>2118ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-015</t>
+  </si>
+  <si>
+    <t>Verify HTML password hidden mask attribute config</t>
+  </si>
+  <si>
+    <t>668ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-001</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Verify load paint FCP under 2.5s threshold</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>124ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-002</t>
+  </si>
+  <si>
+    <t>Verify full render transition load time under limit</t>
+  </si>
+  <si>
+    <t>1185ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-003</t>
+  </si>
+  <si>
+    <t>Verify DNS host domain matches Vercel production edge</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-004</t>
+  </si>
+  <si>
+    <t>Verify favicon.ico endpoint yields clean HTTP status</t>
+  </si>
+  <si>
+    <t>103ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-005</t>
+  </si>
+  <si>
+    <t>Verify production connection protocol HTTPS encryption is active</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-006</t>
+  </si>
+  <si>
+    <t>Verify head links contain manifest registration details</t>
+  </si>
+  <si>
+    <t>147ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-007</t>
+  </si>
+  <si>
+    <t>Verify console logs have no severe exceptions during login page session</t>
+  </si>
+  <si>
+    <t>3ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-008</t>
+  </si>
+  <si>
+    <t>Verify standard responsive layouts align horizontally</t>
+  </si>
+  <si>
     <t>56ms</t>
   </si>
   <si>
-    <t>TC-WEB-UNIT-002</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting zero amount</t>
-  </si>
-  <si>
-    <t>0ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-003</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting negative amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-004</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting large millions scale amount</t>
-  </si>
-  <si>
-    <t>1ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-005</t>
-  </si>
-  <si>
-    <t>Test formatCurrency decimal rounding functionality</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-006</t>
-  </si>
-  <si>
-    <t>Test formatDate string matching date details</t>
-  </si>
-  <si>
-    <t>9ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-007</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for null values</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-008</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for 0 value</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-009</t>
-  </si>
-  <si>
-    <t>Test formatDateTime details formatting</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-010</t>
-  </si>
-  <si>
-    <t>Test formatDateTime null timestamp handling</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-011</t>
-  </si>
-  <si>
-    <t>Verify email validation for valid string</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-012</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing TLD</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-013</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing alias prefix</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-014</t>
-  </si>
-  <si>
-    <t>Verify phone validation for standard 10 digit number</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-015</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks short length</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-016</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks alphabetic characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-017</t>
-  </si>
-  <si>
-    <t>Verify interest formula multiplication logic</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-018</t>
-  </si>
-  <si>
-    <t>Verify installment partitioning amount division</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-019</t>
-  </si>
-  <si>
-    <t>Verify remaining balance arithmetic subtraction</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-020</t>
-  </si>
-  <si>
-    <t>Verify mock environment manifest validator passes</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-001</t>
-  </si>
-  <si>
-    <t>Validation</t>
-  </si>
-  <si>
-    <t>Verify email required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>330ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-002</t>
-  </si>
-  <si>
-    <t>Verify password required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-003</t>
-  </si>
-  <si>
-    <t>Verify browser client blocks submissions for invalid email inputs</t>
-  </si>
-  <si>
-    <t>76ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-004</t>
-  </si>
-  <si>
-    <t>Verify character bounds for data buffers limit to 255 characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-005</t>
-  </si>
-  <si>
-    <t>Verify customer creation form prevents empty submit</t>
-  </si>
-  <si>
-    <t>3054ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-006</t>
-  </si>
-  <si>
-    <t>Verify phone input uses tel semantic element type</t>
-  </si>
-  <si>
-    <t>22ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-007</t>
-  </si>
-  <si>
-    <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
-  </si>
-  <si>
-    <t>600ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-008</t>
-  </si>
-  <si>
-    <t>Verify unit price input restricts negative numbers</t>
-  </si>
-  <si>
-    <t>10ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-009</t>
-  </si>
-  <si>
-    <t>Verify script tag input text does not trigger native alerts</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>1904ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-010</t>
-  </si>
-  <si>
-    <t>Verify database adapter parameters parameterized input query parsing</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-011</t>
-  </si>
-  <si>
-    <t>Verify error prevents overpayment collections</t>
-  </si>
-  <si>
-    <t>1909ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-012</t>
-  </si>
-  <si>
-    <t>Verify collection input restricts 0 value submissions</t>
-  </si>
-  <si>
-    <t>1123ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-013</t>
-  </si>
-  <si>
-    <t>Verify Firestore writes match schema constraints</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-014</t>
-  </si>
-  <si>
-    <t>Verify wildcard URLs redirect to main route base</t>
-  </si>
-  <si>
-    <t>2113ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-015</t>
-  </si>
-  <si>
-    <t>Verify HTML password hidden mask attribute config</t>
-  </si>
-  <si>
-    <t>602ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-001</t>
-  </si>
-  <si>
-    <t>Deployment</t>
-  </si>
-  <si>
-    <t>Verify load paint FCP under 2.5s threshold</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>107ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-002</t>
-  </si>
-  <si>
-    <t>Verify full render transition load time under limit</t>
-  </si>
-  <si>
-    <t>1149ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-003</t>
-  </si>
-  <si>
-    <t>Verify DNS host domain matches Vercel production edge</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-004</t>
-  </si>
-  <si>
-    <t>Verify favicon.ico endpoint yields clean HTTP status</t>
-  </si>
-  <si>
-    <t>94ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-005</t>
-  </si>
-  <si>
-    <t>Verify production connection protocol HTTPS encryption is active</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-006</t>
-  </si>
-  <si>
-    <t>Verify head links contain manifest registration details</t>
-  </si>
-  <si>
-    <t>130ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-007</t>
-  </si>
-  <si>
-    <t>Verify console logs have no severe exceptions during login page session</t>
-  </si>
-  <si>
-    <t>4ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-008</t>
-  </si>
-  <si>
-    <t>Verify standard responsive layouts align horizontally</t>
-  </si>
-  <si>
-    <t>45ms</t>
-  </si>
-  <si>
     <t>TC-WEB-DEP-009</t>
   </si>
   <si>
     <t>Verify DOM count index scales cleanly</t>
-  </si>
-  <si>
-    <t>5ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-010</t>
@@ -1520,7 +1526,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -1528,13 +1534,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1543,7 +1549,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1551,13 +1557,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1566,7 +1572,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1574,13 +1580,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1589,7 +1595,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1597,13 +1603,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1612,7 +1618,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -1620,13 +1626,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1635,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1643,13 +1649,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1658,7 +1664,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -1666,13 +1672,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1681,7 +1687,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1689,13 +1695,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1704,7 +1710,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1712,13 +1718,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1727,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1735,13 +1741,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1750,7 +1756,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -1758,13 +1764,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1773,7 +1779,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -1819,7 +1825,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -1827,13 +1833,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1842,7 +1848,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -1850,13 +1856,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1865,7 +1871,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -1873,13 +1879,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1888,7 +1894,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -1896,13 +1902,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1911,7 +1917,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1919,13 +1925,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1934,7 +1940,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1957,7 +1963,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2008,22 +2014,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2031,22 +2037,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -2054,22 +2060,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -2077,22 +2083,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -2100,22 +2106,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -2126,13 +2132,13 @@
         <v>94</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
@@ -2149,19 +2155,19 @@
         <v>97</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2172,19 +2178,19 @@
         <v>99</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2195,13 +2201,13 @@
         <v>101</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
@@ -2218,19 +2224,19 @@
         <v>104</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -2238,22 +2244,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -2261,22 +2267,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -2284,22 +2290,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -2307,22 +2313,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -2330,16 +2336,16 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
@@ -2353,22 +2359,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2376,22 +2382,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2399,22 +2405,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2422,22 +2428,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2445,22 +2451,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2468,22 +2474,22 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2491,22 +2497,22 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2514,22 +2520,22 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2537,22 +2543,22 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2560,22 +2566,22 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2583,22 +2589,22 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2606,22 +2612,22 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -2629,22 +2635,22 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -2652,22 +2658,22 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2675,22 +2681,22 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2698,22 +2704,22 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2721,22 +2727,22 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2744,22 +2750,22 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2767,22 +2773,22 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2790,22 +2796,22 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2813,22 +2819,22 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2836,22 +2842,22 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2859,22 +2865,22 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2882,22 +2888,22 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -2905,22 +2911,22 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -2971,22 +2977,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>190</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2994,22 +3000,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3017,22 +3023,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3040,16 +3046,16 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
@@ -3063,22 +3069,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3086,22 +3092,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3109,16 +3115,16 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
@@ -3132,22 +3138,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3155,22 +3161,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3178,22 +3184,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3201,22 +3207,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3224,22 +3230,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3247,22 +3253,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3270,22 +3276,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3293,22 +3299,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3316,22 +3322,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -3339,22 +3345,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -3362,22 +3368,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -3385,22 +3391,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -3408,22 +3414,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -3474,22 +3480,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3497,22 +3503,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3520,22 +3526,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3543,22 +3549,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3566,22 +3572,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3589,22 +3595,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3612,22 +3618,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3635,22 +3641,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>254</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3658,22 +3664,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3681,22 +3687,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3704,22 +3710,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3727,22 +3733,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3750,22 +3756,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3773,22 +3779,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3796,22 +3802,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3862,22 +3868,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3885,22 +3891,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3908,16 +3914,16 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
@@ -3931,22 +3937,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3954,22 +3960,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3977,22 +3983,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -4000,22 +4006,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -4023,22 +4029,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -4046,22 +4052,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>301</v>
+        <v>134</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -4069,22 +4075,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>

--- a/tests/reports/Test_Analysis_Report.xlsx
+++ b/tests/reports/Test_Analysis_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="309">
   <si>
     <t>Test ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>304ms</t>
+    <t>2239ms</t>
   </si>
   <si>
     <t>Assertion passed successfully</t>
@@ -68,7 +68,7 @@
     <t>Verify brand name PayBuddy header exists</t>
   </si>
   <si>
-    <t>247ms</t>
+    <t>322ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-003</t>
@@ -77,7 +77,7 @@
     <t>Verify form email input label</t>
   </si>
   <si>
-    <t>15ms</t>
+    <t>53ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-004</t>
@@ -86,850 +86,859 @@
     <t>Verify form password input label</t>
   </si>
   <si>
+    <t>54ms</t>
+  </si>
+  <si>
     <t>TC-WEB-UI-005</t>
   </si>
   <si>
     <t>Verify Sign In button is present</t>
   </si>
   <si>
+    <t>44ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-006</t>
+  </si>
+  <si>
+    <t>Verify secure access footer notice is present</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-007</t>
+  </si>
+  <si>
+    <t>Verify branding subtitle text exists</t>
+  </si>
+  <si>
+    <t>52ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-008</t>
+  </si>
+  <si>
+    <t>Verify email input field placeholder</t>
+  </si>
+  <si>
+    <t>49ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-009</t>
+  </si>
+  <si>
+    <t>Verify password input field placeholder</t>
+  </si>
+  <si>
+    <t>51ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-010</t>
+  </si>
+  <si>
+    <t>Verify font family CSS on headers</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-011</t>
+  </si>
+  <si>
+    <t>Verify primary brand color on buttons</t>
+  </si>
+  <si>
+    <t>47ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-012</t>
+  </si>
+  <si>
+    <t>Verify centered block layout</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-013</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at mobile width 360px</t>
+  </si>
+  <si>
+    <t>945ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-014</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at tablet width 768px</t>
+  </si>
+  <si>
+    <t>942ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-015</t>
+  </si>
+  <si>
+    <t>Restore browser window maximization state</t>
+  </si>
+  <si>
+    <t>59ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-016</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for email input</t>
+  </si>
+  <si>
+    <t>67ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-017</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for password input</t>
+  </si>
+  <si>
+    <t>50ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-018</t>
+  </si>
+  <si>
+    <t>Verify card wrapper styles (border-radius)</t>
+  </si>
+  <si>
+    <t>110ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-019</t>
+  </si>
+  <si>
+    <t>Verify background styling matches design spec</t>
+  </si>
+  <si>
+    <t>45ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-020</t>
+  </si>
+  <si>
+    <t>Verify focus state click handler does not crash</t>
+  </si>
+  <si>
+    <t>156ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-021</t>
+  </si>
+  <si>
+    <t>Verify top-level container viewport classes</t>
+  </si>
+  <si>
+    <t>64ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-022</t>
+  </si>
+  <si>
+    <t>Verify branding and form division layout margins</t>
+  </si>
+  <si>
+    <t>61ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-023</t>
+  </si>
+  <si>
+    <t>Verify clear textual contrast for reader accessibility</t>
+  </si>
+  <si>
+    <t>56ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-024</t>
+  </si>
+  <si>
+    <t>Verify page scales properly without layout clipping</t>
+  </si>
+  <si>
+    <t>38ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-025</t>
+  </si>
+  <si>
+    <t>Verify smooth interactive transitions on button inputs</t>
+  </si>
+  <si>
+    <t>33ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-001</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Verify invalid login rejection message</t>
+  </si>
+  <si>
+    <t>1912ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-002</t>
+  </si>
+  <si>
+    <t>Verify rejection of nonexistent email</t>
+  </si>
+  <si>
+    <t>1667ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-003</t>
+  </si>
+  <si>
+    <t>Verify successful login with valid credentials redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>2080ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-004</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Total Customers count</t>
+  </si>
+  <si>
+    <t>281ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-005</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Active Sales count</t>
+  </si>
+  <si>
+    <t>60ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-006</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Pending Installments count</t>
+  </si>
+  <si>
+    <t>35ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-007</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Today's Due count</t>
+  </si>
+  <si>
+    <t>36ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-008</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Outstanding Balance amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-009</t>
+  </si>
+  <si>
+    <t>Navigate to customers page and verify header</t>
+  </si>
+  <si>
+    <t>393ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-010</t>
+  </si>
+  <si>
+    <t>Verify add new customer input inputs are present</t>
+  </si>
+  <si>
+    <t>57ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-011</t>
+  </si>
+  <si>
+    <t>Verify customer creation and entry addition to table</t>
+  </si>
+  <si>
+    <t>3044ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-012</t>
+  </si>
+  <si>
+    <t>Verify presence of seeded customer</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-013</t>
+  </si>
+  <si>
+    <t>Navigate to specific customer profile page</t>
+  </si>
+  <si>
+    <t>1425ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-014</t>
+  </si>
+  <si>
+    <t>Verify phone number exists on profile detail bar</t>
+  </si>
+  <si>
+    <t>39ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-015</t>
+  </si>
+  <si>
+    <t>Verify Total Amount financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-016</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount financial card is 0 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-017</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>41ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-018</t>
+  </si>
+  <si>
+    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-019</t>
+  </si>
+  <si>
+    <t>Verify redirect to record payment page</t>
+  </si>
+  <si>
+    <t>1096ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-020</t>
+  </si>
+  <si>
+    <t>Verify remaining balance display match before payment</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-021</t>
+  </si>
+  <si>
+    <t>Record payment E2E execution and redirection validation</t>
+  </si>
+  <si>
+    <t>3240ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-022</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
+  </si>
+  <si>
+    <t>1228ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-023</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount updates to 200 INR in customer card</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-024</t>
+  </si>
+  <si>
+    <t>Verify recorded payment entry list matches mode UPI</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-025</t>
+  </si>
+  <si>
+    <t>Verify sales management index loads properly</t>
+  </si>
+  <si>
+    <t>728ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-026</t>
+  </si>
+  <si>
+    <t>Verify sales search filter works properly</t>
+  </si>
+  <si>
+    <t>794ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-027</t>
+  </si>
+  <si>
+    <t>Navigate to Create New Sale form</t>
+  </si>
+  <si>
+    <t>666ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-028</t>
+  </si>
+  <si>
+    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
+  </si>
+  <si>
+    <t>655ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-029</t>
+  </si>
+  <si>
+    <t>Create sale and verify redirect back to sales table</t>
+  </si>
+  <si>
+    <t>500ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-030</t>
+  </si>
+  <si>
+    <t>Verify Payments page path and title</t>
+  </si>
+  <si>
+    <t>662ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-031</t>
+  </si>
+  <si>
+    <t>Verify E2E transaction exists in master list</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-032</t>
+  </si>
+  <si>
+    <t>Verify Ledger Book page loads</t>
+  </si>
+  <si>
+    <t>743ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-033</t>
+  </si>
+  <si>
+    <t>Verify ledger records contain client name</t>
+  </si>
+  <si>
+    <t>71ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-034</t>
+  </si>
+  <si>
+    <t>Verify Installments page title</t>
+  </si>
+  <si>
+    <t>648ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-035</t>
+  </si>
+  <si>
+    <t>Verify customer details exist on installment board</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-036</t>
+  </si>
+  <si>
+    <t>Verify direct Dashboard URL redirect</t>
+  </si>
+  <si>
+    <t>123ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-037</t>
+  </si>
+  <si>
+    <t>Verify customer data updates dynamically on UI edit</t>
+  </si>
+  <si>
+    <t>4674ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-038</t>
+  </si>
+  <si>
+    <t>Verify logout route terminates session and redirects to sign in</t>
+  </si>
+  <si>
+    <t>809ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-039</t>
+  </si>
+  <si>
+    <t>Verify unauthorized dashboard access redirects to login</t>
+  </si>
+  <si>
+    <t>2153ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-040</t>
+  </si>
+  <si>
+    <t>Verify unauthorized customer details access redirects to login</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-001</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting positive amount</t>
+  </si>
+  <si>
+    <t>79ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-002</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting zero amount</t>
+  </si>
+  <si>
+    <t>1ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-003</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting negative amount</t>
+  </si>
+  <si>
+    <t>2ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-004</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting large millions scale amount</t>
+  </si>
+  <si>
+    <t>0ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-005</t>
+  </si>
+  <si>
+    <t>Test formatCurrency decimal rounding functionality</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-006</t>
+  </si>
+  <si>
+    <t>Test formatDate string matching date details</t>
+  </si>
+  <si>
+    <t>22ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-007</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for null values</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-008</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for 0 value</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-009</t>
+  </si>
+  <si>
+    <t>Test formatDateTime details formatting</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-010</t>
+  </si>
+  <si>
+    <t>Test formatDateTime null timestamp handling</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-011</t>
+  </si>
+  <si>
+    <t>Verify email validation for valid string</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-012</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing TLD</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-013</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing alias prefix</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-014</t>
+  </si>
+  <si>
+    <t>Verify phone validation for standard 10 digit number</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-015</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks short length</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-016</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks alphabetic characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-017</t>
+  </si>
+  <si>
+    <t>Verify interest formula multiplication logic</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-018</t>
+  </si>
+  <si>
+    <t>Verify installment partitioning amount division</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-019</t>
+  </si>
+  <si>
+    <t>Verify remaining balance arithmetic subtraction</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-020</t>
+  </si>
+  <si>
+    <t>Verify mock environment manifest validator passes</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-001</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Verify email required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>191ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-002</t>
+  </si>
+  <si>
+    <t>Verify password required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-003</t>
+  </si>
+  <si>
+    <t>Verify browser client blocks submissions for invalid email inputs</t>
+  </si>
+  <si>
+    <t>253ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-004</t>
+  </si>
+  <si>
+    <t>Verify character bounds for data buffers limit to 255 characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-005</t>
+  </si>
+  <si>
+    <t>Verify customer creation form prevents empty submit</t>
+  </si>
+  <si>
+    <t>3184ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-006</t>
+  </si>
+  <si>
+    <t>Verify phone input uses tel semantic element type</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-007</t>
+  </si>
+  <si>
+    <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
+  </si>
+  <si>
+    <t>624ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-008</t>
+  </si>
+  <si>
+    <t>Verify unit price input restricts negative numbers</t>
+  </si>
+  <si>
+    <t>37ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-009</t>
+  </si>
+  <si>
+    <t>Verify script tag input text does not trigger native alerts</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>2472ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-010</t>
+  </si>
+  <si>
+    <t>Verify database adapter parameters parameterized input query parsing</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-011</t>
+  </si>
+  <si>
+    <t>Verify error prevents overpayment collections</t>
+  </si>
+  <si>
+    <t>1936ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-012</t>
+  </si>
+  <si>
+    <t>Verify collection input restricts 0 value submissions</t>
+  </si>
+  <si>
+    <t>1437ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-013</t>
+  </si>
+  <si>
+    <t>Verify Firestore writes match schema constraints</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-014</t>
+  </si>
+  <si>
+    <t>Verify wildcard URLs redirect to main route base</t>
+  </si>
+  <si>
+    <t>2128ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-015</t>
+  </si>
+  <si>
+    <t>Verify HTML password hidden mask attribute config</t>
+  </si>
+  <si>
+    <t>844ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-001</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Verify load paint FCP under 2.5s threshold</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>152ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-002</t>
+  </si>
+  <si>
+    <t>Verify full render transition load time under limit</t>
+  </si>
+  <si>
+    <t>1451ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-003</t>
+  </si>
+  <si>
+    <t>Verify DNS host domain matches Vercel production edge</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-004</t>
+  </si>
+  <si>
+    <t>Verify favicon.ico endpoint yields clean HTTP status</t>
+  </si>
+  <si>
+    <t>127ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-005</t>
+  </si>
+  <si>
+    <t>Verify production connection protocol HTTPS encryption is active</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-006</t>
+  </si>
+  <si>
+    <t>Verify head links contain manifest registration details</t>
+  </si>
+  <si>
+    <t>184ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-007</t>
+  </si>
+  <si>
+    <t>Verify console logs have no severe exceptions during login page session</t>
+  </si>
+  <si>
+    <t>8ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-008</t>
+  </si>
+  <si>
+    <t>Verify standard responsive layouts align horizontally</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-009</t>
+  </si>
+  <si>
+    <t>Verify DOM count index scales cleanly</t>
+  </si>
+  <si>
     <t>14ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-006</t>
-  </si>
-  <si>
-    <t>Verify secure access footer notice is present</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-007</t>
-  </si>
-  <si>
-    <t>Verify branding subtitle text exists</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-008</t>
-  </si>
-  <si>
-    <t>Verify email input field placeholder</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-009</t>
-  </si>
-  <si>
-    <t>Verify password input field placeholder</t>
-  </si>
-  <si>
-    <t>13ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-010</t>
-  </si>
-  <si>
-    <t>Verify font family CSS on headers</t>
-  </si>
-  <si>
-    <t>16ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-011</t>
-  </si>
-  <si>
-    <t>Verify primary brand color on buttons</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-012</t>
-  </si>
-  <si>
-    <t>Verify centered block layout</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-013</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at mobile width 360px</t>
-  </si>
-  <si>
-    <t>890ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-014</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at tablet width 768px</t>
-  </si>
-  <si>
-    <t>884ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-015</t>
-  </si>
-  <si>
-    <t>Restore browser window maximization state</t>
-  </si>
-  <si>
-    <t>23ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-016</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for email input</t>
-  </si>
-  <si>
-    <t>25ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-017</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for password input</t>
-  </si>
-  <si>
-    <t>12ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-018</t>
-  </si>
-  <si>
-    <t>Verify card wrapper styles (border-radius)</t>
-  </si>
-  <si>
-    <t>37ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-019</t>
-  </si>
-  <si>
-    <t>Verify background styling matches design spec</t>
-  </si>
-  <si>
-    <t>17ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-020</t>
-  </si>
-  <si>
-    <t>Verify focus state click handler does not crash</t>
-  </si>
-  <si>
-    <t>131ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-021</t>
-  </si>
-  <si>
-    <t>Verify top-level container viewport classes</t>
-  </si>
-  <si>
-    <t>29ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-022</t>
-  </si>
-  <si>
-    <t>Verify branding and form division layout margins</t>
-  </si>
-  <si>
-    <t>24ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-023</t>
-  </si>
-  <si>
-    <t>Verify clear textual contrast for reader accessibility</t>
-  </si>
-  <si>
-    <t>35ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-024</t>
-  </si>
-  <si>
-    <t>Verify page scales properly without layout clipping</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-025</t>
-  </si>
-  <si>
-    <t>Verify smooth interactive transitions on button inputs</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-001</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>Verify invalid login rejection message</t>
-  </si>
-  <si>
-    <t>1153ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-002</t>
-  </si>
-  <si>
-    <t>Verify rejection of nonexistent email</t>
-  </si>
-  <si>
-    <t>839ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-003</t>
-  </si>
-  <si>
-    <t>Verify successful login with valid credentials redirects to Dashboard</t>
-  </si>
-  <si>
-    <t>1702ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-004</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Total Customers count</t>
-  </si>
-  <si>
-    <t>496ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-005</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Active Sales count</t>
-  </si>
-  <si>
-    <t>43ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-006</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Pending Installments count</t>
-  </si>
-  <si>
-    <t>45ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-007</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Today's Due count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-008</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Outstanding Balance amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-009</t>
-  </si>
-  <si>
-    <t>Navigate to customers page and verify header</t>
-  </si>
-  <si>
-    <t>163ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-010</t>
-  </si>
-  <si>
-    <t>Verify add new customer input inputs are present</t>
-  </si>
-  <si>
-    <t>33ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-011</t>
-  </si>
-  <si>
-    <t>Verify customer creation and entry addition to table</t>
-  </si>
-  <si>
-    <t>2539ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-012</t>
-  </si>
-  <si>
-    <t>Verify presence of seeded customer</t>
-  </si>
-  <si>
-    <t>21ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-013</t>
-  </si>
-  <si>
-    <t>Navigate to specific customer profile page</t>
-  </si>
-  <si>
-    <t>1131ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-014</t>
-  </si>
-  <si>
-    <t>Verify phone number exists on profile detail bar</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-015</t>
-  </si>
-  <si>
-    <t>Verify Total Amount financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-016</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount financial card is 0 INR</t>
-  </si>
-  <si>
-    <t>86ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-017</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>28ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-018</t>
-  </si>
-  <si>
-    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
-  </si>
-  <si>
-    <t>18ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-019</t>
-  </si>
-  <si>
-    <t>Verify redirect to record payment page</t>
-  </si>
-  <si>
-    <t>761ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-020</t>
-  </si>
-  <si>
-    <t>Verify remaining balance display match before payment</t>
-  </si>
-  <si>
-    <t>19ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-021</t>
-  </si>
-  <si>
-    <t>Record payment E2E execution and redirection validation</t>
-  </si>
-  <si>
-    <t>3226ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-022</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
-  </si>
-  <si>
-    <t>1192ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-023</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount updates to 200 INR in customer card</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-024</t>
-  </si>
-  <si>
-    <t>Verify recorded payment entry list matches mode UPI</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-025</t>
-  </si>
-  <si>
-    <t>Verify sales management index loads properly</t>
-  </si>
-  <si>
-    <t>866ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-026</t>
-  </si>
-  <si>
-    <t>Verify sales search filter works properly</t>
-  </si>
-  <si>
-    <t>728ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-027</t>
-  </si>
-  <si>
-    <t>Navigate to Create New Sale form</t>
-  </si>
-  <si>
-    <t>801ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-028</t>
-  </si>
-  <si>
-    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
-  </si>
-  <si>
-    <t>307ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-029</t>
-  </si>
-  <si>
-    <t>Create sale and verify redirect back to sales table</t>
-  </si>
-  <si>
-    <t>207ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-030</t>
-  </si>
-  <si>
-    <t>Verify Payments page path and title</t>
-  </si>
-  <si>
-    <t>591ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-031</t>
-  </si>
-  <si>
-    <t>Verify E2E transaction exists in master list</t>
-  </si>
-  <si>
-    <t>85ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-032</t>
-  </si>
-  <si>
-    <t>Verify Ledger Book page loads</t>
-  </si>
-  <si>
-    <t>799ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-033</t>
-  </si>
-  <si>
-    <t>Verify ledger records contain client name</t>
-  </si>
-  <si>
-    <t>121ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-034</t>
-  </si>
-  <si>
-    <t>Verify Installments page title</t>
-  </si>
-  <si>
-    <t>568ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-035</t>
-  </si>
-  <si>
-    <t>Verify customer details exist on installment board</t>
-  </si>
-  <si>
-    <t>53ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-036</t>
-  </si>
-  <si>
-    <t>Verify direct Dashboard URL redirect</t>
-  </si>
-  <si>
-    <t>106ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-037</t>
-  </si>
-  <si>
-    <t>Verify customer data updates dynamically on UI edit</t>
-  </si>
-  <si>
-    <t>4447ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-038</t>
-  </si>
-  <si>
-    <t>Verify logout route terminates session and redirects to sign in</t>
-  </si>
-  <si>
-    <t>1050ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-039</t>
-  </si>
-  <si>
-    <t>Verify unauthorized dashboard access redirects to login</t>
-  </si>
-  <si>
-    <t>2104ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-040</t>
-  </si>
-  <si>
-    <t>Verify unauthorized customer details access redirects to login</t>
-  </si>
-  <si>
-    <t>2103ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-001</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting positive amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-002</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting zero amount</t>
-  </si>
-  <si>
-    <t>0ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-003</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting negative amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-004</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting large millions scale amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-005</t>
-  </si>
-  <si>
-    <t>Test formatCurrency decimal rounding functionality</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-006</t>
-  </si>
-  <si>
-    <t>Test formatDate string matching date details</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-007</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for null values</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-008</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for 0 value</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-009</t>
-  </si>
-  <si>
-    <t>Test formatDateTime details formatting</t>
-  </si>
-  <si>
-    <t>1ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-010</t>
-  </si>
-  <si>
-    <t>Test formatDateTime null timestamp handling</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-011</t>
-  </si>
-  <si>
-    <t>Verify email validation for valid string</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-012</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing TLD</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-013</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing alias prefix</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-014</t>
-  </si>
-  <si>
-    <t>Verify phone validation for standard 10 digit number</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-015</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks short length</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-016</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks alphabetic characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-017</t>
-  </si>
-  <si>
-    <t>Verify interest formula multiplication logic</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-018</t>
-  </si>
-  <si>
-    <t>Verify installment partitioning amount division</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-019</t>
-  </si>
-  <si>
-    <t>Verify remaining balance arithmetic subtraction</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-020</t>
-  </si>
-  <si>
-    <t>Verify mock environment manifest validator passes</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-001</t>
-  </si>
-  <si>
-    <t>Validation</t>
-  </si>
-  <si>
-    <t>Verify email required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>329ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-002</t>
-  </si>
-  <si>
-    <t>Verify password required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-003</t>
-  </si>
-  <si>
-    <t>Verify browser client blocks submissions for invalid email inputs</t>
-  </si>
-  <si>
-    <t>107ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-004</t>
-  </si>
-  <si>
-    <t>Verify character bounds for data buffers limit to 255 characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-005</t>
-  </si>
-  <si>
-    <t>Verify customer creation form prevents empty submit</t>
-  </si>
-  <si>
-    <t>3059ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-006</t>
-  </si>
-  <si>
-    <t>Verify phone input uses tel semantic element type</t>
-  </si>
-  <si>
-    <t>26ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-007</t>
-  </si>
-  <si>
-    <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
-  </si>
-  <si>
-    <t>563ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-008</t>
-  </si>
-  <si>
-    <t>Verify unit price input restricts negative numbers</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-009</t>
-  </si>
-  <si>
-    <t>Verify script tag input text does not trigger native alerts</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>2311ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-010</t>
-  </si>
-  <si>
-    <t>Verify database adapter parameters parameterized input query parsing</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-011</t>
-  </si>
-  <si>
-    <t>Verify error prevents overpayment collections</t>
-  </si>
-  <si>
-    <t>2120ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-012</t>
-  </si>
-  <si>
-    <t>Verify collection input restricts 0 value submissions</t>
-  </si>
-  <si>
-    <t>1143ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-013</t>
-  </si>
-  <si>
-    <t>Verify Firestore writes match schema constraints</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-014</t>
-  </si>
-  <si>
-    <t>Verify wildcard URLs redirect to main route base</t>
-  </si>
-  <si>
-    <t>2118ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-015</t>
-  </si>
-  <si>
-    <t>Verify HTML password hidden mask attribute config</t>
-  </si>
-  <si>
-    <t>668ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-001</t>
-  </si>
-  <si>
-    <t>Deployment</t>
-  </si>
-  <si>
-    <t>Verify load paint FCP under 2.5s threshold</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>124ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-002</t>
-  </si>
-  <si>
-    <t>Verify full render transition load time under limit</t>
-  </si>
-  <si>
-    <t>1185ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-003</t>
-  </si>
-  <si>
-    <t>Verify DNS host domain matches Vercel production edge</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-004</t>
-  </si>
-  <si>
-    <t>Verify favicon.ico endpoint yields clean HTTP status</t>
-  </si>
-  <si>
-    <t>103ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-005</t>
-  </si>
-  <si>
-    <t>Verify production connection protocol HTTPS encryption is active</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-006</t>
-  </si>
-  <si>
-    <t>Verify head links contain manifest registration details</t>
-  </si>
-  <si>
-    <t>147ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-007</t>
-  </si>
-  <si>
-    <t>Verify console logs have no severe exceptions during login page session</t>
-  </si>
-  <si>
-    <t>3ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-008</t>
-  </si>
-  <si>
-    <t>Verify standard responsive layouts align horizontally</t>
-  </si>
-  <si>
-    <t>56ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-009</t>
-  </si>
-  <si>
-    <t>Verify DOM count index scales cleanly</t>
   </si>
   <si>
     <t>TC-WEB-DEP-010</t>
@@ -1480,7 +1489,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -1488,13 +1497,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -1503,7 +1512,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -1511,13 +1520,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
@@ -1526,7 +1535,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -1534,13 +1543,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1549,7 +1558,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1557,13 +1566,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1572,7 +1581,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1580,13 +1589,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1595,7 +1604,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1603,13 +1612,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1618,7 +1627,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -1626,13 +1635,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1641,7 +1650,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1649,13 +1658,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1664,7 +1673,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -1672,13 +1681,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1687,7 +1696,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1695,13 +1704,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1710,7 +1719,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1718,13 +1727,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1733,7 +1742,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1741,13 +1750,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1756,7 +1765,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -1764,13 +1773,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1779,7 +1788,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -1787,13 +1796,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1802,7 +1811,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -1810,13 +1819,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1825,7 +1834,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -1833,13 +1842,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1848,7 +1857,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -1856,13 +1865,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1871,7 +1880,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -1879,13 +1888,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1894,7 +1903,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -1902,13 +1911,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1917,7 +1926,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1925,13 +1934,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1940,7 +1949,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1948,13 +1957,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1963,7 +1972,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2014,22 +2023,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2037,22 +2046,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -2060,22 +2069,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -2083,22 +2092,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -2106,22 +2115,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -2129,22 +2138,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -2152,22 +2161,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2175,22 +2184,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2198,22 +2207,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -2221,22 +2230,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -2244,22 +2253,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -2267,22 +2276,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -2290,22 +2299,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -2313,22 +2322,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -2336,22 +2345,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -2359,22 +2368,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2382,22 +2391,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2405,22 +2414,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2428,22 +2437,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2451,22 +2460,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2474,22 +2483,22 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2497,22 +2506,22 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2520,22 +2529,22 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2543,22 +2552,22 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2566,22 +2575,22 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2589,22 +2598,22 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2612,22 +2621,22 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -2635,22 +2644,22 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -2658,22 +2667,22 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2681,22 +2690,22 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2704,22 +2713,22 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2727,22 +2736,22 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2750,22 +2759,22 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2773,22 +2782,22 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2796,22 +2805,22 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>177</v>
+        <v>58</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2819,22 +2828,22 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2842,22 +2851,22 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2865,22 +2874,22 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2888,22 +2897,22 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -2911,22 +2920,22 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -2992,7 +3001,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>52</v>
+        <v>196</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3000,13 +3009,13 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>194</v>
@@ -3015,7 +3024,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3023,13 +3032,13 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>194</v>
@@ -3038,7 +3047,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3046,13 +3055,13 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>194</v>
@@ -3061,7 +3070,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3069,13 +3078,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>194</v>
@@ -3084,7 +3093,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3092,13 +3101,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>194</v>
@@ -3107,7 +3116,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
+        <v>210</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3115,13 +3124,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>194</v>
@@ -3130,7 +3139,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3138,13 +3147,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>194</v>
@@ -3153,7 +3162,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3161,13 +3170,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>194</v>
@@ -3176,7 +3185,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3184,13 +3193,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>194</v>
@@ -3199,7 +3208,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3207,13 +3216,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>194</v>
@@ -3222,7 +3231,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3230,13 +3239,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>194</v>
@@ -3245,7 +3254,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3253,13 +3262,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>194</v>
@@ -3268,7 +3277,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3276,13 +3285,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>194</v>
@@ -3291,7 +3300,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3299,13 +3308,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>194</v>
@@ -3314,7 +3323,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3322,13 +3331,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>194</v>
@@ -3337,7 +3346,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -3345,13 +3354,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>194</v>
@@ -3360,7 +3369,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -3368,13 +3377,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>194</v>
@@ -3383,7 +3392,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -3391,13 +3400,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>194</v>
@@ -3406,7 +3415,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -3414,13 +3423,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>194</v>
@@ -3429,7 +3438,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -3480,22 +3489,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3503,22 +3512,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3526,22 +3535,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3549,22 +3558,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3572,22 +3581,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3595,22 +3604,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>252</v>
+        <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3618,22 +3627,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3641,22 +3650,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>260</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3664,22 +3673,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3687,22 +3696,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3710,22 +3719,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3733,22 +3742,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3756,22 +3765,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3779,22 +3788,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3802,22 +3811,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3868,22 +3877,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3891,22 +3900,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3914,22 +3923,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3937,22 +3946,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3960,22 +3969,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3983,22 +3992,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -4006,22 +4015,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -4029,22 +4038,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>301</v>
+        <v>22</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -4052,22 +4061,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -4075,22 +4084,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>

--- a/tests/reports/Test_Analysis_Report.xlsx
+++ b/tests/reports/Test_Analysis_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="314">
   <si>
     <t>Test ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>2239ms</t>
+    <t>1816ms</t>
   </si>
   <si>
     <t>Assertion passed successfully</t>
@@ -68,7 +68,7 @@
     <t>Verify brand name PayBuddy header exists</t>
   </si>
   <si>
-    <t>322ms</t>
+    <t>88ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-003</t>
@@ -77,7 +77,7 @@
     <t>Verify form email input label</t>
   </si>
   <si>
-    <t>53ms</t>
+    <t>50ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-004</t>
@@ -86,579 +86,588 @@
     <t>Verify form password input label</t>
   </si>
   <si>
+    <t>37ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-005</t>
+  </si>
+  <si>
+    <t>Verify Sign In button is present</t>
+  </si>
+  <si>
     <t>54ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-005</t>
-  </si>
-  <si>
-    <t>Verify Sign In button is present</t>
-  </si>
-  <si>
-    <t>44ms</t>
-  </si>
-  <si>
     <t>TC-WEB-UI-006</t>
   </si>
   <si>
     <t>Verify secure access footer notice is present</t>
   </si>
   <si>
+    <t>30ms</t>
+  </si>
+  <si>
     <t>TC-WEB-UI-007</t>
   </si>
   <si>
     <t>Verify branding subtitle text exists</t>
   </si>
   <si>
+    <t>49ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-008</t>
+  </si>
+  <si>
+    <t>Verify email input field placeholder</t>
+  </si>
+  <si>
+    <t>48ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-009</t>
+  </si>
+  <si>
+    <t>Verify password input field placeholder</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-010</t>
+  </si>
+  <si>
+    <t>Verify font family CSS on headers</t>
+  </si>
+  <si>
     <t>52ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-008</t>
-  </si>
-  <si>
-    <t>Verify email input field placeholder</t>
-  </si>
-  <si>
-    <t>49ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-009</t>
-  </si>
-  <si>
-    <t>Verify password input field placeholder</t>
+    <t>TC-WEB-UI-011</t>
+  </si>
+  <si>
+    <t>Verify primary brand color on buttons</t>
+  </si>
+  <si>
+    <t>46ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-012</t>
+  </si>
+  <si>
+    <t>Verify centered block layout</t>
+  </si>
+  <si>
+    <t>56ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-013</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at mobile width 360px</t>
+  </si>
+  <si>
+    <t>935ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-014</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at tablet width 768px</t>
+  </si>
+  <si>
+    <t>912ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-015</t>
+  </si>
+  <si>
+    <t>Restore browser window maximization state</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-016</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for email input</t>
+  </si>
+  <si>
+    <t>68ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-017</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for password input</t>
+  </si>
+  <si>
+    <t>62ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-018</t>
+  </si>
+  <si>
+    <t>Verify card wrapper styles (border-radius)</t>
+  </si>
+  <si>
+    <t>35ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-019</t>
+  </si>
+  <si>
+    <t>Verify background styling matches design spec</t>
+  </si>
+  <si>
+    <t>73ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-020</t>
+  </si>
+  <si>
+    <t>Verify focus state click handler does not crash</t>
+  </si>
+  <si>
+    <t>152ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-021</t>
+  </si>
+  <si>
+    <t>Verify top-level container viewport classes</t>
+  </si>
+  <si>
+    <t>45ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-022</t>
+  </si>
+  <si>
+    <t>Verify branding and form division layout margins</t>
+  </si>
+  <si>
+    <t>40ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-023</t>
+  </si>
+  <si>
+    <t>Verify clear textual contrast for reader accessibility</t>
+  </si>
+  <si>
+    <t>38ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-024</t>
+  </si>
+  <si>
+    <t>Verify page scales properly without layout clipping</t>
+  </si>
+  <si>
+    <t>42ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-025</t>
+  </si>
+  <si>
+    <t>Verify smooth interactive transitions on button inputs</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-001</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Verify invalid login rejection message</t>
+  </si>
+  <si>
+    <t>2196ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-002</t>
+  </si>
+  <si>
+    <t>Verify rejection of nonexistent email</t>
+  </si>
+  <si>
+    <t>1319ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-003</t>
+  </si>
+  <si>
+    <t>Verify successful login with valid credentials redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>2462ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-004</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Total Customers count</t>
+  </si>
+  <si>
+    <t>531ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-005</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Active Sales count</t>
+  </si>
+  <si>
+    <t>78ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-006</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Pending Installments count</t>
+  </si>
+  <si>
+    <t>5121ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-007</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Today's Due count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-008</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Outstanding Balance amount</t>
+  </si>
+  <si>
+    <t>29ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-009</t>
+  </si>
+  <si>
+    <t>Navigate to customers page and verify header</t>
+  </si>
+  <si>
+    <t>254ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-010</t>
+  </si>
+  <si>
+    <t>Verify add new customer input inputs are present</t>
+  </si>
+  <si>
+    <t>69ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-011</t>
+  </si>
+  <si>
+    <t>Verify customer creation and entry addition to table</t>
+  </si>
+  <si>
+    <t>3065ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-012</t>
+  </si>
+  <si>
+    <t>Verify presence of seeded customer</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-013</t>
+  </si>
+  <si>
+    <t>Navigate to specific customer profile page</t>
+  </si>
+  <si>
+    <t>1957ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-014</t>
+  </si>
+  <si>
+    <t>Verify phone number exists on profile detail bar</t>
   </si>
   <si>
     <t>51ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-010</t>
-  </si>
-  <si>
-    <t>Verify font family CSS on headers</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-011</t>
-  </si>
-  <si>
-    <t>Verify primary brand color on buttons</t>
-  </si>
-  <si>
-    <t>47ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-012</t>
-  </si>
-  <si>
-    <t>Verify centered block layout</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-013</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at mobile width 360px</t>
-  </si>
-  <si>
-    <t>945ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-014</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at tablet width 768px</t>
-  </si>
-  <si>
-    <t>942ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-015</t>
-  </si>
-  <si>
-    <t>Restore browser window maximization state</t>
-  </si>
-  <si>
-    <t>59ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-016</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for email input</t>
-  </si>
-  <si>
-    <t>67ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-017</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for password input</t>
-  </si>
-  <si>
-    <t>50ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-018</t>
-  </si>
-  <si>
-    <t>Verify card wrapper styles (border-radius)</t>
-  </si>
-  <si>
-    <t>110ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-019</t>
-  </si>
-  <si>
-    <t>Verify background styling matches design spec</t>
-  </si>
-  <si>
-    <t>45ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-020</t>
-  </si>
-  <si>
-    <t>Verify focus state click handler does not crash</t>
-  </si>
-  <si>
-    <t>156ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-021</t>
-  </si>
-  <si>
-    <t>Verify top-level container viewport classes</t>
-  </si>
-  <si>
-    <t>64ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-022</t>
-  </si>
-  <si>
-    <t>Verify branding and form division layout margins</t>
-  </si>
-  <si>
-    <t>61ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-023</t>
-  </si>
-  <si>
-    <t>Verify clear textual contrast for reader accessibility</t>
-  </si>
-  <si>
-    <t>56ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-024</t>
-  </si>
-  <si>
-    <t>Verify page scales properly without layout clipping</t>
-  </si>
-  <si>
-    <t>38ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-025</t>
-  </si>
-  <si>
-    <t>Verify smooth interactive transitions on button inputs</t>
+    <t>TC-WEB-FUNC-015</t>
+  </si>
+  <si>
+    <t>Verify Total Amount financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-016</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount financial card is 0 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-017</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-018</t>
+  </si>
+  <si>
+    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
+  </si>
+  <si>
+    <t>58ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-019</t>
+  </si>
+  <si>
+    <t>Verify redirect to record payment page</t>
+  </si>
+  <si>
+    <t>1139ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-020</t>
+  </si>
+  <si>
+    <t>Verify remaining balance display match before payment</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-021</t>
+  </si>
+  <si>
+    <t>Record payment E2E execution and redirection validation</t>
+  </si>
+  <si>
+    <t>3532ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-022</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
+  </si>
+  <si>
+    <t>1170ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-023</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount updates to 200 INR in customer card</t>
   </si>
   <si>
     <t>33ms</t>
   </si>
   <si>
-    <t>TC-WEB-FUNC-001</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>Verify invalid login rejection message</t>
-  </si>
-  <si>
-    <t>1912ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-002</t>
-  </si>
-  <si>
-    <t>Verify rejection of nonexistent email</t>
-  </si>
-  <si>
-    <t>1667ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-003</t>
-  </si>
-  <si>
-    <t>Verify successful login with valid credentials redirects to Dashboard</t>
-  </si>
-  <si>
-    <t>2080ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-004</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Total Customers count</t>
-  </si>
-  <si>
-    <t>281ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-005</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Active Sales count</t>
-  </si>
-  <si>
-    <t>60ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-006</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Pending Installments count</t>
-  </si>
-  <si>
-    <t>35ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-007</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Today's Due count</t>
-  </si>
-  <si>
-    <t>36ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-008</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Outstanding Balance amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-009</t>
-  </si>
-  <si>
-    <t>Navigate to customers page and verify header</t>
-  </si>
-  <si>
-    <t>393ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-010</t>
-  </si>
-  <si>
-    <t>Verify add new customer input inputs are present</t>
-  </si>
-  <si>
-    <t>57ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-011</t>
-  </si>
-  <si>
-    <t>Verify customer creation and entry addition to table</t>
-  </si>
-  <si>
-    <t>3044ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-012</t>
-  </si>
-  <si>
-    <t>Verify presence of seeded customer</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-013</t>
-  </si>
-  <si>
-    <t>Navigate to specific customer profile page</t>
-  </si>
-  <si>
-    <t>1425ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-014</t>
-  </si>
-  <si>
-    <t>Verify phone number exists on profile detail bar</t>
+    <t>TC-WEB-FUNC-024</t>
+  </si>
+  <si>
+    <t>Verify recorded payment entry list matches mode UPI</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-025</t>
+  </si>
+  <si>
+    <t>Verify sales management index loads properly</t>
+  </si>
+  <si>
+    <t>882ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-026</t>
+  </si>
+  <si>
+    <t>Verify sales search filter works properly</t>
+  </si>
+  <si>
+    <t>843ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-027</t>
+  </si>
+  <si>
+    <t>Navigate to Create New Sale form</t>
+  </si>
+  <si>
+    <t>927ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-028</t>
+  </si>
+  <si>
+    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
+  </si>
+  <si>
+    <t>673ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-029</t>
+  </si>
+  <si>
+    <t>Create sale and verify redirect back to sales table</t>
+  </si>
+  <si>
+    <t>497ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-030</t>
+  </si>
+  <si>
+    <t>Verify Payments page path and title</t>
+  </si>
+  <si>
+    <t>891ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-031</t>
+  </si>
+  <si>
+    <t>Verify E2E transaction exists in master list</t>
+  </si>
+  <si>
+    <t>66ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-032</t>
+  </si>
+  <si>
+    <t>Verify Ledger Book page loads</t>
+  </si>
+  <si>
+    <t>874ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-033</t>
+  </si>
+  <si>
+    <t>Verify ledger records contain client name</t>
+  </si>
+  <si>
+    <t>98ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-034</t>
+  </si>
+  <si>
+    <t>Verify Installments page title</t>
+  </si>
+  <si>
+    <t>855ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-035</t>
+  </si>
+  <si>
+    <t>Verify customer details exist on installment board</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-036</t>
+  </si>
+  <si>
+    <t>Verify direct Dashboard URL redirect</t>
+  </si>
+  <si>
+    <t>148ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-037</t>
+  </si>
+  <si>
+    <t>Verify customer data updates dynamically on UI edit</t>
+  </si>
+  <si>
+    <t>4889ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-038</t>
+  </si>
+  <si>
+    <t>Verify logout route terminates session and redirects to sign in</t>
+  </si>
+  <si>
+    <t>5357ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-039</t>
+  </si>
+  <si>
+    <t>Verify unauthorized dashboard access redirects to login</t>
+  </si>
+  <si>
+    <t>2201ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-040</t>
+  </si>
+  <si>
+    <t>Verify unauthorized customer details access redirects to login</t>
+  </si>
+  <si>
+    <t>2166ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-001</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting positive amount</t>
+  </si>
+  <si>
+    <t>76ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-002</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting zero amount</t>
+  </si>
+  <si>
+    <t>2ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-003</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting negative amount</t>
+  </si>
+  <si>
+    <t>1ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-004</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting large millions scale amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-005</t>
+  </si>
+  <si>
+    <t>Test formatCurrency decimal rounding functionality</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-006</t>
+  </si>
+  <si>
+    <t>Test formatDate string matching date details</t>
   </si>
   <si>
     <t>39ms</t>
   </si>
   <si>
-    <t>TC-WEB-FUNC-015</t>
-  </si>
-  <si>
-    <t>Verify Total Amount financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-016</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount financial card is 0 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-017</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>41ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-018</t>
-  </si>
-  <si>
-    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-019</t>
-  </si>
-  <si>
-    <t>Verify redirect to record payment page</t>
-  </si>
-  <si>
-    <t>1096ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-020</t>
-  </si>
-  <si>
-    <t>Verify remaining balance display match before payment</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-021</t>
-  </si>
-  <si>
-    <t>Record payment E2E execution and redirection validation</t>
-  </si>
-  <si>
-    <t>3240ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-022</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
-  </si>
-  <si>
-    <t>1228ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-023</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount updates to 200 INR in customer card</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-024</t>
-  </si>
-  <si>
-    <t>Verify recorded payment entry list matches mode UPI</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-025</t>
-  </si>
-  <si>
-    <t>Verify sales management index loads properly</t>
-  </si>
-  <si>
-    <t>728ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-026</t>
-  </si>
-  <si>
-    <t>Verify sales search filter works properly</t>
-  </si>
-  <si>
-    <t>794ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-027</t>
-  </si>
-  <si>
-    <t>Navigate to Create New Sale form</t>
-  </si>
-  <si>
-    <t>666ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-028</t>
-  </si>
-  <si>
-    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
-  </si>
-  <si>
-    <t>655ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-029</t>
-  </si>
-  <si>
-    <t>Create sale and verify redirect back to sales table</t>
-  </si>
-  <si>
-    <t>500ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-030</t>
-  </si>
-  <si>
-    <t>Verify Payments page path and title</t>
-  </si>
-  <si>
-    <t>662ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-031</t>
-  </si>
-  <si>
-    <t>Verify E2E transaction exists in master list</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-032</t>
-  </si>
-  <si>
-    <t>Verify Ledger Book page loads</t>
-  </si>
-  <si>
-    <t>743ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-033</t>
-  </si>
-  <si>
-    <t>Verify ledger records contain client name</t>
-  </si>
-  <si>
-    <t>71ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-034</t>
-  </si>
-  <si>
-    <t>Verify Installments page title</t>
-  </si>
-  <si>
-    <t>648ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-035</t>
-  </si>
-  <si>
-    <t>Verify customer details exist on installment board</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-036</t>
-  </si>
-  <si>
-    <t>Verify direct Dashboard URL redirect</t>
-  </si>
-  <si>
-    <t>123ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-037</t>
-  </si>
-  <si>
-    <t>Verify customer data updates dynamically on UI edit</t>
-  </si>
-  <si>
-    <t>4674ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-038</t>
-  </si>
-  <si>
-    <t>Verify logout route terminates session and redirects to sign in</t>
-  </si>
-  <si>
-    <t>809ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-039</t>
-  </si>
-  <si>
-    <t>Verify unauthorized dashboard access redirects to login</t>
-  </si>
-  <si>
-    <t>2153ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-040</t>
-  </si>
-  <si>
-    <t>Verify unauthorized customer details access redirects to login</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-001</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting positive amount</t>
-  </si>
-  <si>
-    <t>79ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-002</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting zero amount</t>
-  </si>
-  <si>
-    <t>1ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-003</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting negative amount</t>
-  </si>
-  <si>
-    <t>2ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-004</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting large millions scale amount</t>
+    <t>TC-WEB-UNIT-007</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for null values</t>
   </si>
   <si>
     <t>0ms</t>
   </si>
   <si>
-    <t>TC-WEB-UNIT-005</t>
-  </si>
-  <si>
-    <t>Test formatCurrency decimal rounding functionality</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-006</t>
-  </si>
-  <si>
-    <t>Test formatDate string matching date details</t>
-  </si>
-  <si>
-    <t>22ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-007</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for null values</t>
-  </si>
-  <si>
     <t>TC-WEB-UNIT-008</t>
   </si>
   <si>
@@ -746,7 +755,7 @@
     <t>Verify email required constraint is enabled on form</t>
   </si>
   <si>
-    <t>191ms</t>
+    <t>5249ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-002</t>
@@ -755,13 +764,16 @@
     <t>Verify password required constraint is enabled on form</t>
   </si>
   <si>
+    <t>5116ms</t>
+  </si>
+  <si>
     <t>TC-WEB-VAL-003</t>
   </si>
   <si>
     <t>Verify browser client blocks submissions for invalid email inputs</t>
   </si>
   <si>
-    <t>253ms</t>
+    <t>5132ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-004</t>
@@ -776,7 +788,7 @@
     <t>Verify customer creation form prevents empty submit</t>
   </si>
   <si>
-    <t>3184ms</t>
+    <t>10165ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-006</t>
@@ -785,13 +797,16 @@
     <t>Verify phone input uses tel semantic element type</t>
   </si>
   <si>
+    <t>5094ms</t>
+  </si>
+  <si>
     <t>TC-WEB-VAL-007</t>
   </si>
   <si>
     <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
   </si>
   <si>
-    <t>624ms</t>
+    <t>887ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-008</t>
@@ -800,9 +815,6 @@
     <t>Verify unit price input restricts negative numbers</t>
   </si>
   <si>
-    <t>37ms</t>
-  </si>
-  <si>
     <t>TC-WEB-VAL-009</t>
   </si>
   <si>
@@ -812,7 +824,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2472ms</t>
+    <t>2578ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-010</t>
@@ -827,7 +839,7 @@
     <t>Verify error prevents overpayment collections</t>
   </si>
   <si>
-    <t>1936ms</t>
+    <t>2374ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-012</t>
@@ -836,7 +848,7 @@
     <t>Verify collection input restricts 0 value submissions</t>
   </si>
   <si>
-    <t>1437ms</t>
+    <t>1336ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-013</t>
@@ -851,7 +863,7 @@
     <t>Verify wildcard URLs redirect to main route base</t>
   </si>
   <si>
-    <t>2128ms</t>
+    <t>2146ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-015</t>
@@ -860,7 +872,7 @@
     <t>Verify HTML password hidden mask attribute config</t>
   </si>
   <si>
-    <t>844ms</t>
+    <t>5313ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-001</t>
@@ -875,7 +887,7 @@
     <t>Performance</t>
   </si>
   <si>
-    <t>152ms</t>
+    <t>158ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-002</t>
@@ -884,7 +896,7 @@
     <t>Verify full render transition load time under limit</t>
   </si>
   <si>
-    <t>1451ms</t>
+    <t>10151ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-003</t>
@@ -899,7 +911,7 @@
     <t>Verify favicon.ico endpoint yields clean HTTP status</t>
   </si>
   <si>
-    <t>127ms</t>
+    <t>120ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-005</t>
@@ -914,7 +926,7 @@
     <t>Verify head links contain manifest registration details</t>
   </si>
   <si>
-    <t>184ms</t>
+    <t>183ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-007</t>
@@ -923,13 +935,16 @@
     <t>Verify console logs have no severe exceptions during login page session</t>
   </si>
   <si>
-    <t>8ms</t>
+    <t>9ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-008</t>
   </si>
   <si>
     <t>Verify standard responsive layouts align horizontally</t>
+  </si>
+  <si>
+    <t>82ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-009</t>
@@ -1535,7 +1550,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -1543,13 +1558,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1558,7 +1573,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1566,13 +1581,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1581,7 +1596,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1589,13 +1604,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1604,7 +1619,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1627,7 +1642,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -1635,13 +1650,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1650,7 +1665,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1658,13 +1673,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1673,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -1681,13 +1696,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1696,7 +1711,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1704,13 +1719,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1719,7 +1734,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1727,13 +1742,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1742,7 +1757,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1750,13 +1765,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1765,7 +1780,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -1773,13 +1788,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1788,7 +1803,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -1796,13 +1811,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1811,7 +1826,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -1819,13 +1834,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1834,7 +1849,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -1842,13 +1857,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1857,7 +1872,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -1865,13 +1880,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1880,7 +1895,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -1888,13 +1903,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1903,7 +1918,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -1911,13 +1926,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1926,7 +1941,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1934,13 +1949,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1949,7 +1964,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1957,13 +1972,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1972,7 +1987,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2176,7 +2191,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2184,22 +2199,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2291,7 +2306,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -2360,7 +2375,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -2383,7 +2398,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2406,7 +2421,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2414,22 +2429,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2475,7 +2490,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2544,7 +2559,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2552,13 +2567,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>84</v>
@@ -2567,7 +2582,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2575,13 +2590,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>84</v>
@@ -2590,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2598,13 +2613,13 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>84</v>
@@ -2613,7 +2628,7 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2621,13 +2636,13 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>84</v>
@@ -2636,7 +2651,7 @@
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -2644,13 +2659,13 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>84</v>
@@ -2659,7 +2674,7 @@
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -2667,13 +2682,13 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>84</v>
@@ -2682,7 +2697,7 @@
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2690,13 +2705,13 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>84</v>
@@ -2705,7 +2720,7 @@
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2713,13 +2728,13 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>84</v>
@@ -2728,7 +2743,7 @@
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2736,13 +2751,13 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -2751,7 +2766,7 @@
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2759,13 +2774,13 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>84</v>
@@ -2774,7 +2789,7 @@
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2782,13 +2797,13 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>84</v>
@@ -2797,7 +2812,7 @@
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2805,13 +2820,13 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>84</v>
@@ -2820,7 +2835,7 @@
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2828,13 +2843,13 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>84</v>
@@ -2843,7 +2858,7 @@
         <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2851,13 +2866,13 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>84</v>
@@ -2866,7 +2881,7 @@
         <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2874,13 +2889,13 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>84</v>
@@ -2889,7 +2904,7 @@
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2897,13 +2912,13 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>84</v>
@@ -2912,7 +2927,7 @@
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -2920,13 +2935,13 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>84</v>
@@ -2935,7 +2950,7 @@
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -2986,22 +3001,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3009,22 +3024,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3032,22 +3047,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3055,16 +3070,16 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
@@ -3078,22 +3093,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3101,22 +3116,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3124,22 +3139,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3147,22 +3162,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3170,22 +3185,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3193,16 +3208,16 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
@@ -3216,16 +3231,16 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
@@ -3239,22 +3254,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3262,22 +3277,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3285,22 +3300,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3308,22 +3323,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3331,16 +3346,16 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
@@ -3354,22 +3369,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -3377,22 +3392,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -3400,22 +3415,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -3423,22 +3438,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -3489,22 +3504,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3512,22 +3527,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3535,22 +3550,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3558,22 +3573,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3581,22 +3596,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3604,22 +3619,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>64</v>
+        <v>259</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3627,22 +3642,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3650,22 +3665,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>260</v>
+        <v>106</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3673,22 +3688,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3696,22 +3711,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3719,22 +3734,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3742,22 +3757,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3765,22 +3780,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3788,22 +3803,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3811,22 +3826,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3877,22 +3892,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3900,22 +3915,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3923,16 +3938,16 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
@@ -3946,22 +3961,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3969,22 +3984,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3992,22 +4007,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -4015,22 +4030,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -4038,22 +4053,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -4061,22 +4076,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -4084,22 +4099,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>

--- a/tests/reports/Test_Analysis_Report.xlsx
+++ b/tests/reports/Test_Analysis_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="312">
   <si>
     <t>Test ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>1816ms</t>
+    <t>4735ms</t>
   </si>
   <si>
     <t>Assertion passed successfully</t>
@@ -68,7 +68,7 @@
     <t>Verify brand name PayBuddy header exists</t>
   </si>
   <si>
-    <t>88ms</t>
+    <t>105ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-003</t>
@@ -77,883 +77,877 @@
     <t>Verify form email input label</t>
   </si>
   <si>
+    <t>77ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-004</t>
+  </si>
+  <si>
+    <t>Verify form password input label</t>
+  </si>
+  <si>
+    <t>57ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-005</t>
+  </si>
+  <si>
+    <t>Verify Sign In button is present</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-006</t>
+  </si>
+  <si>
+    <t>Verify secure access footer notice is present</t>
+  </si>
+  <si>
+    <t>31ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-007</t>
+  </si>
+  <si>
+    <t>Verify branding subtitle text exists</t>
+  </si>
+  <si>
+    <t>52ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-008</t>
+  </si>
+  <si>
+    <t>Verify email input field placeholder</t>
+  </si>
+  <si>
+    <t>48ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-009</t>
+  </si>
+  <si>
+    <t>Verify password input field placeholder</t>
+  </si>
+  <si>
+    <t>47ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-010</t>
+  </si>
+  <si>
+    <t>Verify font family CSS on headers</t>
+  </si>
+  <si>
+    <t>56ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-011</t>
+  </si>
+  <si>
+    <t>Verify primary brand color on buttons</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-012</t>
+  </si>
+  <si>
+    <t>Verify centered block layout</t>
+  </si>
+  <si>
+    <t>49ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-013</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at mobile width 360px</t>
+  </si>
+  <si>
+    <t>1001ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-014</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at tablet width 768px</t>
+  </si>
+  <si>
+    <t>966ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-015</t>
+  </si>
+  <si>
+    <t>Restore browser window maximization state</t>
+  </si>
+  <si>
+    <t>84ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-016</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for email input</t>
+  </si>
+  <si>
+    <t>100ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-017</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for password input</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-018</t>
+  </si>
+  <si>
+    <t>Verify card wrapper styles (border-radius)</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-019</t>
+  </si>
+  <si>
+    <t>Verify background styling matches design spec</t>
+  </si>
+  <si>
+    <t>42ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-020</t>
+  </si>
+  <si>
+    <t>Verify focus state click handler does not crash</t>
+  </si>
+  <si>
+    <t>229ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-021</t>
+  </si>
+  <si>
+    <t>Verify top-level container viewport classes</t>
+  </si>
+  <si>
+    <t>45ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-022</t>
+  </si>
+  <si>
+    <t>Verify branding and form division layout margins</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-023</t>
+  </si>
+  <si>
+    <t>Verify clear textual contrast for reader accessibility</t>
+  </si>
+  <si>
+    <t>60ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-024</t>
+  </si>
+  <si>
+    <t>Verify page scales properly without layout clipping</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-025</t>
+  </si>
+  <si>
+    <t>Verify smooth interactive transitions on button inputs</t>
+  </si>
+  <si>
+    <t>64ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-001</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Verify invalid login rejection message</t>
+  </si>
+  <si>
+    <t>2667ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-002</t>
+  </si>
+  <si>
+    <t>Verify rejection of nonexistent email</t>
+  </si>
+  <si>
+    <t>1659ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-003</t>
+  </si>
+  <si>
+    <t>Verify successful login with valid credentials redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>5564ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-004</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Total Customers count</t>
+  </si>
+  <si>
+    <t>2248ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-005</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Active Sales count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-006</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Pending Installments count</t>
+  </si>
+  <si>
+    <t>5211ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-007</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Today's Due count</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-008</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Outstanding Balance amount</t>
+  </si>
+  <si>
+    <t>32ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-009</t>
+  </si>
+  <si>
+    <t>Navigate to customers page and verify header</t>
+  </si>
+  <si>
+    <t>377ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-010</t>
+  </si>
+  <si>
+    <t>Verify add new customer input inputs are present</t>
+  </si>
+  <si>
+    <t>67ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-011</t>
+  </si>
+  <si>
+    <t>Verify customer creation and entry addition to table</t>
+  </si>
+  <si>
+    <t>3059ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-012</t>
+  </si>
+  <si>
+    <t>Verify presence of seeded customer</t>
+  </si>
+  <si>
+    <t>43ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-013</t>
+  </si>
+  <si>
+    <t>Navigate to specific customer profile page</t>
+  </si>
+  <si>
+    <t>3143ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-014</t>
+  </si>
+  <si>
+    <t>Verify phone number exists on profile detail bar</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-015</t>
+  </si>
+  <si>
+    <t>Verify Total Amount financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>39ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-016</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount financial card is 0 INR</t>
+  </si>
+  <si>
+    <t>36ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-017</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance financial card is 1000 INR</t>
+  </si>
+  <si>
+    <t>35ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-018</t>
+  </si>
+  <si>
+    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-019</t>
+  </si>
+  <si>
+    <t>Verify redirect to record payment page</t>
+  </si>
+  <si>
+    <t>6593ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-020</t>
+  </si>
+  <si>
+    <t>Verify remaining balance display match before payment</t>
+  </si>
+  <si>
+    <t>289ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-021</t>
+  </si>
+  <si>
+    <t>Record payment E2E execution and redirection validation</t>
+  </si>
+  <si>
+    <t>5100ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-022</t>
+  </si>
+  <si>
+    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
+  </si>
+  <si>
+    <t>3376ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-023</t>
+  </si>
+  <si>
+    <t>Verify Paid Amount updates to 200 INR in customer card</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-024</t>
+  </si>
+  <si>
+    <t>Verify recorded payment entry list matches mode UPI</t>
+  </si>
+  <si>
+    <t>55ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-025</t>
+  </si>
+  <si>
+    <t>Verify sales management index loads properly</t>
+  </si>
+  <si>
+    <t>2581ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-026</t>
+  </si>
+  <si>
+    <t>Verify sales search filter works properly</t>
+  </si>
+  <si>
+    <t>817ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-027</t>
+  </si>
+  <si>
+    <t>Navigate to Create New Sale form</t>
+  </si>
+  <si>
+    <t>2949ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-028</t>
+  </si>
+  <si>
+    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
+  </si>
+  <si>
+    <t>700ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-029</t>
+  </si>
+  <si>
+    <t>Create sale and verify redirect back to sales table</t>
+  </si>
+  <si>
+    <t>568ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-030</t>
+  </si>
+  <si>
+    <t>Verify Payments page path and title</t>
+  </si>
+  <si>
+    <t>2138ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-031</t>
+  </si>
+  <si>
+    <t>Verify E2E transaction exists in master list</t>
+  </si>
+  <si>
+    <t>75ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-032</t>
+  </si>
+  <si>
+    <t>Verify Ledger Book page loads</t>
+  </si>
+  <si>
+    <t>1956ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-033</t>
+  </si>
+  <si>
+    <t>Verify ledger records contain client name</t>
+  </si>
+  <si>
+    <t>175ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-034</t>
+  </si>
+  <si>
+    <t>Verify Installments page title</t>
+  </si>
+  <si>
+    <t>6373ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-035</t>
+  </si>
+  <si>
+    <t>Verify customer details exist on installment board</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-036</t>
+  </si>
+  <si>
+    <t>Verify direct Dashboard URL redirect</t>
+  </si>
+  <si>
+    <t>2878ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-037</t>
+  </si>
+  <si>
+    <t>Verify customer data updates dynamically on UI edit</t>
+  </si>
+  <si>
+    <t>6216ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-038</t>
+  </si>
+  <si>
+    <t>Verify logout route terminates session and redirects to sign in</t>
+  </si>
+  <si>
+    <t>5921ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-039</t>
+  </si>
+  <si>
+    <t>Verify unauthorized dashboard access redirects to login</t>
+  </si>
+  <si>
+    <t>2829ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-040</t>
+  </si>
+  <si>
+    <t>Verify unauthorized customer details access redirects to login</t>
+  </si>
+  <si>
+    <t>3356ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-001</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting positive amount</t>
+  </si>
+  <si>
+    <t>78ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-002</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting zero amount</t>
+  </si>
+  <si>
+    <t>0ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-003</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting negative amount</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-004</t>
+  </si>
+  <si>
+    <t>Test formatCurrency formatting large millions scale amount</t>
+  </si>
+  <si>
+    <t>1ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-005</t>
+  </si>
+  <si>
+    <t>Test formatCurrency decimal rounding functionality</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-006</t>
+  </si>
+  <si>
+    <t>Test formatDate string matching date details</t>
+  </si>
+  <si>
+    <t>20ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-007</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for null values</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-008</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for 0 value</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-009</t>
+  </si>
+  <si>
+    <t>Test formatDateTime details formatting</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-010</t>
+  </si>
+  <si>
+    <t>Test formatDateTime null timestamp handling</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-011</t>
+  </si>
+  <si>
+    <t>Verify email validation for valid string</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-012</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing TLD</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-013</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing alias prefix</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-014</t>
+  </si>
+  <si>
+    <t>Verify phone validation for standard 10 digit number</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-015</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks short length</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-016</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks alphabetic characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-017</t>
+  </si>
+  <si>
+    <t>Verify interest formula multiplication logic</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-018</t>
+  </si>
+  <si>
+    <t>Verify installment partitioning amount division</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-019</t>
+  </si>
+  <si>
+    <t>Verify remaining balance arithmetic subtraction</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-020</t>
+  </si>
+  <si>
+    <t>Verify mock environment manifest validator passes</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-001</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Verify email required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>7170ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-002</t>
+  </si>
+  <si>
+    <t>Verify password required constraint is enabled on form</t>
+  </si>
+  <si>
+    <t>5187ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-003</t>
+  </si>
+  <si>
+    <t>Verify browser client blocks submissions for invalid email inputs</t>
+  </si>
+  <si>
+    <t>5127ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-004</t>
+  </si>
+  <si>
+    <t>Verify character bounds for data buffers limit to 255 characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-005</t>
+  </si>
+  <si>
+    <t>Verify customer creation form prevents empty submit</t>
+  </si>
+  <si>
+    <t>11622ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-006</t>
+  </si>
+  <si>
+    <t>Verify phone input uses tel semantic element type</t>
+  </si>
+  <si>
+    <t>5118ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-007</t>
+  </si>
+  <si>
+    <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
+  </si>
+  <si>
+    <t>9879ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-008</t>
+  </si>
+  <si>
+    <t>Verify unit price input restricts negative numbers</t>
+  </si>
+  <si>
+    <t>2552ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-009</t>
+  </si>
+  <si>
+    <t>Verify script tag input text does not trigger native alerts</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>5825ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-010</t>
+  </si>
+  <si>
+    <t>Verify database adapter parameters parameterized input query parsing</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-011</t>
+  </si>
+  <si>
+    <t>Verify error prevents overpayment collections</t>
+  </si>
+  <si>
+    <t>3060ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-012</t>
+  </si>
+  <si>
+    <t>Verify collection input restricts 0 value submissions</t>
+  </si>
+  <si>
+    <t>1323ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-013</t>
+  </si>
+  <si>
+    <t>Verify Firestore writes match schema constraints</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-014</t>
+  </si>
+  <si>
+    <t>Verify wildcard URLs redirect to main route base</t>
+  </si>
+  <si>
+    <t>2466ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-VAL-015</t>
+  </si>
+  <si>
+    <t>Verify HTML password hidden mask attribute config</t>
+  </si>
+  <si>
+    <t>6420ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-001</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Verify load paint FCP under 2.5s threshold</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>705ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-002</t>
+  </si>
+  <si>
+    <t>Verify full render transition load time under limit</t>
+  </si>
+  <si>
+    <t>10680ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-003</t>
+  </si>
+  <si>
+    <t>Verify DNS host domain matches Vercel production edge</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-004</t>
+  </si>
+  <si>
+    <t>Verify favicon.ico endpoint yields clean HTTP status</t>
+  </si>
+  <si>
+    <t>363ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-005</t>
+  </si>
+  <si>
+    <t>Verify production connection protocol HTTPS encryption is active</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-006</t>
+  </si>
+  <si>
+    <t>Verify head links contain manifest registration details</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-007</t>
+  </si>
+  <si>
+    <t>Verify console logs have no severe exceptions during login page session</t>
+  </si>
+  <si>
+    <t>8ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-DEP-008</t>
+  </si>
+  <si>
+    <t>Verify standard responsive layouts align horizontally</t>
+  </si>
+  <si>
     <t>50ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-004</t>
-  </si>
-  <si>
-    <t>Verify form password input label</t>
-  </si>
-  <si>
-    <t>37ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-005</t>
-  </si>
-  <si>
-    <t>Verify Sign In button is present</t>
-  </si>
-  <si>
-    <t>54ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-006</t>
-  </si>
-  <si>
-    <t>Verify secure access footer notice is present</t>
-  </si>
-  <si>
-    <t>30ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-007</t>
-  </si>
-  <si>
-    <t>Verify branding subtitle text exists</t>
-  </si>
-  <si>
-    <t>49ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-008</t>
-  </si>
-  <si>
-    <t>Verify email input field placeholder</t>
-  </si>
-  <si>
-    <t>48ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-009</t>
-  </si>
-  <si>
-    <t>Verify password input field placeholder</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-010</t>
-  </si>
-  <si>
-    <t>Verify font family CSS on headers</t>
-  </si>
-  <si>
-    <t>52ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-011</t>
-  </si>
-  <si>
-    <t>Verify primary brand color on buttons</t>
-  </si>
-  <si>
-    <t>46ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-012</t>
-  </si>
-  <si>
-    <t>Verify centered block layout</t>
-  </si>
-  <si>
-    <t>56ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-013</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at mobile width 360px</t>
-  </si>
-  <si>
-    <t>935ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-014</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at tablet width 768px</t>
-  </si>
-  <si>
-    <t>912ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-015</t>
-  </si>
-  <si>
-    <t>Restore browser window maximization state</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-016</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for email input</t>
-  </si>
-  <si>
-    <t>68ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-017</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for password input</t>
-  </si>
-  <si>
-    <t>62ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-018</t>
-  </si>
-  <si>
-    <t>Verify card wrapper styles (border-radius)</t>
-  </si>
-  <si>
-    <t>35ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-019</t>
-  </si>
-  <si>
-    <t>Verify background styling matches design spec</t>
-  </si>
-  <si>
-    <t>73ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-020</t>
-  </si>
-  <si>
-    <t>Verify focus state click handler does not crash</t>
-  </si>
-  <si>
-    <t>152ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-021</t>
-  </si>
-  <si>
-    <t>Verify top-level container viewport classes</t>
-  </si>
-  <si>
-    <t>45ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-022</t>
-  </si>
-  <si>
-    <t>Verify branding and form division layout margins</t>
-  </si>
-  <si>
-    <t>40ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-023</t>
-  </si>
-  <si>
-    <t>Verify clear textual contrast for reader accessibility</t>
-  </si>
-  <si>
-    <t>38ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-024</t>
-  </si>
-  <si>
-    <t>Verify page scales properly without layout clipping</t>
-  </si>
-  <si>
-    <t>42ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-025</t>
-  </si>
-  <si>
-    <t>Verify smooth interactive transitions on button inputs</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-001</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>Verify invalid login rejection message</t>
-  </si>
-  <si>
-    <t>2196ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-002</t>
-  </si>
-  <si>
-    <t>Verify rejection of nonexistent email</t>
-  </si>
-  <si>
-    <t>1319ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-003</t>
-  </si>
-  <si>
-    <t>Verify successful login with valid credentials redirects to Dashboard</t>
-  </si>
-  <si>
-    <t>2462ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-004</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Total Customers count</t>
-  </si>
-  <si>
-    <t>531ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-005</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Active Sales count</t>
-  </si>
-  <si>
-    <t>78ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-006</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Pending Installments count</t>
-  </si>
-  <si>
-    <t>5121ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-007</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Today's Due count</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-008</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Outstanding Balance amount</t>
-  </si>
-  <si>
-    <t>29ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-009</t>
-  </si>
-  <si>
-    <t>Navigate to customers page and verify header</t>
-  </si>
-  <si>
-    <t>254ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-010</t>
-  </si>
-  <si>
-    <t>Verify add new customer input inputs are present</t>
-  </si>
-  <si>
-    <t>69ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-011</t>
-  </si>
-  <si>
-    <t>Verify customer creation and entry addition to table</t>
-  </si>
-  <si>
-    <t>3065ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-012</t>
-  </si>
-  <si>
-    <t>Verify presence of seeded customer</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-013</t>
-  </si>
-  <si>
-    <t>Navigate to specific customer profile page</t>
-  </si>
-  <si>
-    <t>1957ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-014</t>
-  </si>
-  <si>
-    <t>Verify phone number exists on profile detail bar</t>
-  </si>
-  <si>
-    <t>51ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-015</t>
-  </si>
-  <si>
-    <t>Verify Total Amount financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-016</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount financial card is 0 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-017</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance financial card is 1000 INR</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-018</t>
-  </si>
-  <si>
-    <t>Verify E2E Test Item pending sale is loaded in sales list</t>
-  </si>
-  <si>
-    <t>58ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-019</t>
-  </si>
-  <si>
-    <t>Verify redirect to record payment page</t>
-  </si>
-  <si>
-    <t>1139ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-020</t>
-  </si>
-  <si>
-    <t>Verify remaining balance display match before payment</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-021</t>
-  </si>
-  <si>
-    <t>Record payment E2E execution and redirection validation</t>
-  </si>
-  <si>
-    <t>3532ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-022</t>
-  </si>
-  <si>
-    <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
-  </si>
-  <si>
-    <t>1170ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-023</t>
-  </si>
-  <si>
-    <t>Verify Paid Amount updates to 200 INR in customer card</t>
-  </si>
-  <si>
-    <t>33ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-024</t>
-  </si>
-  <si>
-    <t>Verify recorded payment entry list matches mode UPI</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-025</t>
-  </si>
-  <si>
-    <t>Verify sales management index loads properly</t>
-  </si>
-  <si>
-    <t>882ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-026</t>
-  </si>
-  <si>
-    <t>Verify sales search filter works properly</t>
-  </si>
-  <si>
-    <t>843ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-027</t>
-  </si>
-  <si>
-    <t>Navigate to Create New Sale form</t>
-  </si>
-  <si>
-    <t>927ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-028</t>
-  </si>
-  <si>
-    <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
-  </si>
-  <si>
-    <t>673ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-029</t>
-  </si>
-  <si>
-    <t>Create sale and verify redirect back to sales table</t>
-  </si>
-  <si>
-    <t>497ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-030</t>
-  </si>
-  <si>
-    <t>Verify Payments page path and title</t>
-  </si>
-  <si>
-    <t>891ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-031</t>
-  </si>
-  <si>
-    <t>Verify E2E transaction exists in master list</t>
-  </si>
-  <si>
-    <t>66ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-032</t>
-  </si>
-  <si>
-    <t>Verify Ledger Book page loads</t>
-  </si>
-  <si>
-    <t>874ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-033</t>
-  </si>
-  <si>
-    <t>Verify ledger records contain client name</t>
-  </si>
-  <si>
-    <t>98ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-034</t>
-  </si>
-  <si>
-    <t>Verify Installments page title</t>
-  </si>
-  <si>
-    <t>855ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-035</t>
-  </si>
-  <si>
-    <t>Verify customer details exist on installment board</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-036</t>
-  </si>
-  <si>
-    <t>Verify direct Dashboard URL redirect</t>
-  </si>
-  <si>
-    <t>148ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-037</t>
-  </si>
-  <si>
-    <t>Verify customer data updates dynamically on UI edit</t>
-  </si>
-  <si>
-    <t>4889ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-038</t>
-  </si>
-  <si>
-    <t>Verify logout route terminates session and redirects to sign in</t>
-  </si>
-  <si>
-    <t>5357ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-039</t>
-  </si>
-  <si>
-    <t>Verify unauthorized dashboard access redirects to login</t>
-  </si>
-  <si>
-    <t>2201ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-040</t>
-  </si>
-  <si>
-    <t>Verify unauthorized customer details access redirects to login</t>
-  </si>
-  <si>
-    <t>2166ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-001</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting positive amount</t>
-  </si>
-  <si>
-    <t>76ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-002</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting zero amount</t>
-  </si>
-  <si>
-    <t>2ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-003</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting negative amount</t>
-  </si>
-  <si>
-    <t>1ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-004</t>
-  </si>
-  <si>
-    <t>Test formatCurrency formatting large millions scale amount</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-005</t>
-  </si>
-  <si>
-    <t>Test formatCurrency decimal rounding functionality</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-006</t>
-  </si>
-  <si>
-    <t>Test formatDate string matching date details</t>
-  </si>
-  <si>
-    <t>39ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-007</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for null values</t>
-  </si>
-  <si>
-    <t>0ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-008</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for 0 value</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-009</t>
-  </si>
-  <si>
-    <t>Test formatDateTime details formatting</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-010</t>
-  </si>
-  <si>
-    <t>Test formatDateTime null timestamp handling</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-011</t>
-  </si>
-  <si>
-    <t>Verify email validation for valid string</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-012</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing TLD</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-013</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing alias prefix</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-014</t>
-  </si>
-  <si>
-    <t>Verify phone validation for standard 10 digit number</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-015</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks short length</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-016</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks alphabetic characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-017</t>
-  </si>
-  <si>
-    <t>Verify interest formula multiplication logic</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-018</t>
-  </si>
-  <si>
-    <t>Verify installment partitioning amount division</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-019</t>
-  </si>
-  <si>
-    <t>Verify remaining balance arithmetic subtraction</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-020</t>
-  </si>
-  <si>
-    <t>Verify mock environment manifest validator passes</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-001</t>
-  </si>
-  <si>
-    <t>Validation</t>
-  </si>
-  <si>
-    <t>Verify email required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>5249ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-002</t>
-  </si>
-  <si>
-    <t>Verify password required constraint is enabled on form</t>
-  </si>
-  <si>
-    <t>5116ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-003</t>
-  </si>
-  <si>
-    <t>Verify browser client blocks submissions for invalid email inputs</t>
-  </si>
-  <si>
-    <t>5132ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-004</t>
-  </si>
-  <si>
-    <t>Verify character bounds for data buffers limit to 255 characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-005</t>
-  </si>
-  <si>
-    <t>Verify customer creation form prevents empty submit</t>
-  </si>
-  <si>
-    <t>10165ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-006</t>
-  </si>
-  <si>
-    <t>Verify phone input uses tel semantic element type</t>
-  </si>
-  <si>
-    <t>5094ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-007</t>
-  </si>
-  <si>
-    <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
-  </si>
-  <si>
-    <t>887ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-008</t>
-  </si>
-  <si>
-    <t>Verify unit price input restricts negative numbers</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-009</t>
-  </si>
-  <si>
-    <t>Verify script tag input text does not trigger native alerts</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>2578ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-010</t>
-  </si>
-  <si>
-    <t>Verify database adapter parameters parameterized input query parsing</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-011</t>
-  </si>
-  <si>
-    <t>Verify error prevents overpayment collections</t>
-  </si>
-  <si>
-    <t>2374ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-012</t>
-  </si>
-  <si>
-    <t>Verify collection input restricts 0 value submissions</t>
-  </si>
-  <si>
-    <t>1336ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-013</t>
-  </si>
-  <si>
-    <t>Verify Firestore writes match schema constraints</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-014</t>
-  </si>
-  <si>
-    <t>Verify wildcard URLs redirect to main route base</t>
-  </si>
-  <si>
-    <t>2146ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-VAL-015</t>
-  </si>
-  <si>
-    <t>Verify HTML password hidden mask attribute config</t>
-  </si>
-  <si>
-    <t>5313ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-001</t>
-  </si>
-  <si>
-    <t>Deployment</t>
-  </si>
-  <si>
-    <t>Verify load paint FCP under 2.5s threshold</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>158ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-002</t>
-  </si>
-  <si>
-    <t>Verify full render transition load time under limit</t>
-  </si>
-  <si>
-    <t>10151ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-003</t>
-  </si>
-  <si>
-    <t>Verify DNS host domain matches Vercel production edge</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-004</t>
-  </si>
-  <si>
-    <t>Verify favicon.ico endpoint yields clean HTTP status</t>
-  </si>
-  <si>
-    <t>120ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-005</t>
-  </si>
-  <si>
-    <t>Verify production connection protocol HTTPS encryption is active</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-006</t>
-  </si>
-  <si>
-    <t>Verify head links contain manifest registration details</t>
-  </si>
-  <si>
-    <t>183ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-007</t>
-  </si>
-  <si>
-    <t>Verify console logs have no severe exceptions during login page session</t>
-  </si>
-  <si>
-    <t>9ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-DEP-008</t>
-  </si>
-  <si>
-    <t>Verify standard responsive layouts align horizontally</t>
-  </si>
-  <si>
-    <t>82ms</t>
-  </si>
-  <si>
     <t>TC-WEB-DEP-009</t>
   </si>
   <si>
     <t>Verify DOM count index scales cleanly</t>
   </si>
   <si>
-    <t>14ms</t>
+    <t>16ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-010</t>
@@ -1527,7 +1521,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -1535,13 +1529,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
@@ -1550,7 +1544,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -1558,13 +1552,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1573,7 +1567,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1581,13 +1575,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1596,7 +1590,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1604,13 +1598,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1619,7 +1613,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1665,7 +1659,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1673,13 +1667,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1688,7 +1682,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -1696,13 +1690,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1711,7 +1705,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1719,13 +1713,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1734,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1742,13 +1736,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1757,7 +1751,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1803,7 +1797,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -1811,13 +1805,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1826,7 +1820,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -1834,13 +1828,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1849,7 +1843,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -1857,13 +1851,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1872,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -1880,13 +1874,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1895,7 +1889,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -1903,13 +1897,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1918,7 +1912,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -1926,13 +1920,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1941,7 +1935,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1949,13 +1943,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1964,7 +1958,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1972,13 +1966,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1987,7 +1981,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2038,22 +2032,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2061,22 +2055,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -2084,22 +2078,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -2107,22 +2101,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -2130,22 +2124,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -2153,22 +2147,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -2176,22 +2170,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2199,22 +2193,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2222,22 +2216,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -2245,22 +2239,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -2268,22 +2262,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -2291,22 +2285,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -2314,22 +2308,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -2337,22 +2331,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -2360,22 +2354,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -2383,22 +2377,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2406,22 +2400,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2429,22 +2423,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2452,22 +2446,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2475,22 +2469,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2498,22 +2492,22 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2521,22 +2515,22 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2544,22 +2538,22 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2567,22 +2561,22 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2590,22 +2584,22 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2613,22 +2607,22 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2636,22 +2630,22 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -2659,22 +2653,22 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -2682,22 +2676,22 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2705,22 +2699,22 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2728,22 +2722,22 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2751,22 +2745,22 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2774,22 +2768,22 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2797,22 +2791,22 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2820,22 +2814,22 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2843,22 +2837,22 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2866,22 +2860,22 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2889,22 +2883,22 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2912,22 +2906,22 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -2935,22 +2929,22 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -3001,22 +2995,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3024,22 +3018,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3047,22 +3041,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3070,22 +3064,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3093,22 +3087,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3116,22 +3110,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3139,22 +3133,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3162,22 +3156,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3185,22 +3179,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3208,22 +3202,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3231,22 +3225,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3254,22 +3248,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3277,22 +3271,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3300,22 +3294,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3323,22 +3317,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3346,22 +3340,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -3369,22 +3363,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -3392,22 +3386,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -3415,22 +3409,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -3438,22 +3432,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -3504,22 +3498,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3527,22 +3521,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3550,22 +3544,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3573,22 +3567,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3596,22 +3590,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3619,22 +3613,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3642,22 +3636,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3665,22 +3659,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3688,22 +3682,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3711,22 +3705,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3734,22 +3728,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3757,22 +3751,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3780,22 +3774,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3803,22 +3797,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3826,22 +3820,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3892,22 +3886,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3915,22 +3909,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3938,22 +3932,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3961,22 +3955,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3984,22 +3978,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -4007,22 +4001,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>302</v>
+        <v>162</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -4030,22 +4024,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -4053,22 +4047,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -4076,22 +4070,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -4099,22 +4093,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>

--- a/tests/reports/Test_Analysis_Report.xlsx
+++ b/tests/reports/Test_Analysis_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="709">
   <si>
     <t>Test ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>4735ms</t>
+    <t>474ms</t>
   </si>
   <si>
     <t>Assertion passed successfully</t>
@@ -68,7 +68,7 @@
     <t>Verify brand name PayBuddy header exists</t>
   </si>
   <si>
-    <t>105ms</t>
+    <t>275ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-003</t>
@@ -77,7 +77,7 @@
     <t>Verify form email input label</t>
   </si>
   <si>
-    <t>77ms</t>
+    <t>16ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-004</t>
@@ -86,7 +86,7 @@
     <t>Verify form password input label</t>
   </si>
   <si>
-    <t>57ms</t>
+    <t>14ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-005</t>
@@ -101,25 +101,19 @@
     <t>Verify secure access footer notice is present</t>
   </si>
   <si>
-    <t>31ms</t>
-  </si>
-  <si>
     <t>TC-WEB-UI-007</t>
   </si>
   <si>
     <t>Verify branding subtitle text exists</t>
   </si>
   <si>
-    <t>52ms</t>
-  </si>
-  <si>
     <t>TC-WEB-UI-008</t>
   </si>
   <si>
     <t>Verify email input field placeholder</t>
   </si>
   <si>
-    <t>48ms</t>
+    <t>19ms</t>
   </si>
   <si>
     <t>TC-WEB-UI-009</t>
@@ -128,190 +122,628 @@
     <t>Verify password input field placeholder</t>
   </si>
   <si>
+    <t>TC-WEB-UI-010</t>
+  </si>
+  <si>
+    <t>Verify font family CSS on headers</t>
+  </si>
+  <si>
+    <t>20ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-011</t>
+  </si>
+  <si>
+    <t>Verify primary brand color on buttons</t>
+  </si>
+  <si>
+    <t>15ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-012</t>
+  </si>
+  <si>
+    <t>Verify centered block layout</t>
+  </si>
+  <si>
+    <t>18ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-013</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at mobile width 360px</t>
+  </si>
+  <si>
+    <t>891ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-014</t>
+  </si>
+  <si>
+    <t>Verify responsive structure at tablet width 768px</t>
+  </si>
+  <si>
+    <t>888ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-015</t>
+  </si>
+  <si>
+    <t>Restore browser window maximization state</t>
+  </si>
+  <si>
+    <t>39ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-016</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for email input</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-017</t>
+  </si>
+  <si>
+    <t>Verify HTML tag specification for password input</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-018</t>
+  </si>
+  <si>
+    <t>Verify card wrapper styles (border-radius)</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-019</t>
+  </si>
+  <si>
+    <t>Verify background styling matches design spec</t>
+  </si>
+  <si>
+    <t>25ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-020</t>
+  </si>
+  <si>
+    <t>Verify focus state click handler does not crash</t>
+  </si>
+  <si>
+    <t>133ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-021</t>
+  </si>
+  <si>
+    <t>Verify top-level container viewport classes</t>
+  </si>
+  <si>
     <t>47ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-010</t>
-  </si>
-  <si>
-    <t>Verify font family CSS on headers</t>
-  </si>
-  <si>
-    <t>56ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-011</t>
-  </si>
-  <si>
-    <t>Verify primary brand color on buttons</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-012</t>
-  </si>
-  <si>
-    <t>Verify centered block layout</t>
-  </si>
-  <si>
-    <t>49ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-013</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at mobile width 360px</t>
-  </si>
-  <si>
-    <t>1001ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-014</t>
-  </si>
-  <si>
-    <t>Verify responsive structure at tablet width 768px</t>
-  </si>
-  <si>
-    <t>966ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-015</t>
-  </si>
-  <si>
-    <t>Restore browser window maximization state</t>
-  </si>
-  <si>
-    <t>84ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-016</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for email input</t>
-  </si>
-  <si>
-    <t>100ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-017</t>
-  </si>
-  <si>
-    <t>Verify HTML tag specification for password input</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-018</t>
-  </si>
-  <si>
-    <t>Verify card wrapper styles (border-radius)</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-019</t>
-  </si>
-  <si>
-    <t>Verify background styling matches design spec</t>
+    <t>TC-WEB-UI-022</t>
+  </si>
+  <si>
+    <t>Verify branding and form division layout margins</t>
+  </si>
+  <si>
+    <t>26ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-023</t>
+  </si>
+  <si>
+    <t>Verify clear textual contrast for reader accessibility</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-024</t>
+  </si>
+  <si>
+    <t>Verify page scales properly without layout clipping</t>
+  </si>
+  <si>
+    <t>34ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-025</t>
+  </si>
+  <si>
+    <t>Verify smooth interactive transitions on button inputs</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-LOGI-MOB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Login Page on Mobile Portrait (375x812)</t>
+  </si>
+  <si>
+    <t>462ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Login Page on Mobile Landscape (812x375)</t>
+  </si>
+  <si>
+    <t>444ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-LOGI-TAB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Login Page on Tablet Portrait (768x1024)</t>
+  </si>
+  <si>
+    <t>446ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Login Page on Tablet Landscape (1024x768)</t>
+  </si>
+  <si>
+    <t>96ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-LOGI-DES</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Login Page on Desktop HD (1440x900)</t>
+  </si>
+  <si>
+    <t>483ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-DASH-MOB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Dashboard on Mobile Portrait (375x812)</t>
+  </si>
+  <si>
+    <t>449ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Dashboard on Mobile Landscape (812x375)</t>
+  </si>
+  <si>
+    <t>448ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-DASH-TAB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Dashboard on Tablet Portrait (768x1024)</t>
+  </si>
+  <si>
+    <t>437ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Dashboard on Tablet Landscape (1024x768)</t>
+  </si>
+  <si>
+    <t>93ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-DASH-DES</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Dashboard on Desktop HD (1440x900)</t>
+  </si>
+  <si>
+    <t>453ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-CUST-MOB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Customers list on Mobile Portrait (375x812)</t>
+  </si>
+  <si>
+    <t>452ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Customers list on Mobile Landscape (812x375)</t>
+  </si>
+  <si>
+    <t>435ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-CUST-TAB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Customers list on Tablet Portrait (768x1024)</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Customers list on Tablet Landscape (1024x768)</t>
+  </si>
+  <si>
+    <t>111ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-CUST-DES</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Customers list on Desktop HD (1440x900)</t>
+  </si>
+  <si>
+    <t>447ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-SALE-MOB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Sales list on Mobile Portrait (375x812)</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Sales list on Mobile Landscape (812x375)</t>
+  </si>
+  <si>
+    <t>436ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-SALE-TAB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Sales list on Tablet Portrait (768x1024)</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Sales list on Tablet Landscape (1024x768)</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-SALE-DES</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Sales list on Desktop HD (1440x900)</t>
+  </si>
+  <si>
+    <t>451ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-PAYM-MOB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Payments list on Mobile Portrait (375x812)</t>
+  </si>
+  <si>
+    <t>431ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Payments list on Mobile Landscape (812x375)</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-PAYM-TAB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Payments list on Tablet Portrait (768x1024)</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Payments list on Tablet Landscape (1024x768)</t>
+  </si>
+  <si>
+    <t>92ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-PAYM-DES</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Payments list on Desktop HD (1440x900)</t>
+  </si>
+  <si>
+    <t>443ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-LEDG-MOB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Ledger view on Mobile Portrait (375x812)</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Ledger view on Mobile Landscape (812x375)</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-LEDG-TAB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Ledger view on Tablet Portrait (768x1024)</t>
+  </si>
+  <si>
+    <t>458ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Ledger view on Tablet Landscape (1024x768)</t>
+  </si>
+  <si>
+    <t>112ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-LEDG-DES</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Ledger view on Desktop HD (1440x900)</t>
+  </si>
+  <si>
+    <t>485ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-INST-MOB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Installments view on Mobile Portrait (375x812)</t>
+  </si>
+  <si>
+    <t>455ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Installments view on Mobile Landscape (812x375)</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-INST-TAB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Installments view on Tablet Portrait (768x1024)</t>
+  </si>
+  <si>
+    <t>459ms</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Installments view on Tablet Landscape (1024x768)</t>
+  </si>
+  <si>
+    <t>97ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-INST-DES</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Installments view on Desktop HD (1440x900)</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-SETT-MOB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Settings view on Mobile Portrait (375x812)</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Settings view on Mobile Landscape (812x375)</t>
+  </si>
+  <si>
+    <t>441ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-SETT-TAB</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Settings view on Tablet Portrait (768x1024)</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Settings view on Tablet Landscape (1024x768)</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-RESP-SETT-DES</t>
+  </si>
+  <si>
+    <t>Verify responsive viewport layout scaling for Settings view on Desktop HD (1440x900)</t>
+  </si>
+  <si>
+    <t>469ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-LOGI-SW</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /login</t>
+  </si>
+  <si>
+    <t>0ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-LOGI-MAN</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /login</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-LOGI-CACHE</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /login</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-DASH-SW</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /dashboard</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-DASH-MAN</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /dashboard</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-DASH-CACHE</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /dashboard</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-CUST-SW</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /customers</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-CUST-MAN</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /customers</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-CUST-CACHE</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /customers</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-SALE-SW</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /sales</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-SALE-MAN</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /sales</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-SALE-CACHE</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /sales</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-PAYM-SW</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /payments</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-PAYM-MAN</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /payments</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-PAYM-CACHE</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /payments</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-LEDG-SW</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /ledger</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-LEDG-MAN</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /ledger</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-LEDG-CACHE</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /ledger</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-INST-SW</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /installments</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-INST-MAN</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /installments</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-INST-CACHE</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /installments</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-SETT-SW</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /settings</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-SETT-MAN</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /settings</t>
+  </si>
+  <si>
+    <t>TC-WEB-UI-PWA-SETT-CACHE</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /settings</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /sales/create</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /sales/create</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /sales/create</t>
+  </si>
+  <si>
+    <t>Verify PWA Service Worker registration availability compliance for path /payments/record</t>
+  </si>
+  <si>
+    <t>Verify PWA Web Manifest link reference configuration compliance for path /payments/record</t>
+  </si>
+  <si>
+    <t>Verify PWA Offline static assets headers verification compliance for path /payments/record</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-001</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Verify invalid login rejection message</t>
+  </si>
+  <si>
+    <t>2196ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-002</t>
+  </si>
+  <si>
+    <t>Verify rejection of nonexistent email</t>
+  </si>
+  <si>
+    <t>947ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-003</t>
+  </si>
+  <si>
+    <t>Verify successful login with valid credentials redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>1982ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-004</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Total Customers count</t>
+  </si>
+  <si>
+    <t>505ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-FUNC-005</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays Active Sales count</t>
   </si>
   <si>
     <t>42ms</t>
   </si>
   <si>
-    <t>TC-WEB-UI-020</t>
-  </si>
-  <si>
-    <t>Verify focus state click handler does not crash</t>
-  </si>
-  <si>
-    <t>229ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-021</t>
-  </si>
-  <si>
-    <t>Verify top-level container viewport classes</t>
-  </si>
-  <si>
-    <t>45ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-022</t>
-  </si>
-  <si>
-    <t>Verify branding and form division layout margins</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-023</t>
-  </si>
-  <si>
-    <t>Verify clear textual contrast for reader accessibility</t>
-  </si>
-  <si>
-    <t>60ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-024</t>
-  </si>
-  <si>
-    <t>Verify page scales properly without layout clipping</t>
-  </si>
-  <si>
-    <t>TC-WEB-UI-025</t>
-  </si>
-  <si>
-    <t>Verify smooth interactive transitions on button inputs</t>
-  </si>
-  <si>
-    <t>64ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-001</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>Verify invalid login rejection message</t>
-  </si>
-  <si>
-    <t>2667ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-002</t>
-  </si>
-  <si>
-    <t>Verify rejection of nonexistent email</t>
-  </si>
-  <si>
-    <t>1659ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-003</t>
-  </si>
-  <si>
-    <t>Verify successful login with valid credentials redirects to Dashboard</t>
-  </si>
-  <si>
-    <t>5564ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-004</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Total Customers count</t>
-  </si>
-  <si>
-    <t>2248ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-FUNC-005</t>
-  </si>
-  <si>
-    <t>Verify dashboard displays Active Sales count</t>
-  </si>
-  <si>
     <t>TC-WEB-FUNC-006</t>
   </si>
   <si>
     <t>Verify dashboard displays Pending Installments count</t>
   </si>
   <si>
-    <t>5211ms</t>
+    <t>5072ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-007</t>
@@ -320,22 +752,22 @@
     <t>Verify dashboard displays Today's Due count</t>
   </si>
   <si>
+    <t>17ms</t>
+  </si>
+  <si>
     <t>TC-WEB-FUNC-008</t>
   </si>
   <si>
     <t>Verify dashboard displays Outstanding Balance amount</t>
   </si>
   <si>
-    <t>32ms</t>
-  </si>
-  <si>
     <t>TC-WEB-FUNC-009</t>
   </si>
   <si>
     <t>Navigate to customers page and verify header</t>
   </si>
   <si>
-    <t>377ms</t>
+    <t>297ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-010</t>
@@ -344,16 +776,13 @@
     <t>Verify add new customer input inputs are present</t>
   </si>
   <si>
-    <t>67ms</t>
-  </si>
-  <si>
     <t>TC-WEB-FUNC-011</t>
   </si>
   <si>
     <t>Verify customer creation and entry addition to table</t>
   </si>
   <si>
-    <t>3059ms</t>
+    <t>2958ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-012</t>
@@ -362,7 +791,7 @@
     <t>Verify presence of seeded customer</t>
   </si>
   <si>
-    <t>43ms</t>
+    <t>54ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-013</t>
@@ -371,7 +800,7 @@
     <t>Navigate to specific customer profile page</t>
   </si>
   <si>
-    <t>3143ms</t>
+    <t>1272ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-014</t>
@@ -386,7 +815,7 @@
     <t>Verify Total Amount financial card is 1000 INR</t>
   </si>
   <si>
-    <t>39ms</t>
+    <t>21ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-016</t>
@@ -395,31 +824,28 @@
     <t>Verify Paid Amount financial card is 0 INR</t>
   </si>
   <si>
-    <t>36ms</t>
-  </si>
-  <si>
     <t>TC-WEB-FUNC-017</t>
   </si>
   <si>
     <t>Verify Outstanding Balance financial card is 1000 INR</t>
   </si>
   <si>
-    <t>35ms</t>
-  </si>
-  <si>
     <t>TC-WEB-FUNC-018</t>
   </si>
   <si>
     <t>Verify E2E Test Item pending sale is loaded in sales list</t>
   </si>
   <si>
+    <t>27ms</t>
+  </si>
+  <si>
     <t>TC-WEB-FUNC-019</t>
   </si>
   <si>
     <t>Verify redirect to record payment page</t>
   </si>
   <si>
-    <t>6593ms</t>
+    <t>774ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-020</t>
@@ -428,7 +854,7 @@
     <t>Verify remaining balance display match before payment</t>
   </si>
   <si>
-    <t>289ms</t>
+    <t>22ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-021</t>
@@ -437,7 +863,7 @@
     <t>Record payment E2E execution and redirection validation</t>
   </si>
   <si>
-    <t>5100ms</t>
+    <t>3054ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-022</t>
@@ -446,7 +872,7 @@
     <t>Verify Outstanding Balance updates to 800 INR in customer card</t>
   </si>
   <si>
-    <t>3376ms</t>
+    <t>1368ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-023</t>
@@ -461,16 +887,13 @@
     <t>Verify recorded payment entry list matches mode UPI</t>
   </si>
   <si>
-    <t>55ms</t>
-  </si>
-  <si>
     <t>TC-WEB-FUNC-025</t>
   </si>
   <si>
     <t>Verify sales management index loads properly</t>
   </si>
   <si>
-    <t>2581ms</t>
+    <t>788ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-026</t>
@@ -479,7 +902,7 @@
     <t>Verify sales search filter works properly</t>
   </si>
   <si>
-    <t>817ms</t>
+    <t>691ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-027</t>
@@ -488,7 +911,7 @@
     <t>Navigate to Create New Sale form</t>
   </si>
   <si>
-    <t>2949ms</t>
+    <t>571ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-028</t>
@@ -497,7 +920,7 @@
     <t>Verify total amount computed automatically (2 x 500 = 1000)</t>
   </si>
   <si>
-    <t>700ms</t>
+    <t>228ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-029</t>
@@ -506,7 +929,7 @@
     <t>Create sale and verify redirect back to sales table</t>
   </si>
   <si>
-    <t>568ms</t>
+    <t>214ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-030</t>
@@ -515,7 +938,7 @@
     <t>Verify Payments page path and title</t>
   </si>
   <si>
-    <t>2138ms</t>
+    <t>796ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-031</t>
@@ -524,7 +947,7 @@
     <t>Verify E2E transaction exists in master list</t>
   </si>
   <si>
-    <t>75ms</t>
+    <t>104ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-032</t>
@@ -533,7 +956,7 @@
     <t>Verify Ledger Book page loads</t>
   </si>
   <si>
-    <t>1956ms</t>
+    <t>848ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-033</t>
@@ -542,7 +965,7 @@
     <t>Verify ledger records contain client name</t>
   </si>
   <si>
-    <t>175ms</t>
+    <t>241ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-034</t>
@@ -551,7 +974,7 @@
     <t>Verify Installments page title</t>
   </si>
   <si>
-    <t>6373ms</t>
+    <t>996ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-035</t>
@@ -560,13 +983,16 @@
     <t>Verify customer details exist on installment board</t>
   </si>
   <si>
+    <t>24ms</t>
+  </si>
+  <si>
     <t>TC-WEB-FUNC-036</t>
   </si>
   <si>
     <t>Verify direct Dashboard URL redirect</t>
   </si>
   <si>
-    <t>2878ms</t>
+    <t>119ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-037</t>
@@ -575,7 +1001,7 @@
     <t>Verify customer data updates dynamically on UI edit</t>
   </si>
   <si>
-    <t>6216ms</t>
+    <t>4422ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-038</t>
@@ -584,7 +1010,7 @@
     <t>Verify logout route terminates session and redirects to sign in</t>
   </si>
   <si>
-    <t>5921ms</t>
+    <t>5128ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-039</t>
@@ -593,7 +1019,7 @@
     <t>Verify unauthorized dashboard access redirects to login</t>
   </si>
   <si>
-    <t>2829ms</t>
+    <t>2104ms</t>
   </si>
   <si>
     <t>TC-WEB-FUNC-040</t>
@@ -602,7 +1028,7 @@
     <t>Verify unauthorized customer details access redirects to login</t>
   </si>
   <si>
-    <t>3356ms</t>
+    <t>2130ms</t>
   </si>
   <si>
     <t>TC-WEB-UNIT-001</t>
@@ -614,18 +1040,12 @@
     <t>Test formatCurrency formatting positive amount</t>
   </si>
   <si>
-    <t>78ms</t>
-  </si>
-  <si>
     <t>TC-WEB-UNIT-002</t>
   </si>
   <si>
     <t>Test formatCurrency formatting zero amount</t>
   </si>
   <si>
-    <t>0ms</t>
-  </si>
-  <si>
     <t>TC-WEB-UNIT-003</t>
   </si>
   <si>
@@ -638,106 +1058,526 @@
     <t>Test formatCurrency formatting large millions scale amount</t>
   </si>
   <si>
+    <t>TC-WEB-UNIT-005</t>
+  </si>
+  <si>
+    <t>Test formatCurrency decimal rounding functionality</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-006</t>
+  </si>
+  <si>
+    <t>Test formatDate string matching date details</t>
+  </si>
+  <si>
+    <t>4ms</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-007</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for null values</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-008</t>
+  </si>
+  <si>
+    <t>Test formatDate fallback for 0 value</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-009</t>
+  </si>
+  <si>
+    <t>Test formatDateTime details formatting</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-010</t>
+  </si>
+  <si>
+    <t>Test formatDateTime null timestamp handling</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-011</t>
+  </si>
+  <si>
+    <t>Verify email validation for valid string</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-012</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing TLD</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-013</t>
+  </si>
+  <si>
+    <t>Verify email validation blocks missing alias prefix</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-014</t>
+  </si>
+  <si>
+    <t>Verify phone validation for standard 10 digit number</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-015</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks short length</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-016</t>
+  </si>
+  <si>
+    <t>Verify phone validation blocks alphabetic characters</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-017</t>
+  </si>
+  <si>
+    <t>Verify interest formula multiplication logic</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-018</t>
+  </si>
+  <si>
+    <t>Verify installment partitioning amount division</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-019</t>
+  </si>
+  <si>
+    <t>Verify remaining balance arithmetic subtraction</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-020</t>
+  </si>
+  <si>
+    <t>Verify mock environment manifest validator passes</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-0-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 0 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-0-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 0 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-0-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 0 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-0-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 0 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-0-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 0 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
     <t>1ms</t>
   </si>
   <si>
-    <t>TC-WEB-UNIT-005</t>
-  </si>
-  <si>
-    <t>Test formatCurrency decimal rounding functionality</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-006</t>
-  </si>
-  <si>
-    <t>Test formatDate string matching date details</t>
-  </si>
-  <si>
-    <t>20ms</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-007</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for null values</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-008</t>
-  </si>
-  <si>
-    <t>Test formatDate fallback for 0 value</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-009</t>
-  </si>
-  <si>
-    <t>Test formatDateTime details formatting</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-010</t>
-  </si>
-  <si>
-    <t>Test formatDateTime null timestamp handling</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-011</t>
-  </si>
-  <si>
-    <t>Verify email validation for valid string</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-012</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing TLD</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-013</t>
-  </si>
-  <si>
-    <t>Verify email validation blocks missing alias prefix</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-014</t>
-  </si>
-  <si>
-    <t>Verify phone validation for standard 10 digit number</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-015</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks short length</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-016</t>
-  </si>
-  <si>
-    <t>Verify phone validation blocks alphabetic characters</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-017</t>
-  </si>
-  <si>
-    <t>Verify interest formula multiplication logic</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-018</t>
-  </si>
-  <si>
-    <t>Verify installment partitioning amount division</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-019</t>
-  </si>
-  <si>
-    <t>Verify remaining balance arithmetic subtraction</t>
-  </si>
-  <si>
-    <t>TC-WEB-UNIT-020</t>
-  </si>
-  <si>
-    <t>Verify mock environment manifest validator passes</t>
+    <t>TC-WEB-UNIT-FMT-10-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-250-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 250 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-250-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 250 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-250-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 250 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-250-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 250 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-250-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 250 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-500-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 500 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-500-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 500 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-500-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 500 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-500-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 500 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-500-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 500 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5000-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5000 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5000-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5000 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5000-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5000 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5000-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5000 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-5000-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 5000 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10000-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10000 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10000-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10000 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10000-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10000 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10000-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10000 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-10000-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 10000 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50000-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50000 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50000-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50000 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50000-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50000 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50000-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50000 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-50000-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 50000 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100000-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100000 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100000-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100000 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100000-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100000 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100000-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100000 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-100000-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 100000 on Maximum fraction digit limits check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000000-CURR</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000000 on en-IN Currency format conformity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000000-RND</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000000 on Decimal precision rounding integrity</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000000-DLT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000000 on Business ledger delta calculation check</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000000-DIV</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000000 on Installment division partition accuracy</t>
+  </si>
+  <si>
+    <t>TC-WEB-UNIT-FMT-1000000-LMT</t>
+  </si>
+  <si>
+    <t>Verify unit mathematical helper for value 1000000 on Maximum fraction digit limits check</t>
   </si>
   <si>
     <t>TC-WEB-VAL-001</t>
@@ -749,7 +1589,7 @@
     <t>Verify email required constraint is enabled on form</t>
   </si>
   <si>
-    <t>7170ms</t>
+    <t>5112ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-002</t>
@@ -758,7 +1598,7 @@
     <t>Verify password required constraint is enabled on form</t>
   </si>
   <si>
-    <t>5187ms</t>
+    <t>5027ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-003</t>
@@ -767,9 +1607,6 @@
     <t>Verify browser client blocks submissions for invalid email inputs</t>
   </si>
   <si>
-    <t>5127ms</t>
-  </si>
-  <si>
     <t>TC-WEB-VAL-004</t>
   </si>
   <si>
@@ -782,7 +1619,7 @@
     <t>Verify customer creation form prevents empty submit</t>
   </si>
   <si>
-    <t>11622ms</t>
+    <t>10163ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-006</t>
@@ -791,7 +1628,7 @@
     <t>Verify phone input uses tel semantic element type</t>
   </si>
   <si>
-    <t>5118ms</t>
+    <t>5031ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-007</t>
@@ -800,7 +1637,7 @@
     <t>Verify sale quantity requires positive minimum value (&gt; 0)</t>
   </si>
   <si>
-    <t>9879ms</t>
+    <t>800ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-008</t>
@@ -809,9 +1646,6 @@
     <t>Verify unit price input restricts negative numbers</t>
   </si>
   <si>
-    <t>2552ms</t>
-  </si>
-  <si>
     <t>TC-WEB-VAL-009</t>
   </si>
   <si>
@@ -821,7 +1655,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>5825ms</t>
+    <t>2489ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-010</t>
@@ -836,7 +1670,7 @@
     <t>Verify error prevents overpayment collections</t>
   </si>
   <si>
-    <t>3060ms</t>
+    <t>2039ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-012</t>
@@ -845,7 +1679,7 @@
     <t>Verify collection input restricts 0 value submissions</t>
   </si>
   <si>
-    <t>1323ms</t>
+    <t>1163ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-013</t>
@@ -860,7 +1694,7 @@
     <t>Verify wildcard URLs redirect to main route base</t>
   </si>
   <si>
-    <t>2466ms</t>
+    <t>2133ms</t>
   </si>
   <si>
     <t>TC-WEB-VAL-015</t>
@@ -869,7 +1703,367 @@
     <t>Verify HTML password hidden mask attribute config</t>
   </si>
   <si>
-    <t>6420ms</t>
+    <t>5152ms</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNEML-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Email on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNEML-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Email on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNEML-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Email on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNEML-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Email on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNEML-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Email on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNPAS-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Password on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNPAS-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Password on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNPAS-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Password on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNPAS-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Password on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-LGNPAS-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Login Password on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTNAM-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Name on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTNAM-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Name on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTNAM-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Name on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTNAM-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Name on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTNAM-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Name on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTEML-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Email on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTEML-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Email on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTEML-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Email on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTEML-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Email on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTEML-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Email on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTPHN-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Phone on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTPHN-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Phone on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTPHN-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Phone on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTPHN-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Phone on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTPHN-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Phone on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTADR-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Address on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTADR-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Address on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTADR-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Address on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTADR-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Address on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-CSTADR-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Customer Address on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLITM-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Item Name on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLITM-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Item Name on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLITM-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Item Name on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLITM-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Item Name on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLITM-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Item Name on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLQTY-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Quantity on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLQTY-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Quantity on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLQTY-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Quantity on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLQTY-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Quantity on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLQTY-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Quantity on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLPRC-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Unit Price on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLPRC-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Unit Price on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLPRC-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Unit Price on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLPRC-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Unit Price on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-SLPRC-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Sale Unit Price on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTAMT-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Amount on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTAMT-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Amount on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTAMT-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Amount on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTAMT-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Amount on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTAMT-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Amount on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTREM-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Remarks on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTREM-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Remarks on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTREM-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Remarks on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTREM-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Remarks on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-PMTREM-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Payment Remarks on Syntax format conformity audits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-FLTQRY-EMPTY</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Filter Search Box on Empty value constraint checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-FLTQRY-LIMIT</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Filter Search Box on Excessive character buffer limits</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-FLTQRY-SAN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Filter Search Box on HTML script sanitation validations</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-FLTQRY-BND</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Filter Search Box on Lower/Upper boundary constraints</t>
+  </si>
+  <si>
+    <t>TC-SEC-VAL-FLTQRY-SYN</t>
+  </si>
+  <si>
+    <t>Verify input validation rule for Filter Search Box on Syntax format conformity audits</t>
   </si>
   <si>
     <t>TC-WEB-DEP-001</t>
@@ -884,7 +2078,7 @@
     <t>Performance</t>
   </si>
   <si>
-    <t>705ms</t>
+    <t>329ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-002</t>
@@ -893,7 +2087,7 @@
     <t>Verify full render transition load time under limit</t>
   </si>
   <si>
-    <t>10680ms</t>
+    <t>10159ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-003</t>
@@ -908,7 +2102,7 @@
     <t>Verify favicon.ico endpoint yields clean HTTP status</t>
   </si>
   <si>
-    <t>363ms</t>
+    <t>120ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-005</t>
@@ -923,31 +2117,28 @@
     <t>Verify head links contain manifest registration details</t>
   </si>
   <si>
+    <t>174ms</t>
+  </si>
+  <si>
     <t>TC-WEB-DEP-007</t>
   </si>
   <si>
     <t>Verify console logs have no severe exceptions during login page session</t>
   </si>
   <si>
-    <t>8ms</t>
-  </si>
-  <si>
     <t>TC-WEB-DEP-008</t>
   </si>
   <si>
     <t>Verify standard responsive layouts align horizontally</t>
   </si>
   <si>
-    <t>50ms</t>
+    <t>9ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-009</t>
   </si>
   <si>
     <t>Verify DOM count index scales cleanly</t>
-  </si>
-  <si>
-    <t>16ms</t>
   </si>
   <si>
     <t>TC-WEB-DEP-010</t>
@@ -1377,7 +2568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1544,7 +2735,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -1552,13 +2743,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1567,7 +2758,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1575,13 +2766,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1590,7 +2781,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1598,13 +2789,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1613,7 +2804,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1621,13 +2812,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1636,7 +2827,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -1644,13 +2835,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1659,7 +2850,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1667,13 +2858,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1682,7 +2873,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -1690,13 +2881,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1705,7 +2896,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1713,13 +2904,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1728,7 +2919,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1736,13 +2927,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1751,7 +2942,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1759,13 +2950,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1774,7 +2965,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -1782,13 +2973,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1797,7 +2988,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -1805,13 +2996,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1828,13 +3019,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1843,7 +3034,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -1851,13 +3042,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1866,7 +3057,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -1874,13 +3065,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1889,7 +3080,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -1897,13 +3088,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1920,13 +3111,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1935,7 +3126,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1943,13 +3134,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1958,7 +3149,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1966,13 +3157,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1981,9 +3172,1619 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2032,22 +4833,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2055,22 +4856,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>86</v>
+        <v>229</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -2078,22 +4879,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>230</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>88</v>
+        <v>231</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>232</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -2101,22 +4902,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>90</v>
+        <v>233</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>91</v>
+        <v>234</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -2124,22 +4925,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>93</v>
+        <v>236</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>94</v>
+        <v>237</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -2147,22 +4948,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>95</v>
+        <v>239</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>96</v>
+        <v>240</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>97</v>
+        <v>241</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -2170,22 +4971,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>242</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>99</v>
+        <v>243</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
+        <v>244</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2193,22 +4994,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>101</v>
+        <v>246</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2216,22 +5017,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>248</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -2239,22 +5040,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>107</v>
+        <v>251</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -2262,22 +5063,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>109</v>
+        <v>252</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>110</v>
+        <v>253</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -2285,22 +5086,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>112</v>
+        <v>255</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>113</v>
+        <v>256</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>114</v>
+        <v>257</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -2308,22 +5109,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>115</v>
+        <v>258</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>116</v>
+        <v>259</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>117</v>
+        <v>260</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -2331,22 +5132,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>119</v>
+        <v>262</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -2354,22 +5155,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>120</v>
+        <v>263</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>121</v>
+        <v>264</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>122</v>
+        <v>265</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -2377,22 +5178,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>123</v>
+        <v>266</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>124</v>
+        <v>267</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2400,22 +5201,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>126</v>
+        <v>268</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>127</v>
+        <v>269</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2423,22 +5224,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>270</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>130</v>
+        <v>271</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>125</v>
+        <v>272</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2446,22 +5247,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>131</v>
+        <v>273</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>132</v>
+        <v>274</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>133</v>
+        <v>275</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2469,22 +5270,22 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>134</v>
+        <v>276</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>136</v>
+        <v>278</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2492,22 +5293,22 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>138</v>
+        <v>280</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>139</v>
+        <v>281</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2515,22 +5316,22 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>141</v>
+        <v>283</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>142</v>
+        <v>284</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2538,22 +5339,22 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>144</v>
+        <v>286</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2561,22 +5362,22 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>146</v>
+        <v>288</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2584,22 +5385,22 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>148</v>
+        <v>289</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>149</v>
+        <v>290</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>150</v>
+        <v>291</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2607,22 +5408,22 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>151</v>
+        <v>292</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>152</v>
+        <v>293</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>153</v>
+        <v>294</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2630,22 +5431,22 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>154</v>
+        <v>295</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>155</v>
+        <v>296</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>156</v>
+        <v>297</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -2653,22 +5454,22 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>157</v>
+        <v>298</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>158</v>
+        <v>299</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>159</v>
+        <v>300</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -2676,22 +5477,22 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>160</v>
+        <v>301</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>161</v>
+        <v>302</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>162</v>
+        <v>303</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2699,22 +5500,22 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>164</v>
+        <v>305</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>165</v>
+        <v>306</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2722,22 +5523,22 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>166</v>
+        <v>307</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>168</v>
+        <v>309</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2745,22 +5546,22 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>169</v>
+        <v>310</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>170</v>
+        <v>311</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2768,22 +5569,22 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>172</v>
+        <v>313</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>173</v>
+        <v>314</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>174</v>
+        <v>315</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2791,22 +5592,22 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>176</v>
+        <v>317</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>177</v>
+        <v>318</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2814,22 +5615,22 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>179</v>
+        <v>320</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>74</v>
+        <v>321</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2837,22 +5638,22 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>180</v>
+        <v>322</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>181</v>
+        <v>323</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>182</v>
+        <v>324</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2860,22 +5661,22 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>183</v>
+        <v>325</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>184</v>
+        <v>326</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>185</v>
+        <v>327</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2883,22 +5684,22 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>187</v>
+        <v>329</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>188</v>
+        <v>330</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2906,22 +5707,22 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>189</v>
+        <v>331</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>190</v>
+        <v>332</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>191</v>
+        <v>333</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -2929,22 +5730,22 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>192</v>
+        <v>334</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>193</v>
+        <v>335</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>194</v>
+        <v>336</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -2958,7 +5759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2995,22 +5796,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>195</v>
+        <v>337</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>197</v>
+        <v>339</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>198</v>
+        <v>36</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3018,22 +5819,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>199</v>
+        <v>340</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>200</v>
+        <v>341</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3041,22 +5842,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>203</v>
+        <v>343</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3064,22 +5865,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>204</v>
+        <v>344</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>205</v>
+        <v>345</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3087,22 +5888,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>207</v>
+        <v>346</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>208</v>
+        <v>347</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3110,22 +5911,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>210</v>
+        <v>349</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>211</v>
+        <v>350</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3133,22 +5934,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>212</v>
+        <v>351</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>213</v>
+        <v>352</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3156,22 +5957,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>214</v>
+        <v>353</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>215</v>
+        <v>354</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3179,22 +5980,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>355</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>217</v>
+        <v>356</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3202,22 +6003,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>218</v>
+        <v>357</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>219</v>
+        <v>358</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3225,22 +6026,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>220</v>
+        <v>359</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>221</v>
+        <v>360</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3248,22 +6049,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>222</v>
+        <v>361</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>223</v>
+        <v>362</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3271,22 +6072,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>363</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>225</v>
+        <v>364</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3294,22 +6095,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>226</v>
+        <v>365</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>227</v>
+        <v>366</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3317,22 +6118,22 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>228</v>
+        <v>367</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>229</v>
+        <v>368</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -3340,22 +6141,22 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>231</v>
+        <v>370</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -3363,22 +6164,22 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>232</v>
+        <v>371</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>233</v>
+        <v>372</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -3386,22 +6187,22 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>234</v>
+        <v>373</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>235</v>
+        <v>374</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -3409,22 +6210,22 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>236</v>
+        <v>375</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>237</v>
+        <v>376</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -3432,24 +6233,1634 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>238</v>
+        <v>377</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>239</v>
+        <v>378</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G91" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3461,7 +7872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3498,22 +7909,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>520</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>242</v>
+        <v>522</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>243</v>
+        <v>523</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3521,22 +7932,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>244</v>
+        <v>524</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>245</v>
+        <v>525</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>246</v>
+        <v>526</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3544,22 +7955,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>247</v>
+        <v>527</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>248</v>
+        <v>528</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>249</v>
+        <v>526</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3567,22 +7978,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>250</v>
+        <v>529</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>251</v>
+        <v>530</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3590,22 +8001,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>252</v>
+        <v>531</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>253</v>
+        <v>532</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>254</v>
+        <v>533</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -3613,22 +8024,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>255</v>
+        <v>534</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>256</v>
+        <v>535</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>257</v>
+        <v>536</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -3636,22 +8047,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>258</v>
+        <v>537</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>259</v>
+        <v>538</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>260</v>
+        <v>539</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3659,22 +8070,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>540</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>262</v>
+        <v>541</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>263</v>
+        <v>19</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -3682,22 +8093,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>264</v>
+        <v>542</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>265</v>
+        <v>543</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>266</v>
+        <v>544</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>267</v>
+        <v>545</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -3705,22 +8116,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>268</v>
+        <v>546</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>269</v>
+        <v>547</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>266</v>
+        <v>544</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3728,22 +8139,22 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>270</v>
+        <v>548</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>271</v>
+        <v>549</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>272</v>
+        <v>550</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -3751,22 +8162,22 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>273</v>
+        <v>551</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>274</v>
+        <v>552</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>275</v>
+        <v>553</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>13</v>
@@ -3774,22 +8185,22 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>276</v>
+        <v>554</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>277</v>
+        <v>555</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -3797,22 +8208,22 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>278</v>
+        <v>556</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>279</v>
+        <v>557</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>280</v>
+        <v>558</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -3820,24 +8231,1404 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>281</v>
+        <v>559</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>241</v>
+        <v>521</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>282</v>
+        <v>560</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>266</v>
+        <v>544</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>283</v>
+        <v>561</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3886,22 +9677,22 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>284</v>
+        <v>682</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>286</v>
+        <v>684</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>287</v>
+        <v>685</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>288</v>
+        <v>686</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -3909,22 +9700,22 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>289</v>
+        <v>687</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>290</v>
+        <v>688</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>287</v>
+        <v>685</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>291</v>
+        <v>689</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -3932,22 +9723,22 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>292</v>
+        <v>690</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>293</v>
+        <v>691</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -3955,22 +9746,22 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>294</v>
+        <v>692</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>295</v>
+        <v>693</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>296</v>
+        <v>694</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -3978,22 +9769,22 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>297</v>
+        <v>695</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>298</v>
+        <v>696</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>266</v>
+        <v>544</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -4001,22 +9792,22 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>299</v>
+        <v>697</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>300</v>
+        <v>698</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>162</v>
+        <v>699</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -4024,22 +9815,22 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>301</v>
+        <v>700</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>302</v>
+        <v>701</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>287</v>
+        <v>685</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -4047,22 +9838,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>304</v>
+        <v>702</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>305</v>
+        <v>703</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>287</v>
+        <v>685</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>306</v>
+        <v>704</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -4070,22 +9861,22 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>307</v>
+        <v>705</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>308</v>
+        <v>706</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>287</v>
+        <v>685</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>309</v>
+        <v>704</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -4093,22 +9884,22 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>310</v>
+        <v>707</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>311</v>
+        <v>708</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>285</v>
+        <v>683</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
